--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -6764,10 +6764,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121134873</v>
+        <v>121134866</v>
       </c>
       <c r="B48" t="n">
-        <v>77535</v>
+        <v>90705</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6780,21 +6780,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6804,10 +6804,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>446269</v>
+        <v>446218</v>
       </c>
       <c r="R48" t="n">
-        <v>7026478</v>
+        <v>7026544</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6896,10 +6896,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121134866</v>
+        <v>121134853</v>
       </c>
       <c r="B49" t="n">
-        <v>90705</v>
+        <v>74696</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6908,25 +6908,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6936,10 +6936,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446218</v>
+        <v>445965</v>
       </c>
       <c r="R49" t="n">
-        <v>7026544</v>
+        <v>7026512</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121134853</v>
+        <v>121134873</v>
       </c>
       <c r="B50" t="n">
-        <v>74696</v>
+        <v>77535</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7040,25 +7040,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>492</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7068,10 +7068,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445965</v>
+        <v>446269</v>
       </c>
       <c r="R50" t="n">
-        <v>7026512</v>
+        <v>7026478</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -9264,10 +9264,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121132928</v>
+        <v>121134867</v>
       </c>
       <c r="B67" t="n">
-        <v>78598</v>
+        <v>77535</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9280,43 +9280,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>446290</v>
+        <v>446244</v>
       </c>
       <c r="R67" t="n">
-        <v>7026577</v>
+        <v>7026516</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9343,17 +9334,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>20 bålar</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9367,7 +9363,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>i gammal gles barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -9382,7 +9378,7 @@
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9400,10 +9396,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121134867</v>
+        <v>121134540</v>
       </c>
       <c r="B68" t="n">
-        <v>77535</v>
+        <v>74691</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9412,25 +9408,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228579</v>
+        <v>306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9440,10 +9436,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>446244</v>
+        <v>446088</v>
       </c>
       <c r="R68" t="n">
-        <v>7026516</v>
+        <v>7026528</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9470,22 +9466,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9494,12 +9490,13 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9514,7 +9511,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9525,17 +9522,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121134540</v>
+        <v>121132928</v>
       </c>
       <c r="B69" t="n">
-        <v>74691</v>
+        <v>78598</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9544,38 +9541,47 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>446088</v>
+        <v>446290</v>
       </c>
       <c r="R69" t="n">
-        <v>7026528</v>
+        <v>7026577</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9602,22 +9608,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>20 bålar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9626,13 +9627,12 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -9909,10 +9909,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121134869</v>
+        <v>121134855</v>
       </c>
       <c r="B72" t="n">
-        <v>90687</v>
+        <v>78598</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9925,21 +9925,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>446262</v>
+        <v>446045</v>
       </c>
       <c r="R72" t="n">
-        <v>7026488</v>
+        <v>7026526</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10041,7 +10041,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121134544</v>
+        <v>121134869</v>
       </c>
       <c r="B73" t="n">
         <v>90687</v>
@@ -10081,10 +10081,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>446005</v>
+        <v>446262</v>
       </c>
       <c r="R73" t="n">
-        <v>7026502</v>
+        <v>7026488</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10111,22 +10111,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10166,17 +10166,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121132950</v>
+        <v>121134544</v>
       </c>
       <c r="B74" t="n">
-        <v>78761</v>
+        <v>90687</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10185,47 +10185,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>446118</v>
+        <v>446005</v>
       </c>
       <c r="R74" t="n">
-        <v>7026441</v>
+        <v>7026502</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10252,17 +10243,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>1 bål</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10276,7 +10272,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -10291,7 +10287,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10302,17 +10298,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121134855</v>
+        <v>121132950</v>
       </c>
       <c r="B75" t="n">
-        <v>78598</v>
+        <v>78761</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10321,38 +10317,47 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>446045</v>
+        <v>446118</v>
       </c>
       <c r="R75" t="n">
-        <v>7026526</v>
+        <v>7026441</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10379,22 +10384,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>1 bål</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121134858</v>
+        <v>121134871</v>
       </c>
       <c r="B76" t="n">
-        <v>90705</v>
+        <v>74517</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10453,25 +10453,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6428</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>446092</v>
+        <v>446269</v>
       </c>
       <c r="R76" t="n">
-        <v>7026520</v>
+        <v>7026478</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10573,10 +10573,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121134542</v>
+        <v>121134858</v>
       </c>
       <c r="B77" t="n">
-        <v>95618</v>
+        <v>90705</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>446080</v>
+        <v>446092</v>
       </c>
       <c r="R77" t="n">
-        <v>7026521</v>
+        <v>7026520</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10643,22 +10643,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10672,7 +10672,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>På mycket gammal granlåga # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10698,17 +10698,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121134871</v>
+        <v>121134542</v>
       </c>
       <c r="B78" t="n">
-        <v>74517</v>
+        <v>95618</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10717,25 +10717,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6428</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10745,10 +10745,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>446269</v>
+        <v>446080</v>
       </c>
       <c r="R78" t="n">
-        <v>7026478</v>
+        <v>7026521</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10775,22 +10775,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På mycket gammal granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -14892,10 +14892,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252823</v>
+        <v>121252837</v>
       </c>
       <c r="B110" t="n">
-        <v>78598</v>
+        <v>77535</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14908,21 +14908,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -14932,10 +14932,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>446274</v>
+        <v>446201</v>
       </c>
       <c r="R110" t="n">
-        <v>7026540</v>
+        <v>7026410</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14967,7 +14967,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15024,10 +15024,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252837</v>
+        <v>121252823</v>
       </c>
       <c r="B111" t="n">
-        <v>77535</v>
+        <v>78598</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15040,21 +15040,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -15064,10 +15064,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446201</v>
+        <v>446274</v>
       </c>
       <c r="R111" t="n">
-        <v>7026410</v>
+        <v>7026540</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -16485,10 +16485,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252806</v>
+        <v>121252811</v>
       </c>
       <c r="B122" t="n">
-        <v>74517</v>
+        <v>90683</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -16497,25 +16497,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6428</v>
+        <v>1108</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -16525,10 +16525,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446038</v>
+        <v>446106</v>
       </c>
       <c r="R122" t="n">
-        <v>7026546</v>
+        <v>7026528</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>i gammal granskog</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16617,10 +16617,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252811</v>
+        <v>121252806</v>
       </c>
       <c r="B123" t="n">
-        <v>90683</v>
+        <v>74517</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16629,25 +16629,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1108</v>
+        <v>6428</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16657,10 +16657,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446106</v>
+        <v>446038</v>
       </c>
       <c r="R123" t="n">
-        <v>7026528</v>
+        <v>7026546</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -3551,10 +3551,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121117416</v>
+        <v>121117887</v>
       </c>
       <c r="B23" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3584,26 +3584,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svedaun, Svedaun, Jmt</t>
+          <t>Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445930</v>
+        <v>446262</v>
       </c>
       <c r="R23" t="n">
-        <v>7026585</v>
+        <v>7026371</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3635,7 +3626,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3645,12 +3636,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 20, långa Gammal gran</t>
+          <t>1 stor garnlav</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3670,17 +3661,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121117887</v>
+        <v>121117063</v>
       </c>
       <c r="B24" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3710,17 +3701,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svedaunsmyren, Jmt</t>
+          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446262</v>
+        <v>446063</v>
       </c>
       <c r="R24" t="n">
-        <v>7026371</v>
+        <v>7026497</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1 stor garnlav</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3797,7 +3797,7 @@
         <v>121117375</v>
       </c>
       <c r="B25" t="n">
-        <v>77535</v>
+        <v>77538</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3904,17 +3904,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121117224</v>
+        <v>121117416</v>
       </c>
       <c r="B26" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3960,10 +3960,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446032</v>
+        <v>445930</v>
       </c>
       <c r="R26" t="n">
-        <v>7026520</v>
+        <v>7026585</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4005,7 +4005,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 20, långa Gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4032,10 +4037,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121117063</v>
+        <v>121117224</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4067,7 +4072,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4077,14 +4082,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
+          <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446063</v>
+        <v>446032</v>
       </c>
       <c r="R27" t="n">
-        <v>7026497</v>
+        <v>7026520</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4116,7 +4121,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4126,12 +4131,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121132931</v>
+        <v>121134550</v>
       </c>
       <c r="B28" t="n">
-        <v>74705</v>
+        <v>90468</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446284</v>
+        <v>445911</v>
       </c>
       <c r="R28" t="n">
-        <v>7026556</v>
+        <v>7026564</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4228,12 +4228,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4247,22 +4257,12 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal barrblandskog, sumpskog/myr</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121134552</v>
+        <v>121134878</v>
       </c>
       <c r="B29" t="n">
-        <v>77535</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4296,34 +4296,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445924</v>
+        <v>446262</v>
       </c>
       <c r="R29" t="n">
-        <v>7026587</v>
+        <v>7026436</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4350,22 +4359,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4379,7 +4388,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4394,7 +4403,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4405,17 +4414,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121132943</v>
+        <v>121134545</v>
       </c>
       <c r="B30" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4428,34 +4437,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446259</v>
+        <v>445987</v>
       </c>
       <c r="R30" t="n">
-        <v>7026469</v>
+        <v>7026510</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4482,12 +4500,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10 bålar, den längsta 30 cm</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4501,7 +4534,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4516,7 +4549,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4527,17 +4560,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121134550</v>
+        <v>121134875</v>
       </c>
       <c r="B31" t="n">
-        <v>90458</v>
+        <v>74708</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4546,25 +4579,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3215</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4574,10 +4607,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445911</v>
+        <v>446269</v>
       </c>
       <c r="R31" t="n">
-        <v>7026564</v>
+        <v>7026478</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4604,22 +4637,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4633,12 +4666,22 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog, sumpskog/myr</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4649,17 +4692,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121134536</v>
+        <v>121134552</v>
       </c>
       <c r="B32" t="n">
-        <v>90683</v>
+        <v>77538</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4672,21 +4715,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4696,10 +4739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446164</v>
+        <v>445924</v>
       </c>
       <c r="R32" t="n">
-        <v>7026463</v>
+        <v>7026587</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4731,7 +4774,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4741,7 +4784,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4755,7 +4798,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4770,7 +4813,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>På död gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4788,10 +4831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121134849</v>
+        <v>121134850</v>
       </c>
       <c r="B33" t="n">
-        <v>91127</v>
+        <v>91630</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4800,25 +4843,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4828,10 +4871,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445948</v>
+        <v>445960</v>
       </c>
       <c r="R33" t="n">
-        <v>7026487</v>
+        <v>7026492</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4863,7 +4906,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4873,7 +4916,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4890,19 +4933,9 @@
           <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>På grov granlåga # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4920,10 +4953,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121134546</v>
+        <v>121134558</v>
       </c>
       <c r="B34" t="n">
-        <v>77535</v>
+        <v>78601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4936,21 +4969,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4960,10 +4993,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445987</v>
+        <v>446050</v>
       </c>
       <c r="R34" t="n">
-        <v>7026512</v>
+        <v>7026501</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4995,7 +5028,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5005,7 +5038,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5019,7 +5052,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gles gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5034,7 +5067,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5052,10 +5085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121134543</v>
+        <v>121134551</v>
       </c>
       <c r="B35" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5064,47 +5097,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446069</v>
+        <v>445899</v>
       </c>
       <c r="R35" t="n">
-        <v>7026527</v>
+        <v>7026589</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5136,7 +5160,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5146,12 +5170,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5165,12 +5184,22 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>I gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5188,10 +5217,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121134556</v>
+        <v>121134877</v>
       </c>
       <c r="B36" t="n">
-        <v>74710</v>
+        <v>77538</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5204,21 +5233,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1467</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5228,10 +5257,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446026</v>
+        <v>446271</v>
       </c>
       <c r="R36" t="n">
-        <v>7026520</v>
+        <v>7026473</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5258,22 +5287,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5287,22 +5316,22 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5313,17 +5342,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121134851</v>
+        <v>121134852</v>
       </c>
       <c r="B37" t="n">
-        <v>90687</v>
+        <v>90711</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5336,21 +5365,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5360,7 +5389,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445959</v>
+        <v>445963</v>
       </c>
       <c r="R37" t="n">
         <v>7026504</v>
@@ -5395,7 +5424,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5405,7 +5434,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5452,10 +5481,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121134535</v>
+        <v>121134540</v>
       </c>
       <c r="B38" t="n">
-        <v>78761</v>
+        <v>74694</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5464,47 +5493,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1249</v>
+        <v>306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446119</v>
+        <v>446088</v>
       </c>
       <c r="R38" t="n">
-        <v>7026442</v>
+        <v>7026528</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5536,7 +5556,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5546,12 +5566,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:41</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Samma som sedd tidigare i år</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5560,6 +5575,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5580,7 +5596,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5598,10 +5614,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121134860</v>
+        <v>121132927</v>
       </c>
       <c r="B39" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5631,26 +5647,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446170</v>
+        <v>446305</v>
       </c>
       <c r="R39" t="n">
-        <v>7026558</v>
+        <v>7026607</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5677,22 +5684,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>60 cm lång bål</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5706,22 +5708,22 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5739,10 +5741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121134553</v>
+        <v>121132928</v>
       </c>
       <c r="B40" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5755,34 +5757,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445925</v>
+        <v>446290</v>
       </c>
       <c r="R40" t="n">
-        <v>7026580</v>
+        <v>7026577</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5809,22 +5820,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20 bålar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5838,7 +5844,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5853,7 +5859,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5864,17 +5870,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121132934</v>
+        <v>121134535</v>
       </c>
       <c r="B41" t="n">
-        <v>78598</v>
+        <v>78764</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5883,38 +5889,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446253</v>
+        <v>446119</v>
       </c>
       <c r="R41" t="n">
-        <v>7026514</v>
+        <v>7026442</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5941,12 +5956,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Samma som sedd tidigare i år</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5960,7 +5990,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5975,7 +6005,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5986,17 +6016,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121134864</v>
+        <v>121132926</v>
       </c>
       <c r="B42" t="n">
-        <v>74705</v>
+        <v>56563</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6005,25 +6035,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6033,10 +6063,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446203</v>
+        <v>446305</v>
       </c>
       <c r="R42" t="n">
-        <v>7026536</v>
+        <v>7026607</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6063,22 +6093,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>uppflog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6092,22 +6117,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6125,10 +6135,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121134868</v>
+        <v>121132932</v>
       </c>
       <c r="B43" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6165,10 +6175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446262</v>
+        <v>446284</v>
       </c>
       <c r="R43" t="n">
-        <v>7026488</v>
+        <v>7026556</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6195,22 +6205,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121134850</v>
+        <v>121134546</v>
       </c>
       <c r="B44" t="n">
-        <v>91620</v>
+        <v>77538</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6269,25 +6269,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445960</v>
+        <v>445987</v>
       </c>
       <c r="R44" t="n">
-        <v>7026492</v>
+        <v>7026512</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6327,22 +6327,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6356,12 +6356,22 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6372,17 +6382,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121134557</v>
+        <v>121134880</v>
       </c>
       <c r="B45" t="n">
-        <v>74696</v>
+        <v>56563</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6391,38 +6401,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>492</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446026</v>
+        <v>446259</v>
       </c>
       <c r="R45" t="n">
-        <v>7026520</v>
+        <v>7026406</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6449,22 +6468,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Satt i gammal gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6478,22 +6502,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6504,17 +6513,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121132926</v>
+        <v>121134538</v>
       </c>
       <c r="B46" t="n">
-        <v>56560</v>
+        <v>105171</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6527,21 +6536,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>221725</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6551,10 +6560,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>446305</v>
+        <v>446142</v>
       </c>
       <c r="R46" t="n">
-        <v>7026607</v>
+        <v>7026514</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6581,17 +6590,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>uppflog</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6605,7 +6619,12 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6616,17 +6635,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121134878</v>
+        <v>121134873</v>
       </c>
       <c r="B47" t="n">
-        <v>78598</v>
+        <v>77538</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6639,43 +6658,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>446262</v>
+        <v>446269</v>
       </c>
       <c r="R47" t="n">
-        <v>7026436</v>
+        <v>7026478</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6707,7 +6717,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6717,7 +6727,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6746,7 +6756,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6764,10 +6774,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121134866</v>
+        <v>121134858</v>
       </c>
       <c r="B48" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6804,10 +6814,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>446218</v>
+        <v>446092</v>
       </c>
       <c r="R48" t="n">
-        <v>7026544</v>
+        <v>7026520</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6839,7 +6849,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6849,7 +6859,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6878,7 +6888,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6896,10 +6906,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121134853</v>
+        <v>121134849</v>
       </c>
       <c r="B49" t="n">
-        <v>74696</v>
+        <v>91137</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6912,21 +6922,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>492</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6936,10 +6946,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445965</v>
+        <v>445948</v>
       </c>
       <c r="R49" t="n">
-        <v>7026512</v>
+        <v>7026487</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6971,7 +6981,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6981,7 +6991,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7010,7 +7020,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På grov granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7028,10 +7038,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121134873</v>
+        <v>121134555</v>
       </c>
       <c r="B50" t="n">
-        <v>77535</v>
+        <v>90662</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7040,25 +7050,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7068,10 +7078,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446269</v>
+        <v>446030</v>
       </c>
       <c r="R50" t="n">
-        <v>7026478</v>
+        <v>7026523</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7098,22 +7108,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7127,7 +7137,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7142,7 +7152,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7153,17 +7163,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121132945</v>
+        <v>121134870</v>
       </c>
       <c r="B51" t="n">
-        <v>90705</v>
+        <v>91137</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7172,25 +7182,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7200,10 +7210,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446220</v>
+        <v>446262</v>
       </c>
       <c r="R51" t="n">
-        <v>7026528</v>
+        <v>7026488</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7230,12 +7240,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7249,7 +7269,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7264,7 +7284,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>på gammal dubbelgran # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7282,10 +7302,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121134880</v>
+        <v>121132931</v>
       </c>
       <c r="B52" t="n">
-        <v>56560</v>
+        <v>74708</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7294,47 +7314,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446259</v>
+        <v>446284</v>
       </c>
       <c r="R52" t="n">
-        <v>7026406</v>
+        <v>7026556</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7361,27 +7372,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Satt i gammal gran</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7395,7 +7391,22 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7413,10 +7424,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121134862</v>
+        <v>121134860</v>
       </c>
       <c r="B53" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7429,34 +7440,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446197</v>
+        <v>446170</v>
       </c>
       <c r="R53" t="n">
-        <v>7026538</v>
+        <v>7026558</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7488,7 +7508,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7498,7 +7518,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7527,7 +7547,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7545,10 +7565,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121134551</v>
+        <v>121134865</v>
       </c>
       <c r="B54" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7578,17 +7598,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445899</v>
+        <v>446213</v>
       </c>
       <c r="R54" t="n">
-        <v>7026589</v>
+        <v>7026555</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7615,22 +7644,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7644,7 +7673,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7659,7 +7688,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7670,17 +7699,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121134857</v>
+        <v>121134542</v>
       </c>
       <c r="B55" t="n">
-        <v>78598</v>
+        <v>95628</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7693,21 +7722,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7717,10 +7746,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446075</v>
+        <v>446080</v>
       </c>
       <c r="R55" t="n">
-        <v>7026515</v>
+        <v>7026521</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7747,22 +7776,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7776,7 +7805,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -7791,7 +7820,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På mycket gammal granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7802,17 +7831,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121134865</v>
+        <v>121134869</v>
       </c>
       <c r="B56" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7825,43 +7854,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446213</v>
+        <v>446262</v>
       </c>
       <c r="R56" t="n">
-        <v>7026555</v>
+        <v>7026488</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7893,7 +7913,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7903,7 +7923,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7917,7 +7937,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -7932,7 +7952,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7950,10 +7970,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121134548</v>
+        <v>121134853</v>
       </c>
       <c r="B57" t="n">
-        <v>88018</v>
+        <v>74699</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7962,25 +7982,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7990,10 +8010,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445938</v>
+        <v>445965</v>
       </c>
       <c r="R57" t="n">
-        <v>7026514</v>
+        <v>7026512</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8020,22 +8040,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8049,7 +8069,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -8064,7 +8084,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8075,17 +8095,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121134541</v>
+        <v>121132936</v>
       </c>
       <c r="B58" t="n">
-        <v>74697</v>
+        <v>77538</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8098,21 +8118,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>308</v>
+        <v>228579</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8122,10 +8142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446088</v>
+        <v>446254</v>
       </c>
       <c r="R58" t="n">
-        <v>7026528</v>
+        <v>7026486</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8152,22 +8172,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8181,7 +8191,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -8196,7 +8206,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8207,17 +8217,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121134870</v>
+        <v>121132949</v>
       </c>
       <c r="B59" t="n">
-        <v>91127</v>
+        <v>78601</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8226,38 +8236,47 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446262</v>
+        <v>446118</v>
       </c>
       <c r="R59" t="n">
-        <v>7026488</v>
+        <v>7026441</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8284,22 +8303,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>7 bålar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8313,7 +8327,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -8328,7 +8342,7 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8346,10 +8360,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121134863</v>
+        <v>121134867</v>
       </c>
       <c r="B60" t="n">
-        <v>78598</v>
+        <v>77538</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8362,21 +8376,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8386,10 +8400,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446203</v>
+        <v>446244</v>
       </c>
       <c r="R60" t="n">
-        <v>7026536</v>
+        <v>7026516</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8421,7 +8435,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8431,7 +8445,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8460,7 +8474,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8478,10 +8492,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121134859</v>
+        <v>121134536</v>
       </c>
       <c r="B61" t="n">
-        <v>74705</v>
+        <v>90693</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8494,21 +8508,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8518,10 +8532,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>446158</v>
+        <v>446164</v>
       </c>
       <c r="R61" t="n">
-        <v>7026570</v>
+        <v>7026463</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8548,22 +8562,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8577,7 +8591,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8592,7 +8606,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8603,17 +8617,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121132927</v>
+        <v>121132945</v>
       </c>
       <c r="B62" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8626,21 +8640,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8650,10 +8664,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>446305</v>
+        <v>446220</v>
       </c>
       <c r="R62" t="n">
-        <v>7026607</v>
+        <v>7026528</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8688,11 +8702,6 @@
           <t>2024-03-03</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>60 cm lång bål</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8704,22 +8713,22 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
+          <t>på gammal dubbelgran # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8737,10 +8746,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121134537</v>
+        <v>121134556</v>
       </c>
       <c r="B63" t="n">
-        <v>74689</v>
+        <v>74713</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8749,25 +8758,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6439</v>
+        <v>1467</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8777,10 +8786,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>446153</v>
+        <v>446026</v>
       </c>
       <c r="R63" t="n">
-        <v>7026500</v>
+        <v>7026520</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8812,7 +8821,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8822,7 +8831,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8851,7 +8860,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>På björkhögstubbe # Betula pubescens</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8869,10 +8878,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121132949</v>
+        <v>121134857</v>
       </c>
       <c r="B64" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8902,26 +8911,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>446118</v>
+        <v>446075</v>
       </c>
       <c r="R64" t="n">
-        <v>7026441</v>
+        <v>7026515</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8948,17 +8948,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>7 bålar</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8972,7 +8977,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -8987,7 +8992,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9005,10 +9010,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121132944</v>
+        <v>121132934</v>
       </c>
       <c r="B65" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9045,10 +9050,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>446279</v>
+        <v>446253</v>
       </c>
       <c r="R65" t="n">
-        <v>7026455</v>
+        <v>7026514</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9083,11 +9088,6 @@
           <t>2024-03-03</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>40 cm lång bål</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -9104,17 +9104,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
+          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9132,10 +9132,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121134549</v>
+        <v>121132950</v>
       </c>
       <c r="B66" t="n">
-        <v>74705</v>
+        <v>78764</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9144,38 +9144,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445936</v>
+        <v>446118</v>
       </c>
       <c r="R66" t="n">
-        <v>7026522</v>
+        <v>7026441</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9202,22 +9211,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>1 bål</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9231,7 +9235,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9246,7 +9250,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9257,17 +9261,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121134867</v>
+        <v>121134548</v>
       </c>
       <c r="B67" t="n">
-        <v>77535</v>
+        <v>88024</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9280,21 +9284,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228579</v>
+        <v>510</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9304,10 +9308,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>446244</v>
+        <v>445938</v>
       </c>
       <c r="R67" t="n">
-        <v>7026516</v>
+        <v>7026514</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9334,22 +9338,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9363,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -9378,7 +9382,7 @@
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9389,17 +9393,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121134540</v>
+        <v>121134541</v>
       </c>
       <c r="B68" t="n">
-        <v>74691</v>
+        <v>74700</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9408,25 +9412,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9471,7 +9475,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9481,7 +9485,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9490,7 +9494,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9529,10 +9532,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121132928</v>
+        <v>121134557</v>
       </c>
       <c r="B69" t="n">
-        <v>78598</v>
+        <v>74699</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9541,47 +9544,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>446290</v>
+        <v>446026</v>
       </c>
       <c r="R69" t="n">
-        <v>7026577</v>
+        <v>7026520</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9608,17 +9602,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>20 bålar</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9632,22 +9631,22 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>i gammal gles barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9658,17 +9657,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121134538</v>
+        <v>121134871</v>
       </c>
       <c r="B70" t="n">
-        <v>105161</v>
+        <v>74520</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9681,21 +9680,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221725</v>
+        <v>6428</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9705,10 +9704,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>446142</v>
+        <v>446269</v>
       </c>
       <c r="R70" t="n">
-        <v>7026514</v>
+        <v>7026478</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9735,22 +9734,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9764,12 +9763,22 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9780,17 +9789,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121132930</v>
+        <v>121134553</v>
       </c>
       <c r="B71" t="n">
-        <v>77535</v>
+        <v>74708</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9803,21 +9812,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9827,10 +9836,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>446284</v>
+        <v>445925</v>
       </c>
       <c r="R71" t="n">
-        <v>7026556</v>
+        <v>7026580</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9857,12 +9866,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9876,7 +9895,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9891,7 +9910,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9902,17 +9921,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121134855</v>
+        <v>121134862</v>
       </c>
       <c r="B72" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9925,21 +9944,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9949,10 +9968,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>446045</v>
+        <v>446197</v>
       </c>
       <c r="R72" t="n">
-        <v>7026526</v>
+        <v>7026538</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9984,7 +10003,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9994,7 +10013,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10023,7 +10042,7 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10041,10 +10060,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121134869</v>
+        <v>121134549</v>
       </c>
       <c r="B73" t="n">
-        <v>90687</v>
+        <v>74708</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10057,21 +10076,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10081,10 +10100,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>446262</v>
+        <v>445936</v>
       </c>
       <c r="R73" t="n">
-        <v>7026488</v>
+        <v>7026522</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10111,22 +10130,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10140,7 +10159,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10155,7 +10174,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10166,17 +10185,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121134544</v>
+        <v>121134859</v>
       </c>
       <c r="B74" t="n">
-        <v>90687</v>
+        <v>74708</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10189,21 +10208,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10213,10 +10232,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>446005</v>
+        <v>446158</v>
       </c>
       <c r="R74" t="n">
-        <v>7026502</v>
+        <v>7026570</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10243,22 +10262,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10272,7 +10291,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -10287,7 +10306,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10298,17 +10317,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121132950</v>
+        <v>121132943</v>
       </c>
       <c r="B75" t="n">
-        <v>78761</v>
+        <v>74708</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10317,47 +10336,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>446118</v>
+        <v>446259</v>
       </c>
       <c r="R75" t="n">
-        <v>7026441</v>
+        <v>7026469</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10392,11 +10402,6 @@
           <t>2024-03-03</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>1 bål</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -10408,7 +10413,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -10423,7 +10428,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10441,10 +10446,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121134871</v>
+        <v>121134537</v>
       </c>
       <c r="B76" t="n">
-        <v>74517</v>
+        <v>74692</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10457,21 +10462,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6428</v>
+        <v>6439</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10481,10 +10486,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>446269</v>
+        <v>446153</v>
       </c>
       <c r="R76" t="n">
-        <v>7026478</v>
+        <v>7026500</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10511,22 +10516,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10540,22 +10545,22 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På björkhögstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10566,17 +10571,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121134858</v>
+        <v>121134868</v>
       </c>
       <c r="B77" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10589,21 +10594,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10613,10 +10618,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>446092</v>
+        <v>446262</v>
       </c>
       <c r="R77" t="n">
-        <v>7026520</v>
+        <v>7026488</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10648,7 +10653,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10658,7 +10663,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10672,7 +10677,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -10687,7 +10692,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10705,10 +10710,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121134542</v>
+        <v>121134539</v>
       </c>
       <c r="B78" t="n">
-        <v>95618</v>
+        <v>74713</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10721,21 +10726,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>1467</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10745,10 +10750,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>446080</v>
+        <v>446088</v>
       </c>
       <c r="R78" t="n">
-        <v>7026521</v>
+        <v>7026528</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10780,7 +10785,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10790,7 +10795,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10804,7 +10809,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -10819,7 +10824,7 @@
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>På mycket gammal granlåga # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10837,10 +10842,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121132935</v>
+        <v>121134866</v>
       </c>
       <c r="B79" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10853,21 +10858,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10877,10 +10882,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>446246</v>
+        <v>446218</v>
       </c>
       <c r="R79" t="n">
-        <v>7026518</v>
+        <v>7026544</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10907,12 +10912,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10926,7 +10941,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -10941,7 +10956,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10959,10 +10974,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121134877</v>
+        <v>121134863</v>
       </c>
       <c r="B80" t="n">
-        <v>77535</v>
+        <v>78601</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10975,21 +10990,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10999,10 +11014,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>446271</v>
+        <v>446203</v>
       </c>
       <c r="R80" t="n">
-        <v>7026473</v>
+        <v>7026536</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11034,7 +11049,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11044,7 +11059,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11058,7 +11073,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
@@ -11073,7 +11088,7 @@
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11091,10 +11106,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121134861</v>
+        <v>121134864</v>
       </c>
       <c r="B81" t="n">
-        <v>77535</v>
+        <v>74708</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11107,21 +11122,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11131,10 +11146,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>446197</v>
+        <v>446203</v>
       </c>
       <c r="R81" t="n">
-        <v>7026538</v>
+        <v>7026536</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11166,7 +11181,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11176,7 +11191,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11205,7 +11220,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11223,10 +11238,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121134539</v>
+        <v>121132930</v>
       </c>
       <c r="B82" t="n">
-        <v>74710</v>
+        <v>77538</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11239,21 +11254,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1467</v>
+        <v>228579</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11263,10 +11278,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>446088</v>
+        <v>446284</v>
       </c>
       <c r="R82" t="n">
-        <v>7026528</v>
+        <v>7026556</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11293,22 +11308,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11322,7 +11327,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -11337,7 +11342,7 @@
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11348,17 +11353,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121132936</v>
+        <v>121134861</v>
       </c>
       <c r="B83" t="n">
-        <v>77535</v>
+        <v>77538</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11395,10 +11400,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>446254</v>
+        <v>446197</v>
       </c>
       <c r="R83" t="n">
-        <v>7026486</v>
+        <v>7026538</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11425,12 +11430,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11444,7 +11459,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -11459,7 +11474,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11477,10 +11492,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121134852</v>
+        <v>121134544</v>
       </c>
       <c r="B84" t="n">
-        <v>90701</v>
+        <v>90697</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11493,21 +11508,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11517,10 +11532,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445963</v>
+        <v>446005</v>
       </c>
       <c r="R84" t="n">
-        <v>7026504</v>
+        <v>7026502</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11547,22 +11562,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11576,7 +11591,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11602,17 +11617,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121132932</v>
+        <v>121132944</v>
       </c>
       <c r="B85" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11649,10 +11664,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>446284</v>
+        <v>446279</v>
       </c>
       <c r="R85" t="n">
-        <v>7026556</v>
+        <v>7026455</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11687,6 +11702,11 @@
           <t>2024-03-03</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>40 cm lång bål</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -11703,17 +11723,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11731,10 +11751,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121134558</v>
+        <v>121134855</v>
       </c>
       <c r="B86" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11771,10 +11791,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>446050</v>
+        <v>446045</v>
       </c>
       <c r="R86" t="n">
-        <v>7026501</v>
+        <v>7026526</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11801,22 +11821,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11830,7 +11850,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>I gles gammal gransumpskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -11845,7 +11865,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11856,17 +11876,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121134555</v>
+        <v>121134851</v>
       </c>
       <c r="B87" t="n">
-        <v>90652</v>
+        <v>90697</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11875,25 +11895,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11903,10 +11923,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>446030</v>
+        <v>445959</v>
       </c>
       <c r="R87" t="n">
-        <v>7026523</v>
+        <v>7026504</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11933,22 +11953,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11962,7 +11982,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -11977,7 +11997,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11988,17 +12008,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121134875</v>
+        <v>121134543</v>
       </c>
       <c r="B88" t="n">
-        <v>74705</v>
+        <v>98081</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12007,38 +12027,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>446269</v>
+        <v>446069</v>
       </c>
       <c r="R88" t="n">
-        <v>7026478</v>
+        <v>7026527</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12065,22 +12094,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12094,22 +12128,12 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12120,17 +12144,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121134545</v>
+        <v>121132948</v>
       </c>
       <c r="B89" t="n">
-        <v>78598</v>
+        <v>77538</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12143,43 +12167,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445987</v>
+        <v>446111</v>
       </c>
       <c r="R89" t="n">
-        <v>7026510</v>
+        <v>7026483</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12206,27 +12221,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>10 bålar, den längsta 30 cm</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12266,17 +12266,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121132948</v>
+        <v>121132935</v>
       </c>
       <c r="B90" t="n">
-        <v>77535</v>
+        <v>78601</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12289,21 +12289,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12313,10 +12313,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>446111</v>
+        <v>446246</v>
       </c>
       <c r="R90" t="n">
-        <v>7026483</v>
+        <v>7026518</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12395,10 +12395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252821</v>
+        <v>121252824</v>
       </c>
       <c r="B91" t="n">
-        <v>78598</v>
+        <v>77538</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12411,21 +12411,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>446282</v>
+        <v>446278</v>
       </c>
       <c r="R91" t="n">
-        <v>7026592</v>
+        <v>7026536</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12527,10 +12527,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252825</v>
+        <v>121252826</v>
       </c>
       <c r="B92" t="n">
-        <v>78854</v>
+        <v>78601</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12539,25 +12539,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>446278</v>
+        <v>446279</v>
       </c>
       <c r="R92" t="n">
-        <v>7026536</v>
+        <v>7026520</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12659,10 +12659,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252824</v>
+        <v>121252822</v>
       </c>
       <c r="B93" t="n">
-        <v>77535</v>
+        <v>78601</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12675,21 +12675,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>446278</v>
+        <v>446284</v>
       </c>
       <c r="R93" t="n">
-        <v>7026536</v>
+        <v>7026552</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12791,10 +12791,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121252812</v>
+        <v>121252821</v>
       </c>
       <c r="B94" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12831,10 +12831,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>446185</v>
+        <v>446282</v>
       </c>
       <c r="R94" t="n">
-        <v>7026655</v>
+        <v>7026592</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12923,10 +12923,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252827</v>
+        <v>121252815</v>
       </c>
       <c r="B95" t="n">
-        <v>78598</v>
+        <v>57504</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12939,34 +12939,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>446252</v>
+        <v>446189</v>
       </c>
       <c r="R95" t="n">
-        <v>7026536</v>
+        <v>7026651</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12998,7 +13007,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13008,7 +13017,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13022,22 +13031,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13055,10 +13049,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252833</v>
+        <v>121252820</v>
       </c>
       <c r="B96" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13071,43 +13065,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446233</v>
+        <v>446258</v>
       </c>
       <c r="R96" t="n">
-        <v>7026512</v>
+        <v>7026597</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13139,7 +13124,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13149,12 +13134,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13168,7 +13148,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -13183,7 +13163,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13201,10 +13181,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252810</v>
+        <v>121252837</v>
       </c>
       <c r="B97" t="n">
-        <v>74691</v>
+        <v>77538</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13213,25 +13193,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>306</v>
+        <v>228579</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -13241,10 +13221,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446089</v>
+        <v>446201</v>
       </c>
       <c r="R97" t="n">
-        <v>7026536</v>
+        <v>7026410</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13276,7 +13256,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13286,7 +13266,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13295,7 +13275,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -13316,7 +13295,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13334,10 +13313,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252830</v>
+        <v>121252827</v>
       </c>
       <c r="B98" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13350,21 +13329,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13409,7 +13388,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13419,7 +13398,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13448,7 +13427,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13466,10 +13445,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121252835</v>
+        <v>121252818</v>
       </c>
       <c r="B99" t="n">
-        <v>77982</v>
+        <v>74520</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13478,25 +13457,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6437</v>
+        <v>6428</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -13509,7 +13488,7 @@
         <v>446209</v>
       </c>
       <c r="R99" t="n">
-        <v>7026444</v>
+        <v>7026630</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13541,7 +13520,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13551,7 +13530,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13565,22 +13544,22 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>I gammal sumpskog/myr</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13598,10 +13577,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121252815</v>
+        <v>121252838</v>
       </c>
       <c r="B100" t="n">
-        <v>57501</v>
+        <v>74708</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13614,43 +13593,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>446189</v>
+        <v>446201</v>
       </c>
       <c r="R100" t="n">
-        <v>7026651</v>
+        <v>7026410</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13682,7 +13652,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13692,7 +13662,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13706,7 +13676,22 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13724,10 +13709,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252807</v>
+        <v>121252803</v>
       </c>
       <c r="B101" t="n">
-        <v>78598</v>
+        <v>105171</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13736,25 +13721,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -13764,10 +13749,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>446038</v>
+        <v>446013</v>
       </c>
       <c r="R101" t="n">
-        <v>7026546</v>
+        <v>7026516</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13799,7 +13784,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13809,7 +13794,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13823,22 +13808,12 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13856,10 +13831,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121252839</v>
+        <v>121252807</v>
       </c>
       <c r="B102" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13872,21 +13847,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13896,10 +13871,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>446209</v>
+        <v>446038</v>
       </c>
       <c r="R102" t="n">
-        <v>7026395</v>
+        <v>7026546</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13931,7 +13906,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13941,7 +13916,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13955,7 +13930,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13970,7 +13945,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13988,10 +13963,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252800</v>
+        <v>121252840</v>
       </c>
       <c r="B103" t="n">
-        <v>57348</v>
+        <v>77538</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -14004,39 +13979,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>446056</v>
+        <v>446209</v>
       </c>
       <c r="R103" t="n">
-        <v>7026521</v>
+        <v>7026394</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -14068,7 +14038,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14078,12 +14048,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14097,12 +14062,22 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid dike</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14120,10 +14095,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121252803</v>
+        <v>121252806</v>
       </c>
       <c r="B104" t="n">
-        <v>105161</v>
+        <v>74520</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14136,21 +14111,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221725</v>
+        <v>6428</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -14160,10 +14135,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>446013</v>
+        <v>446038</v>
       </c>
       <c r="R104" t="n">
-        <v>7026516</v>
+        <v>7026546</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14195,7 +14170,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14205,7 +14180,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14219,12 +14194,22 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14242,10 +14227,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252817</v>
+        <v>121252814</v>
       </c>
       <c r="B105" t="n">
-        <v>74689</v>
+        <v>78601</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14254,25 +14239,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -14282,10 +14267,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>446209</v>
+        <v>446185</v>
       </c>
       <c r="R105" t="n">
-        <v>7026630</v>
+        <v>7026627</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14317,7 +14302,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14327,7 +14312,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14356,7 +14341,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14374,10 +14359,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121252809</v>
+        <v>121252801</v>
       </c>
       <c r="B106" t="n">
-        <v>77535</v>
+        <v>91380</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14386,25 +14371,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -14414,10 +14399,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>446044</v>
+        <v>445969</v>
       </c>
       <c r="R106" t="n">
-        <v>7026549</v>
+        <v>7026495</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14449,7 +14434,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14459,7 +14444,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14473,7 +14458,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -14488,7 +14473,7 @@
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14506,10 +14491,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121252826</v>
+        <v>121252823</v>
       </c>
       <c r="B107" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14546,10 +14531,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>446279</v>
+        <v>446274</v>
       </c>
       <c r="R107" t="n">
-        <v>7026520</v>
+        <v>7026540</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14581,7 +14566,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14591,7 +14576,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14620,7 +14605,7 @@
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14638,10 +14623,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252804</v>
+        <v>121252819</v>
       </c>
       <c r="B108" t="n">
-        <v>97084</v>
+        <v>77538</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14650,25 +14635,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221063</v>
+        <v>228579</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14678,10 +14663,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>446013</v>
+        <v>446258</v>
       </c>
       <c r="R108" t="n">
-        <v>7026514</v>
+        <v>7026597</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14713,7 +14698,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14723,7 +14708,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14740,9 +14725,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14760,10 +14755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252801</v>
+        <v>121252800</v>
       </c>
       <c r="B109" t="n">
-        <v>91370</v>
+        <v>57351</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14772,38 +14767,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445969</v>
+        <v>446056</v>
       </c>
       <c r="R109" t="n">
-        <v>7026495</v>
+        <v>7026521</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14845,7 +14845,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14862,19 +14867,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14892,10 +14887,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252837</v>
+        <v>121252808</v>
       </c>
       <c r="B110" t="n">
-        <v>77535</v>
+        <v>78635</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14908,34 +14903,43 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228579</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>446201</v>
+        <v>446038</v>
       </c>
       <c r="R110" t="n">
-        <v>7026410</v>
+        <v>7026546</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14967,7 +14971,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14977,7 +14981,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14991,7 +14995,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -15006,7 +15010,7 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15024,10 +15028,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252823</v>
+        <v>121252811</v>
       </c>
       <c r="B111" t="n">
-        <v>78598</v>
+        <v>90693</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15040,21 +15044,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -15064,10 +15068,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446274</v>
+        <v>446106</v>
       </c>
       <c r="R111" t="n">
-        <v>7026540</v>
+        <v>7026528</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15099,7 +15103,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15109,7 +15113,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15123,7 +15127,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>i gammal granskog</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -15138,7 +15142,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15156,10 +15160,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121252836</v>
+        <v>121252835</v>
       </c>
       <c r="B112" t="n">
-        <v>78598</v>
+        <v>77985</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15172,21 +15176,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -15196,10 +15200,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>446201</v>
+        <v>446209</v>
       </c>
       <c r="R112" t="n">
-        <v>7026410</v>
+        <v>7026444</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15231,7 +15235,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -15241,7 +15245,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15255,22 +15259,22 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal sumpskog/myr</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15288,10 +15292,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121252840</v>
+        <v>121252812</v>
       </c>
       <c r="B113" t="n">
-        <v>77535</v>
+        <v>78601</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15304,21 +15308,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -15328,10 +15332,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>446209</v>
+        <v>446185</v>
       </c>
       <c r="R113" t="n">
-        <v>7026394</v>
+        <v>7026655</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15363,7 +15367,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -15373,7 +15377,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15387,7 +15391,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -15402,7 +15406,7 @@
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15420,10 +15424,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121252808</v>
+        <v>121252825</v>
       </c>
       <c r="B114" t="n">
-        <v>78632</v>
+        <v>78857</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -15432,47 +15436,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6459</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>446038</v>
+        <v>446278</v>
       </c>
       <c r="R114" t="n">
-        <v>7026546</v>
+        <v>7026536</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15504,7 +15499,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -15514,7 +15509,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15528,7 +15523,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -15543,7 +15538,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15561,10 +15556,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252820</v>
+        <v>121252817</v>
       </c>
       <c r="B115" t="n">
-        <v>74705</v>
+        <v>74692</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15573,25 +15568,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15601,10 +15596,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446258</v>
+        <v>446209</v>
       </c>
       <c r="R115" t="n">
-        <v>7026597</v>
+        <v>7026630</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15636,7 +15631,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15646,7 +15641,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15660,7 +15655,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -15675,7 +15670,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15693,10 +15688,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252838</v>
+        <v>121252804</v>
       </c>
       <c r="B116" t="n">
-        <v>74705</v>
+        <v>97094</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15705,25 +15700,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6440</v>
+        <v>221063</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15733,10 +15728,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446201</v>
+        <v>446013</v>
       </c>
       <c r="R116" t="n">
-        <v>7026410</v>
+        <v>7026514</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15768,7 +15763,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15778,7 +15773,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15795,19 +15790,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15825,10 +15810,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252818</v>
+        <v>121252810</v>
       </c>
       <c r="B117" t="n">
-        <v>74517</v>
+        <v>74694</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15841,21 +15826,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6428</v>
+        <v>306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15865,10 +15850,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446209</v>
+        <v>446089</v>
       </c>
       <c r="R117" t="n">
-        <v>7026630</v>
+        <v>7026536</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15900,7 +15885,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15910,7 +15895,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15919,12 +15904,13 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -15939,7 +15925,7 @@
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15957,10 +15943,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252814</v>
+        <v>121252802</v>
       </c>
       <c r="B118" t="n">
-        <v>78598</v>
+        <v>90693</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15973,21 +15959,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15997,10 +15983,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446185</v>
+        <v>445982</v>
       </c>
       <c r="R118" t="n">
-        <v>7026627</v>
+        <v>7026514</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16032,7 +16018,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16042,7 +16028,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16056,7 +16042,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -16071,7 +16057,7 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16089,10 +16075,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252813</v>
+        <v>121252830</v>
       </c>
       <c r="B119" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16105,21 +16091,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -16129,10 +16115,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446166</v>
+        <v>446252</v>
       </c>
       <c r="R119" t="n">
-        <v>7026698</v>
+        <v>7026536</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16164,7 +16150,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16174,7 +16160,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16188,7 +16174,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -16203,7 +16189,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16221,10 +16207,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121252822</v>
+        <v>121252833</v>
       </c>
       <c r="B120" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16254,17 +16240,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446284</v>
+        <v>446233</v>
       </c>
       <c r="R120" t="n">
-        <v>7026552</v>
+        <v>7026512</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16296,7 +16291,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -16306,7 +16301,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16353,10 +16353,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121252802</v>
+        <v>121252839</v>
       </c>
       <c r="B121" t="n">
-        <v>90683</v>
+        <v>90715</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -16369,21 +16369,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -16393,10 +16393,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445982</v>
+        <v>446209</v>
       </c>
       <c r="R121" t="n">
-        <v>7026514</v>
+        <v>7026395</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16452,7 +16452,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16485,10 +16485,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252811</v>
+        <v>121252836</v>
       </c>
       <c r="B122" t="n">
-        <v>90683</v>
+        <v>78601</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -16501,21 +16501,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -16525,10 +16525,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446106</v>
+        <v>446201</v>
       </c>
       <c r="R122" t="n">
-        <v>7026528</v>
+        <v>7026410</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16617,10 +16617,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252806</v>
+        <v>121252813</v>
       </c>
       <c r="B123" t="n">
-        <v>74517</v>
+        <v>78601</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16629,25 +16629,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16657,10 +16657,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446038</v>
+        <v>446166</v>
       </c>
       <c r="R123" t="n">
-        <v>7026546</v>
+        <v>7026698</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -16749,10 +16749,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252819</v>
+        <v>121252809</v>
       </c>
       <c r="B124" t="n">
-        <v>77535</v>
+        <v>77538</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16789,10 +16789,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>446258</v>
+        <v>446044</v>
       </c>
       <c r="R124" t="n">
-        <v>7026597</v>
+        <v>7026549</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121134550</v>
+        <v>121134850</v>
       </c>
       <c r="B28" t="n">
-        <v>90468</v>
+        <v>91630</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445911</v>
+        <v>445960</v>
       </c>
       <c r="R28" t="n">
-        <v>7026564</v>
+        <v>7026492</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4228,22 +4228,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog, sumpskog/myr</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121134545</v>
+        <v>121134552</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4437,43 +4437,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445987</v>
+        <v>445924</v>
       </c>
       <c r="R30" t="n">
-        <v>7026510</v>
+        <v>7026587</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4505,7 +4496,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4515,12 +4506,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10 bålar, den längsta 30 cm</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4534,7 +4520,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4549,7 +4535,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4567,10 +4553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121134875</v>
+        <v>121134550</v>
       </c>
       <c r="B31" t="n">
-        <v>74708</v>
+        <v>90468</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4579,25 +4565,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>3215</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4607,10 +4593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446269</v>
+        <v>445911</v>
       </c>
       <c r="R31" t="n">
-        <v>7026478</v>
+        <v>7026564</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4637,22 +4623,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4666,22 +4652,12 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal barrblandskog, sumpskog/myr</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4692,17 +4668,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121134552</v>
+        <v>121134545</v>
       </c>
       <c r="B32" t="n">
-        <v>77538</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4715,34 +4691,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445924</v>
+        <v>445987</v>
       </c>
       <c r="R32" t="n">
-        <v>7026587</v>
+        <v>7026510</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4774,7 +4759,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4784,7 +4769,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>10 bålar, den längsta 30 cm</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4798,7 +4788,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4813,7 +4803,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4831,10 +4821,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121134850</v>
+        <v>121134875</v>
       </c>
       <c r="B33" t="n">
-        <v>91630</v>
+        <v>74708</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4843,25 +4833,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4871,10 +4861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445960</v>
+        <v>446269</v>
       </c>
       <c r="R33" t="n">
-        <v>7026492</v>
+        <v>7026478</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4906,7 +4896,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4916,7 +4906,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4930,12 +4920,22 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121132932</v>
+        <v>121134546</v>
       </c>
       <c r="B43" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6151,21 +6151,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446284</v>
+        <v>445987</v>
       </c>
       <c r="R43" t="n">
-        <v>7026556</v>
+        <v>7026512</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6205,12 +6205,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6224,7 +6234,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6239,7 +6249,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6250,17 +6260,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121134546</v>
+        <v>121132932</v>
       </c>
       <c r="B44" t="n">
-        <v>77538</v>
+        <v>78601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6273,21 +6283,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6297,10 +6307,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445987</v>
+        <v>446284</v>
       </c>
       <c r="R44" t="n">
-        <v>7026512</v>
+        <v>7026556</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6327,22 +6337,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6774,10 +6774,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121134858</v>
+        <v>121134849</v>
       </c>
       <c r="B48" t="n">
-        <v>90715</v>
+        <v>91137</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6786,25 +6786,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>446092</v>
+        <v>445948</v>
       </c>
       <c r="R48" t="n">
-        <v>7026520</v>
+        <v>7026487</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På grov granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121134849</v>
+        <v>121134555</v>
       </c>
       <c r="B49" t="n">
-        <v>91137</v>
+        <v>90662</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6918,25 +6918,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445948</v>
+        <v>446030</v>
       </c>
       <c r="R49" t="n">
-        <v>7026487</v>
+        <v>7026523</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6976,22 +6976,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>På grov granlåga # Picea abies</t>
+          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7031,17 +7031,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121134555</v>
+        <v>121134858</v>
       </c>
       <c r="B50" t="n">
-        <v>90662</v>
+        <v>90715</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7050,25 +7050,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446030</v>
+        <v>446092</v>
       </c>
       <c r="R50" t="n">
-        <v>7026523</v>
+        <v>7026520</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7108,22 +7108,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121132949</v>
+        <v>121134867</v>
       </c>
       <c r="B59" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8240,43 +8240,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446118</v>
+        <v>446244</v>
       </c>
       <c r="R59" t="n">
-        <v>7026441</v>
+        <v>7026516</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8303,17 +8294,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>7 bålar</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8327,7 +8323,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -8342,7 +8338,7 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8360,10 +8356,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121134867</v>
+        <v>121132949</v>
       </c>
       <c r="B60" t="n">
-        <v>77538</v>
+        <v>78601</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8376,34 +8372,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446244</v>
+        <v>446118</v>
       </c>
       <c r="R60" t="n">
-        <v>7026516</v>
+        <v>7026441</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8430,22 +8435,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>7 bålar</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -9664,10 +9664,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121134871</v>
+        <v>121134549</v>
       </c>
       <c r="B70" t="n">
-        <v>74520</v>
+        <v>74708</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9676,25 +9676,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6428</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9704,10 +9704,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>446269</v>
+        <v>445936</v>
       </c>
       <c r="R70" t="n">
-        <v>7026478</v>
+        <v>7026522</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9734,22 +9734,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9789,14 +9789,14 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121134553</v>
+        <v>121134859</v>
       </c>
       <c r="B71" t="n">
         <v>74708</v>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445925</v>
+        <v>446158</v>
       </c>
       <c r="R71" t="n">
-        <v>7026580</v>
+        <v>7026570</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9866,22 +9866,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9921,17 +9921,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121134862</v>
+        <v>121134871</v>
       </c>
       <c r="B72" t="n">
-        <v>74708</v>
+        <v>74520</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9940,25 +9940,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>446197</v>
+        <v>446269</v>
       </c>
       <c r="R72" t="n">
-        <v>7026538</v>
+        <v>7026478</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10060,7 +10060,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121134549</v>
+        <v>121134553</v>
       </c>
       <c r="B73" t="n">
         <v>74708</v>
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445936</v>
+        <v>445925</v>
       </c>
       <c r="R73" t="n">
-        <v>7026522</v>
+        <v>7026580</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10192,7 +10192,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121134859</v>
+        <v>121132943</v>
       </c>
       <c r="B74" t="n">
         <v>74708</v>
@@ -10232,10 +10232,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>446158</v>
+        <v>446259</v>
       </c>
       <c r="R74" t="n">
-        <v>7026570</v>
+        <v>7026469</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10262,22 +10262,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>16:07</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>16:07</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10291,7 +10281,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -10306,7 +10296,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10324,7 +10314,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121132943</v>
+        <v>121134862</v>
       </c>
       <c r="B75" t="n">
         <v>74708</v>
@@ -10364,10 +10354,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>446259</v>
+        <v>446197</v>
       </c>
       <c r="R75" t="n">
-        <v>7026469</v>
+        <v>7026538</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10394,12 +10384,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -11883,10 +11883,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121134851</v>
+        <v>121134543</v>
       </c>
       <c r="B87" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11895,38 +11895,47 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445959</v>
+        <v>446069</v>
       </c>
       <c r="R87" t="n">
-        <v>7026504</v>
+        <v>7026527</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11953,22 +11962,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11982,22 +11996,12 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12008,17 +12012,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121134543</v>
+        <v>121132948</v>
       </c>
       <c r="B88" t="n">
-        <v>98081</v>
+        <v>77538</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12027,47 +12031,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>446069</v>
+        <v>446111</v>
       </c>
       <c r="R88" t="n">
-        <v>7026527</v>
+        <v>7026483</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12094,27 +12089,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12128,12 +12108,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12144,17 +12134,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121132948</v>
+        <v>121134851</v>
       </c>
       <c r="B89" t="n">
-        <v>77538</v>
+        <v>90697</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12167,21 +12157,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12191,10 +12181,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>446111</v>
+        <v>445959</v>
       </c>
       <c r="R89" t="n">
-        <v>7026483</v>
+        <v>7026504</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12221,12 +12211,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -15556,10 +15556,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252817</v>
+        <v>121252810</v>
       </c>
       <c r="B115" t="n">
-        <v>74692</v>
+        <v>74694</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15572,21 +15572,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6439</v>
+        <v>306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15596,10 +15596,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446209</v>
+        <v>446089</v>
       </c>
       <c r="R115" t="n">
-        <v>7026630</v>
+        <v>7026536</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15650,12 +15650,13 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -15670,7 +15671,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15688,10 +15689,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252804</v>
+        <v>121252817</v>
       </c>
       <c r="B116" t="n">
-        <v>97094</v>
+        <v>74692</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15704,21 +15705,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221063</v>
+        <v>6439</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15728,10 +15729,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446013</v>
+        <v>446209</v>
       </c>
       <c r="R116" t="n">
-        <v>7026514</v>
+        <v>7026630</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15763,7 +15764,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15773,7 +15774,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15787,12 +15788,22 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15810,10 +15821,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252810</v>
+        <v>121252804</v>
       </c>
       <c r="B117" t="n">
-        <v>74694</v>
+        <v>97094</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15826,21 +15837,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>306</v>
+        <v>221063</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15850,10 +15861,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446089</v>
+        <v>446013</v>
       </c>
       <c r="R117" t="n">
-        <v>7026536</v>
+        <v>7026514</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15885,7 +15896,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15895,7 +15906,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15904,7 +15915,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -15913,19 +15923,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121134850</v>
+        <v>121134550</v>
       </c>
       <c r="B28" t="n">
-        <v>91630</v>
+        <v>90468</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445960</v>
+        <v>445911</v>
       </c>
       <c r="R28" t="n">
-        <v>7026492</v>
+        <v>7026564</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4228,22 +4228,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal barrblandskog, sumpskog/myr</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121134552</v>
+        <v>121134545</v>
       </c>
       <c r="B30" t="n">
-        <v>77538</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4437,34 +4437,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445924</v>
+        <v>445987</v>
       </c>
       <c r="R30" t="n">
-        <v>7026587</v>
+        <v>7026510</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4496,7 +4505,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4506,7 +4515,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10 bålar, den längsta 30 cm</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4520,7 +4534,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4535,7 +4549,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4553,10 +4567,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121134550</v>
+        <v>121134875</v>
       </c>
       <c r="B31" t="n">
-        <v>90468</v>
+        <v>74708</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4565,25 +4579,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3215</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4593,10 +4607,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445911</v>
+        <v>446269</v>
       </c>
       <c r="R31" t="n">
-        <v>7026564</v>
+        <v>7026478</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4623,22 +4637,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4652,12 +4666,22 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog, sumpskog/myr</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4668,17 +4692,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121134545</v>
+        <v>121134552</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4691,43 +4715,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445987</v>
+        <v>445924</v>
       </c>
       <c r="R32" t="n">
-        <v>7026510</v>
+        <v>7026587</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4759,7 +4774,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4769,12 +4784,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>10 bålar, den längsta 30 cm</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4788,7 +4798,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4803,7 +4813,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4821,10 +4831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121134875</v>
+        <v>121134850</v>
       </c>
       <c r="B33" t="n">
-        <v>74708</v>
+        <v>91630</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4833,25 +4843,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4861,10 +4871,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446269</v>
+        <v>445960</v>
       </c>
       <c r="R33" t="n">
-        <v>7026478</v>
+        <v>7026492</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4896,7 +4906,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4906,7 +4916,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4920,22 +4930,12 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4953,10 +4953,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121134558</v>
+        <v>121134852</v>
       </c>
       <c r="B34" t="n">
-        <v>78601</v>
+        <v>90711</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446050</v>
+        <v>445963</v>
       </c>
       <c r="R34" t="n">
-        <v>7026501</v>
+        <v>7026504</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5023,22 +5023,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>I gles gammal gransumpskog</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5078,17 +5078,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121134551</v>
+        <v>121134540</v>
       </c>
       <c r="B35" t="n">
-        <v>78601</v>
+        <v>74694</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5097,25 +5097,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445899</v>
+        <v>446088</v>
       </c>
       <c r="R35" t="n">
-        <v>7026589</v>
+        <v>7026528</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5179,12 +5179,13 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5199,7 +5200,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5217,10 +5218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121134877</v>
+        <v>121134558</v>
       </c>
       <c r="B36" t="n">
-        <v>77538</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5233,21 +5234,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5257,10 +5258,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446271</v>
+        <v>446050</v>
       </c>
       <c r="R36" t="n">
-        <v>7026473</v>
+        <v>7026501</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5287,22 +5288,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5316,7 +5317,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gles gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5331,7 +5332,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5342,17 +5343,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121134852</v>
+        <v>121134551</v>
       </c>
       <c r="B37" t="n">
-        <v>90711</v>
+        <v>78601</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5365,21 +5366,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5389,10 +5390,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445963</v>
+        <v>445899</v>
       </c>
       <c r="R37" t="n">
-        <v>7026504</v>
+        <v>7026589</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5419,22 +5420,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5448,7 +5449,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5463,7 +5464,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5474,17 +5475,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121134540</v>
+        <v>121134877</v>
       </c>
       <c r="B38" t="n">
-        <v>74694</v>
+        <v>77538</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5493,25 +5494,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>306</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5521,10 +5522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446088</v>
+        <v>446271</v>
       </c>
       <c r="R38" t="n">
-        <v>7026528</v>
+        <v>7026473</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5551,22 +5552,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5575,13 +5576,12 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5607,17 +5607,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121132927</v>
+        <v>121134535</v>
       </c>
       <c r="B39" t="n">
-        <v>78601</v>
+        <v>78764</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5626,38 +5626,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446305</v>
+        <v>446119</v>
       </c>
       <c r="R39" t="n">
-        <v>7026607</v>
+        <v>7026442</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5684,17 +5693,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>60 cm lång bål</t>
+          <t>Samma som sedd tidigare i år</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5708,22 +5727,22 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
+          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5734,14 +5753,14 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121132928</v>
+        <v>121132927</v>
       </c>
       <c r="B40" t="n">
         <v>78601</v>
@@ -5774,26 +5793,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446290</v>
+        <v>446305</v>
       </c>
       <c r="R40" t="n">
-        <v>7026577</v>
+        <v>7026607</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5830,7 +5840,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>20 bålar</t>
+          <t>60 cm lång bål</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5844,22 +5854,22 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>i gammal gles barrblandskog</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
+          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5877,10 +5887,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121134535</v>
+        <v>121132926</v>
       </c>
       <c r="B41" t="n">
-        <v>78764</v>
+        <v>56563</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5889,47 +5899,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1249</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446119</v>
+        <v>446305</v>
       </c>
       <c r="R41" t="n">
-        <v>7026442</v>
+        <v>7026607</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5956,27 +5957,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Samma som sedd tidigare i år</t>
+          <t>uppflog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5990,22 +5981,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6016,17 +5992,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121132926</v>
+        <v>121132932</v>
       </c>
       <c r="B42" t="n">
-        <v>56563</v>
+        <v>78601</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6035,25 +6011,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6063,10 +6039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446305</v>
+        <v>446284</v>
       </c>
       <c r="R42" t="n">
-        <v>7026607</v>
+        <v>7026556</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6101,11 +6077,6 @@
           <t>2024-03-03</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>uppflog</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6117,7 +6088,22 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6135,10 +6121,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121134546</v>
+        <v>121132928</v>
       </c>
       <c r="B43" t="n">
-        <v>77538</v>
+        <v>78601</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6151,34 +6137,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445987</v>
+        <v>446290</v>
       </c>
       <c r="R43" t="n">
-        <v>7026512</v>
+        <v>7026577</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6205,22 +6200,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>20 bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6234,7 +6224,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6249,7 +6239,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6260,17 +6250,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121132932</v>
+        <v>121134546</v>
       </c>
       <c r="B44" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6283,21 +6273,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6307,10 +6297,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446284</v>
+        <v>445987</v>
       </c>
       <c r="R44" t="n">
-        <v>7026556</v>
+        <v>7026512</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6337,12 +6327,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6382,17 +6382,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121134880</v>
+        <v>121134538</v>
       </c>
       <c r="B45" t="n">
-        <v>56563</v>
+        <v>105171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6405,43 +6405,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>221725</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446259</v>
+        <v>446142</v>
       </c>
       <c r="R45" t="n">
-        <v>7026406</v>
+        <v>7026514</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6468,27 +6459,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Satt i gammal gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6502,7 +6488,12 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6513,17 +6504,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121134538</v>
+        <v>121134880</v>
       </c>
       <c r="B46" t="n">
-        <v>105171</v>
+        <v>56563</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6536,34 +6527,43 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221725</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>446142</v>
+        <v>446259</v>
       </c>
       <c r="R46" t="n">
-        <v>7026514</v>
+        <v>7026406</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6590,22 +6590,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Satt i gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6619,12 +6624,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>På marken</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -7170,10 +7170,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121134870</v>
+        <v>121134860</v>
       </c>
       <c r="B51" t="n">
-        <v>91137</v>
+        <v>78601</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7182,38 +7182,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446262</v>
+        <v>446170</v>
       </c>
       <c r="R51" t="n">
-        <v>7026488</v>
+        <v>7026558</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7245,7 +7254,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7255,7 +7264,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7269,7 +7278,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7284,7 +7293,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7302,10 +7311,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121132931</v>
+        <v>121134865</v>
       </c>
       <c r="B52" t="n">
-        <v>74708</v>
+        <v>78601</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7318,34 +7327,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446284</v>
+        <v>446213</v>
       </c>
       <c r="R52" t="n">
-        <v>7026556</v>
+        <v>7026555</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7372,12 +7390,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7391,7 +7419,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -7406,7 +7434,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7424,10 +7452,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121134860</v>
+        <v>121134870</v>
       </c>
       <c r="B53" t="n">
-        <v>78601</v>
+        <v>91137</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7436,47 +7464,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446170</v>
+        <v>446262</v>
       </c>
       <c r="R53" t="n">
-        <v>7026558</v>
+        <v>7026488</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7508,7 +7527,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7518,7 +7537,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7532,7 +7551,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -7547,7 +7566,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7565,10 +7584,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121134865</v>
+        <v>121132931</v>
       </c>
       <c r="B54" t="n">
-        <v>78601</v>
+        <v>74708</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7581,43 +7600,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446213</v>
+        <v>446284</v>
       </c>
       <c r="R54" t="n">
-        <v>7026555</v>
+        <v>7026556</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7644,22 +7654,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8492,10 +8492,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121134536</v>
+        <v>121132945</v>
       </c>
       <c r="B61" t="n">
-        <v>90693</v>
+        <v>90715</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8508,21 +8508,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>446164</v>
+        <v>446220</v>
       </c>
       <c r="R61" t="n">
-        <v>7026463</v>
+        <v>7026528</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8562,22 +8562,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8591,7 +8581,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8606,7 +8596,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>På död gran # Picea abies</t>
+          <t>på gammal dubbelgran # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8617,17 +8607,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121132945</v>
+        <v>121134536</v>
       </c>
       <c r="B62" t="n">
-        <v>90715</v>
+        <v>90693</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8640,21 +8630,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8664,10 +8654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>446220</v>
+        <v>446164</v>
       </c>
       <c r="R62" t="n">
-        <v>7026528</v>
+        <v>7026463</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8694,12 +8684,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>på gammal dubbelgran # Picea abies</t>
+          <t>På död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -11883,10 +11883,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121134543</v>
+        <v>121134851</v>
       </c>
       <c r="B87" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11895,47 +11895,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>446069</v>
+        <v>445959</v>
       </c>
       <c r="R87" t="n">
-        <v>7026527</v>
+        <v>7026504</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11962,27 +11953,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11996,12 +11982,22 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12012,17 +12008,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121132948</v>
+        <v>121134543</v>
       </c>
       <c r="B88" t="n">
-        <v>77538</v>
+        <v>98081</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12031,38 +12027,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>446111</v>
+        <v>446069</v>
       </c>
       <c r="R88" t="n">
-        <v>7026483</v>
+        <v>7026527</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12089,12 +12094,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12108,22 +12128,12 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12134,17 +12144,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121134851</v>
+        <v>121132948</v>
       </c>
       <c r="B89" t="n">
-        <v>90697</v>
+        <v>77538</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12157,21 +12167,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12181,10 +12191,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445959</v>
+        <v>446111</v>
       </c>
       <c r="R89" t="n">
-        <v>7026504</v>
+        <v>7026483</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12211,22 +12221,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -15556,10 +15556,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252810</v>
+        <v>121252817</v>
       </c>
       <c r="B115" t="n">
-        <v>74694</v>
+        <v>74692</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15572,21 +15572,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>306</v>
+        <v>6439</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15596,10 +15596,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446089</v>
+        <v>446209</v>
       </c>
       <c r="R115" t="n">
-        <v>7026536</v>
+        <v>7026630</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15650,13 +15650,12 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -15671,7 +15670,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15689,10 +15688,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252817</v>
+        <v>121252804</v>
       </c>
       <c r="B116" t="n">
-        <v>74692</v>
+        <v>97094</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15705,21 +15704,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6439</v>
+        <v>221063</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15729,10 +15728,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446209</v>
+        <v>446013</v>
       </c>
       <c r="R116" t="n">
-        <v>7026630</v>
+        <v>7026514</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15764,7 +15763,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15774,7 +15773,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15788,22 +15787,12 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15821,10 +15810,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252804</v>
+        <v>121252810</v>
       </c>
       <c r="B117" t="n">
-        <v>97094</v>
+        <v>74694</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15837,21 +15826,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221063</v>
+        <v>306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15861,10 +15850,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446013</v>
+        <v>446089</v>
       </c>
       <c r="R117" t="n">
-        <v>7026514</v>
+        <v>7026536</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15896,7 +15885,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15906,7 +15895,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15915,6 +15904,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -15923,9 +15913,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -3551,7 +3551,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121117887</v>
+        <v>121117416</v>
       </c>
       <c r="B23" t="n">
         <v>78601</v>
@@ -3584,17 +3584,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svedaunsmyren, Jmt</t>
+          <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446262</v>
+        <v>445930</v>
       </c>
       <c r="R23" t="n">
-        <v>7026371</v>
+        <v>7026585</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3626,7 +3635,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3636,12 +3645,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 stor garnlav</t>
+          <t>Minst 20, långa Gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3668,10 +3677,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121117063</v>
+        <v>121117375</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3684,43 +3693,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
+          <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446063</v>
+        <v>445930</v>
       </c>
       <c r="R24" t="n">
-        <v>7026497</v>
+        <v>7026568</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121117375</v>
+        <v>121117063</v>
       </c>
       <c r="B25" t="n">
-        <v>77538</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3810,34 +3810,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svedaun, Svedaun, Jmt</t>
+          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445930</v>
+        <v>446063</v>
       </c>
       <c r="R25" t="n">
-        <v>7026568</v>
+        <v>7026497</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3869,7 +3878,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3879,7 +3888,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3911,7 +3920,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121117416</v>
+        <v>121117887</v>
       </c>
       <c r="B26" t="n">
         <v>78601</v>
@@ -3944,26 +3953,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svedaun, Svedaun, Jmt</t>
+          <t>Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445930</v>
+        <v>446262</v>
       </c>
       <c r="R26" t="n">
-        <v>7026585</v>
+        <v>7026371</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 20, långa Gammal gran</t>
+          <t>1 stor garnlav</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121134550</v>
+        <v>121132927</v>
       </c>
       <c r="B28" t="n">
-        <v>90468</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445911</v>
+        <v>446305</v>
       </c>
       <c r="R28" t="n">
-        <v>7026564</v>
+        <v>7026607</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4228,22 +4228,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>60 cm lång bål</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4257,12 +4252,22 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog, sumpskog/myr</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4273,14 +4278,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121134878</v>
+        <v>121134860</v>
       </c>
       <c r="B29" t="n">
         <v>78601</v>
@@ -4315,7 +4320,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4329,10 +4334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446262</v>
+        <v>446170</v>
       </c>
       <c r="R29" t="n">
-        <v>7026436</v>
+        <v>7026558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4364,7 +4369,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4374,7 +4379,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4388,7 +4393,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4403,7 +4408,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4421,7 +4426,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121134545</v>
+        <v>121132928</v>
       </c>
       <c r="B30" t="n">
         <v>78601</v>
@@ -4456,7 +4461,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4470,10 +4475,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445987</v>
+        <v>446290</v>
       </c>
       <c r="R30" t="n">
-        <v>7026510</v>
+        <v>7026577</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4500,27 +4505,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>10 bålar, den längsta 30 cm</t>
+          <t>20 bålar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4534,7 +4529,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4549,7 +4544,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4560,17 +4555,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121134875</v>
+        <v>121132950</v>
       </c>
       <c r="B31" t="n">
-        <v>74708</v>
+        <v>78764</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4579,38 +4574,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446269</v>
+        <v>446118</v>
       </c>
       <c r="R31" t="n">
-        <v>7026478</v>
+        <v>7026441</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4637,22 +4641,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:39</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:39</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1 bål</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4666,7 +4665,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4681,7 +4680,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4699,10 +4698,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121134552</v>
+        <v>121134875</v>
       </c>
       <c r="B32" t="n">
-        <v>77538</v>
+        <v>74708</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4715,21 +4714,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4739,10 +4738,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445924</v>
+        <v>446269</v>
       </c>
       <c r="R32" t="n">
-        <v>7026587</v>
+        <v>7026478</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4769,22 +4768,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4798,7 +4797,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4813,7 +4812,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4824,17 +4823,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121134850</v>
+        <v>121134880</v>
       </c>
       <c r="B33" t="n">
-        <v>91630</v>
+        <v>56563</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4847,34 +4846,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445960</v>
+        <v>446259</v>
       </c>
       <c r="R33" t="n">
-        <v>7026492</v>
+        <v>7026406</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4906,7 +4914,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4916,7 +4924,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Satt i gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4930,12 +4943,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>På marken</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4953,10 +4961,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121134852</v>
+        <v>121134549</v>
       </c>
       <c r="B34" t="n">
-        <v>90711</v>
+        <v>74708</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4969,21 +4977,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4993,10 +5001,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445963</v>
+        <v>445936</v>
       </c>
       <c r="R34" t="n">
-        <v>7026504</v>
+        <v>7026522</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5023,22 +5031,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5052,7 +5060,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5067,7 +5075,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5078,17 +5086,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121134540</v>
+        <v>121134543</v>
       </c>
       <c r="B35" t="n">
-        <v>74694</v>
+        <v>98081</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5097,38 +5105,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>306</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446088</v>
+        <v>446069</v>
       </c>
       <c r="R35" t="n">
-        <v>7026528</v>
+        <v>7026527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5160,7 +5177,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5170,7 +5187,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5179,28 +5201,17 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5218,10 +5229,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121134558</v>
+        <v>121134553</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>74708</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5234,21 +5245,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5258,10 +5269,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446050</v>
+        <v>445925</v>
       </c>
       <c r="R36" t="n">
-        <v>7026501</v>
+        <v>7026580</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5293,7 +5304,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5303,7 +5314,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5317,7 +5328,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>I gles gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5332,7 +5343,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5350,10 +5361,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121134551</v>
+        <v>121134552</v>
       </c>
       <c r="B37" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5366,21 +5377,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5390,10 +5401,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445899</v>
+        <v>445924</v>
       </c>
       <c r="R37" t="n">
-        <v>7026589</v>
+        <v>7026587</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5425,7 +5436,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5435,7 +5446,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5464,7 +5475,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5482,7 +5493,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121134877</v>
+        <v>121132936</v>
       </c>
       <c r="B38" t="n">
         <v>77538</v>
@@ -5522,10 +5533,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446271</v>
+        <v>446254</v>
       </c>
       <c r="R38" t="n">
-        <v>7026473</v>
+        <v>7026486</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5552,22 +5563,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5581,7 +5582,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5596,7 +5597,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5614,10 +5615,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121134535</v>
+        <v>121134865</v>
       </c>
       <c r="B39" t="n">
-        <v>78764</v>
+        <v>78601</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5626,30 +5627,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5663,10 +5664,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446119</v>
+        <v>446213</v>
       </c>
       <c r="R39" t="n">
-        <v>7026442</v>
+        <v>7026555</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5693,27 +5694,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:41</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Samma som sedd tidigare i år</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5727,7 +5723,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5742,7 +5738,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5753,17 +5749,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121132927</v>
+        <v>121134536</v>
       </c>
       <c r="B40" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5776,21 +5772,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5800,10 +5796,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446305</v>
+        <v>446164</v>
       </c>
       <c r="R40" t="n">
-        <v>7026607</v>
+        <v>7026463</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5830,17 +5826,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>60 cm lång bål</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5854,22 +5855,22 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
+          <t>På död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5880,17 +5881,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121132926</v>
+        <v>121134858</v>
       </c>
       <c r="B41" t="n">
-        <v>56563</v>
+        <v>90715</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5899,25 +5900,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5927,10 +5928,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446305</v>
+        <v>446092</v>
       </c>
       <c r="R41" t="n">
-        <v>7026607</v>
+        <v>7026520</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5957,17 +5958,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>uppflog</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5981,7 +5987,22 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5999,10 +6020,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121132932</v>
+        <v>121134866</v>
       </c>
       <c r="B42" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6015,21 +6036,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6039,10 +6060,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446284</v>
+        <v>446218</v>
       </c>
       <c r="R42" t="n">
-        <v>7026556</v>
+        <v>7026544</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6069,12 +6090,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6088,7 +6119,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -6103,7 +6134,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6121,10 +6152,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121132928</v>
+        <v>121134544</v>
       </c>
       <c r="B43" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6137,43 +6168,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446290</v>
+        <v>446005</v>
       </c>
       <c r="R43" t="n">
-        <v>7026577</v>
+        <v>7026502</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6200,17 +6222,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>20 bålar</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6224,7 +6251,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>i gammal gles barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6239,7 +6266,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6250,17 +6277,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121134546</v>
+        <v>121134868</v>
       </c>
       <c r="B44" t="n">
-        <v>77538</v>
+        <v>78601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6273,21 +6300,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6297,10 +6324,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445987</v>
+        <v>446262</v>
       </c>
       <c r="R44" t="n">
-        <v>7026512</v>
+        <v>7026488</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6327,22 +6354,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6356,7 +6383,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6371,7 +6398,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6382,17 +6409,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121134538</v>
+        <v>121134535</v>
       </c>
       <c r="B45" t="n">
-        <v>105171</v>
+        <v>78764</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6401,38 +6428,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221725</v>
+        <v>1249</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446142</v>
+        <v>446119</v>
       </c>
       <c r="R45" t="n">
-        <v>7026514</v>
+        <v>7026442</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6464,7 +6500,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6474,7 +6510,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Samma som sedd tidigare i år</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6491,9 +6532,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6511,10 +6562,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121134880</v>
+        <v>121134864</v>
       </c>
       <c r="B46" t="n">
-        <v>56563</v>
+        <v>74708</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6523,47 +6574,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>446259</v>
+        <v>446203</v>
       </c>
       <c r="R46" t="n">
-        <v>7026406</v>
+        <v>7026536</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6595,7 +6637,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6605,12 +6647,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Satt i gammal gran</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6624,7 +6661,22 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6642,7 +6694,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121134873</v>
+        <v>121134861</v>
       </c>
       <c r="B47" t="n">
         <v>77538</v>
@@ -6682,10 +6734,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>446269</v>
+        <v>446197</v>
       </c>
       <c r="R47" t="n">
-        <v>7026478</v>
+        <v>7026538</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6717,7 +6769,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6727,7 +6779,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6741,7 +6793,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6756,7 +6808,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6774,10 +6826,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121134849</v>
+        <v>121134851</v>
       </c>
       <c r="B48" t="n">
-        <v>91137</v>
+        <v>90697</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6786,25 +6838,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6814,10 +6866,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445948</v>
+        <v>445959</v>
       </c>
       <c r="R48" t="n">
-        <v>7026487</v>
+        <v>7026504</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6849,7 +6901,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6859,7 +6911,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6888,7 +6940,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>På grov granlåga # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6906,10 +6958,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121134555</v>
+        <v>121134870</v>
       </c>
       <c r="B49" t="n">
-        <v>90662</v>
+        <v>91137</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6918,25 +6970,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6946,10 +6998,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446030</v>
+        <v>446262</v>
       </c>
       <c r="R49" t="n">
-        <v>7026523</v>
+        <v>7026488</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6976,22 +7028,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7005,7 +7057,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7020,7 +7072,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7031,14 +7083,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121134858</v>
+        <v>121132945</v>
       </c>
       <c r="B50" t="n">
         <v>90715</v>
@@ -7078,10 +7130,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446092</v>
+        <v>446220</v>
       </c>
       <c r="R50" t="n">
-        <v>7026520</v>
+        <v>7026528</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7108,22 +7160,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7137,7 +7179,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7152,7 +7194,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>på gammal dubbelgran # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7170,7 +7212,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121134860</v>
+        <v>121132949</v>
       </c>
       <c r="B51" t="n">
         <v>78601</v>
@@ -7205,7 +7247,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7219,10 +7261,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446170</v>
+        <v>446118</v>
       </c>
       <c r="R51" t="n">
-        <v>7026558</v>
+        <v>7026441</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7249,22 +7291,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>7 bålar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7278,7 +7315,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7293,7 +7330,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7311,10 +7348,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121134865</v>
+        <v>121134871</v>
       </c>
       <c r="B52" t="n">
-        <v>78601</v>
+        <v>74520</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7323,47 +7360,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446213</v>
+        <v>446269</v>
       </c>
       <c r="R52" t="n">
-        <v>7026555</v>
+        <v>7026478</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7395,7 +7423,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7405,7 +7433,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7419,7 +7447,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -7434,7 +7462,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7452,10 +7480,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121134870</v>
+        <v>121134557</v>
       </c>
       <c r="B53" t="n">
-        <v>91137</v>
+        <v>74699</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7468,21 +7496,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>492</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7492,10 +7520,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446262</v>
+        <v>446026</v>
       </c>
       <c r="R53" t="n">
-        <v>7026488</v>
+        <v>7026520</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7522,22 +7550,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7551,22 +7579,22 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7577,17 +7605,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121132931</v>
+        <v>121134852</v>
       </c>
       <c r="B54" t="n">
-        <v>74708</v>
+        <v>90711</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7600,21 +7628,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7624,10 +7652,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446284</v>
+        <v>445963</v>
       </c>
       <c r="R54" t="n">
-        <v>7026556</v>
+        <v>7026504</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7654,12 +7682,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7673,7 +7711,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7688,7 +7726,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7706,10 +7744,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121134542</v>
+        <v>121134548</v>
       </c>
       <c r="B55" t="n">
-        <v>95628</v>
+        <v>88024</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7722,21 +7760,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>510</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7746,10 +7784,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446080</v>
+        <v>445938</v>
       </c>
       <c r="R55" t="n">
-        <v>7026521</v>
+        <v>7026514</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7781,7 +7819,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7791,7 +7829,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7805,7 +7843,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -7820,7 +7858,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>På mycket gammal granlåga # Picea abies</t>
+          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7838,10 +7876,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121134869</v>
+        <v>121134873</v>
       </c>
       <c r="B56" t="n">
-        <v>90697</v>
+        <v>77538</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7854,21 +7892,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7878,10 +7916,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446262</v>
+        <v>446269</v>
       </c>
       <c r="R56" t="n">
-        <v>7026488</v>
+        <v>7026478</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7913,7 +7951,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7923,7 +7961,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7952,7 +7990,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7970,10 +8008,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121134853</v>
+        <v>121134540</v>
       </c>
       <c r="B57" t="n">
-        <v>74699</v>
+        <v>74694</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7982,25 +8020,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>492</v>
+        <v>306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8010,10 +8048,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445965</v>
+        <v>446088</v>
       </c>
       <c r="R57" t="n">
-        <v>7026512</v>
+        <v>7026528</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8040,22 +8078,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8064,12 +8102,13 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -8084,7 +8123,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8095,17 +8134,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121132936</v>
+        <v>121134863</v>
       </c>
       <c r="B58" t="n">
-        <v>77538</v>
+        <v>78601</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8118,21 +8157,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8142,10 +8181,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446254</v>
+        <v>446203</v>
       </c>
       <c r="R58" t="n">
-        <v>7026486</v>
+        <v>7026536</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8172,12 +8211,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8191,7 +8240,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -8206,7 +8255,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8224,10 +8273,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121134867</v>
+        <v>121134859</v>
       </c>
       <c r="B59" t="n">
-        <v>77538</v>
+        <v>74708</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8240,21 +8289,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8264,10 +8313,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446244</v>
+        <v>446158</v>
       </c>
       <c r="R59" t="n">
-        <v>7026516</v>
+        <v>7026570</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8299,7 +8348,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8309,7 +8358,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8338,7 +8387,7 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8356,10 +8405,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121132949</v>
+        <v>121132930</v>
       </c>
       <c r="B60" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8372,43 +8421,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446118</v>
+        <v>446284</v>
       </c>
       <c r="R60" t="n">
-        <v>7026441</v>
+        <v>7026556</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8443,11 +8483,6 @@
           <t>2024-03-03</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>7 bålar</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -8459,7 +8494,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8474,7 +8509,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8492,10 +8527,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121132945</v>
+        <v>121134556</v>
       </c>
       <c r="B61" t="n">
-        <v>90715</v>
+        <v>74713</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8508,21 +8543,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8532,10 +8567,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>446220</v>
+        <v>446026</v>
       </c>
       <c r="R61" t="n">
-        <v>7026528</v>
+        <v>7026520</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8562,12 +8597,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8581,22 +8626,22 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>på gammal dubbelgran # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8607,17 +8652,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121134536</v>
+        <v>121134855</v>
       </c>
       <c r="B62" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8630,21 +8675,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8654,10 +8699,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>446164</v>
+        <v>446045</v>
       </c>
       <c r="R62" t="n">
-        <v>7026463</v>
+        <v>7026526</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8684,22 +8729,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8713,7 +8758,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8728,7 +8773,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>På död gran # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8739,17 +8784,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121134556</v>
+        <v>121134537</v>
       </c>
       <c r="B63" t="n">
-        <v>74713</v>
+        <v>74692</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8758,25 +8803,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1467</v>
+        <v>6439</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8786,10 +8831,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>446026</v>
+        <v>446153</v>
       </c>
       <c r="R63" t="n">
-        <v>7026520</v>
+        <v>7026500</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8821,7 +8866,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8831,7 +8876,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8860,7 +8905,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>På björkhögstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8878,10 +8923,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121134857</v>
+        <v>121134538</v>
       </c>
       <c r="B64" t="n">
-        <v>78601</v>
+        <v>105171</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8890,25 +8935,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8918,10 +8963,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>446075</v>
+        <v>446142</v>
       </c>
       <c r="R64" t="n">
-        <v>7026515</v>
+        <v>7026514</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8948,22 +8993,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8977,22 +9022,12 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9003,17 +9038,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121132934</v>
+        <v>121134539</v>
       </c>
       <c r="B65" t="n">
-        <v>78601</v>
+        <v>74713</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9026,21 +9061,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9050,10 +9085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>446253</v>
+        <v>446088</v>
       </c>
       <c r="R65" t="n">
-        <v>7026514</v>
+        <v>7026528</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9080,12 +9115,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9099,7 +9144,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -9114,7 +9159,7 @@
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9125,17 +9170,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121132950</v>
+        <v>121132931</v>
       </c>
       <c r="B66" t="n">
-        <v>78764</v>
+        <v>74708</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9144,47 +9189,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>446118</v>
+        <v>446284</v>
       </c>
       <c r="R66" t="n">
-        <v>7026441</v>
+        <v>7026556</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9219,11 +9255,6 @@
           <t>2024-03-03</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>1 bål</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9235,7 +9266,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9250,7 +9281,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9268,10 +9299,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121134548</v>
+        <v>121134555</v>
       </c>
       <c r="B67" t="n">
-        <v>88024</v>
+        <v>90662</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9280,25 +9311,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9308,10 +9339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445938</v>
+        <v>446030</v>
       </c>
       <c r="R67" t="n">
-        <v>7026514</v>
+        <v>7026523</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9343,7 +9374,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9353,7 +9384,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9382,7 +9413,7 @@
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9400,10 +9431,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121134541</v>
+        <v>121134546</v>
       </c>
       <c r="B68" t="n">
-        <v>74700</v>
+        <v>77538</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9416,21 +9447,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>308</v>
+        <v>228579</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9440,10 +9471,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>446088</v>
+        <v>445987</v>
       </c>
       <c r="R68" t="n">
-        <v>7026528</v>
+        <v>7026512</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9475,7 +9506,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9485,7 +9516,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9514,7 +9545,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9532,10 +9563,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121134557</v>
+        <v>121134541</v>
       </c>
       <c r="B69" t="n">
-        <v>74699</v>
+        <v>74700</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9544,25 +9575,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9572,10 +9603,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>446026</v>
+        <v>446088</v>
       </c>
       <c r="R69" t="n">
-        <v>7026520</v>
+        <v>7026528</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9607,7 +9638,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9617,7 +9648,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9636,17 +9667,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9664,10 +9695,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121134549</v>
+        <v>121134877</v>
       </c>
       <c r="B70" t="n">
-        <v>74708</v>
+        <v>77538</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9680,21 +9711,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9704,10 +9735,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445936</v>
+        <v>446271</v>
       </c>
       <c r="R70" t="n">
-        <v>7026522</v>
+        <v>7026473</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9734,22 +9765,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9763,7 +9794,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -9778,7 +9809,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9789,17 +9820,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121134859</v>
+        <v>121134867</v>
       </c>
       <c r="B71" t="n">
-        <v>74708</v>
+        <v>77538</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9812,21 +9843,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9836,10 +9867,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>446158</v>
+        <v>446244</v>
       </c>
       <c r="R71" t="n">
-        <v>7026570</v>
+        <v>7026516</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9871,7 +9902,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9881,7 +9912,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9910,7 +9941,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9928,10 +9959,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121134871</v>
+        <v>121134869</v>
       </c>
       <c r="B72" t="n">
-        <v>74520</v>
+        <v>90697</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9940,25 +9971,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9968,10 +9999,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>446269</v>
+        <v>446262</v>
       </c>
       <c r="R72" t="n">
-        <v>7026478</v>
+        <v>7026488</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10003,7 +10034,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10013,7 +10044,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10042,7 +10073,7 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10060,10 +10091,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121134553</v>
+        <v>121134545</v>
       </c>
       <c r="B73" t="n">
-        <v>74708</v>
+        <v>78601</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10076,34 +10107,43 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445925</v>
+        <v>445987</v>
       </c>
       <c r="R73" t="n">
-        <v>7026580</v>
+        <v>7026510</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10135,7 +10175,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10145,7 +10185,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>10 bålar, den längsta 30 cm</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10159,7 +10204,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10174,7 +10219,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10192,10 +10237,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121132943</v>
+        <v>121132926</v>
       </c>
       <c r="B74" t="n">
-        <v>74708</v>
+        <v>56563</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10204,25 +10249,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10232,10 +10277,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>446259</v>
+        <v>446305</v>
       </c>
       <c r="R74" t="n">
-        <v>7026469</v>
+        <v>7026607</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10270,6 +10315,11 @@
           <t>2024-03-03</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>uppflog</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -10281,22 +10331,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10314,10 +10349,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121134862</v>
+        <v>121134849</v>
       </c>
       <c r="B75" t="n">
-        <v>74708</v>
+        <v>91137</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10326,25 +10361,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10354,10 +10389,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>446197</v>
+        <v>445948</v>
       </c>
       <c r="R75" t="n">
-        <v>7026538</v>
+        <v>7026487</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10389,7 +10424,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10399,7 +10434,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10413,7 +10448,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -10428,7 +10463,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På grov granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10446,10 +10481,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121134537</v>
+        <v>121134550</v>
       </c>
       <c r="B76" t="n">
-        <v>74692</v>
+        <v>90468</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10462,21 +10497,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6439</v>
+        <v>3215</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10486,10 +10521,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>446153</v>
+        <v>445911</v>
       </c>
       <c r="R76" t="n">
-        <v>7026500</v>
+        <v>7026564</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10521,7 +10556,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10531,7 +10566,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10545,22 +10580,12 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
+          <t>I gammal barrblandskog, sumpskog/myr</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>På björkhögstubbe # Betula pubescens</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10578,10 +10603,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121134868</v>
+        <v>121134850</v>
       </c>
       <c r="B77" t="n">
-        <v>78601</v>
+        <v>91630</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10590,25 +10615,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10618,10 +10643,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>446262</v>
+        <v>445960</v>
       </c>
       <c r="R77" t="n">
-        <v>7026488</v>
+        <v>7026492</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10653,7 +10678,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10663,7 +10688,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10677,22 +10702,12 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10710,10 +10725,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121134539</v>
+        <v>121134853</v>
       </c>
       <c r="B78" t="n">
-        <v>74713</v>
+        <v>74699</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10722,25 +10737,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1467</v>
+        <v>492</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10750,10 +10765,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>446088</v>
+        <v>445965</v>
       </c>
       <c r="R78" t="n">
-        <v>7026528</v>
+        <v>7026512</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10780,22 +10795,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10809,7 +10824,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -10824,7 +10839,7 @@
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10835,17 +10850,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121134866</v>
+        <v>121134558</v>
       </c>
       <c r="B79" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10858,21 +10873,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10882,10 +10897,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>446218</v>
+        <v>446050</v>
       </c>
       <c r="R79" t="n">
-        <v>7026544</v>
+        <v>7026501</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10912,22 +10927,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10941,7 +10956,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gles gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -10956,7 +10971,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10967,14 +10982,14 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121134863</v>
+        <v>121134551</v>
       </c>
       <c r="B80" t="n">
         <v>78601</v>
@@ -11014,10 +11029,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>446203</v>
+        <v>445899</v>
       </c>
       <c r="R80" t="n">
-        <v>7026536</v>
+        <v>7026589</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11044,22 +11059,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11073,7 +11088,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
@@ -11088,7 +11103,7 @@
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11099,17 +11114,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121134864</v>
+        <v>121132935</v>
       </c>
       <c r="B81" t="n">
-        <v>74708</v>
+        <v>78601</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11122,21 +11137,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11146,10 +11161,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>446203</v>
+        <v>446246</v>
       </c>
       <c r="R81" t="n">
-        <v>7026536</v>
+        <v>7026518</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11176,22 +11191,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11205,7 +11210,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -11220,7 +11225,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11238,10 +11243,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121132930</v>
+        <v>121134862</v>
       </c>
       <c r="B82" t="n">
-        <v>77538</v>
+        <v>74708</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11254,21 +11259,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11278,10 +11283,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>446284</v>
+        <v>446197</v>
       </c>
       <c r="R82" t="n">
-        <v>7026556</v>
+        <v>7026538</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11308,12 +11313,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11327,7 +11342,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -11342,7 +11357,7 @@
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11360,10 +11375,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121134861</v>
+        <v>121134857</v>
       </c>
       <c r="B83" t="n">
-        <v>77538</v>
+        <v>78601</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11376,21 +11391,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -11400,10 +11415,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>446197</v>
+        <v>446075</v>
       </c>
       <c r="R83" t="n">
-        <v>7026538</v>
+        <v>7026515</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11435,7 +11450,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11445,7 +11460,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11474,7 +11489,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11492,10 +11507,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121134544</v>
+        <v>121132943</v>
       </c>
       <c r="B84" t="n">
-        <v>90697</v>
+        <v>74708</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11508,21 +11523,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11532,10 +11547,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>446005</v>
+        <v>446259</v>
       </c>
       <c r="R84" t="n">
-        <v>7026502</v>
+        <v>7026469</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11562,22 +11577,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11591,7 +11596,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11606,7 +11611,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11617,14 +11622,14 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121132944</v>
+        <v>121134878</v>
       </c>
       <c r="B85" t="n">
         <v>78601</v>
@@ -11657,17 +11662,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>446279</v>
+        <v>446262</v>
       </c>
       <c r="R85" t="n">
-        <v>7026455</v>
+        <v>7026436</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11694,17 +11708,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>40 cm lång bål</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11718,22 +11737,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
+          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11751,7 +11770,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121134855</v>
+        <v>121132934</v>
       </c>
       <c r="B86" t="n">
         <v>78601</v>
@@ -11791,10 +11810,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>446045</v>
+        <v>446253</v>
       </c>
       <c r="R86" t="n">
-        <v>7026526</v>
+        <v>7026514</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11821,22 +11840,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11850,7 +11859,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -11865,7 +11874,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11883,10 +11892,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121134851</v>
+        <v>121132932</v>
       </c>
       <c r="B87" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11899,21 +11908,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11923,10 +11932,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445959</v>
+        <v>446284</v>
       </c>
       <c r="R87" t="n">
-        <v>7026504</v>
+        <v>7026556</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11953,22 +11962,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11982,7 +11981,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -11997,7 +11996,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12015,10 +12014,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121134543</v>
+        <v>121134542</v>
       </c>
       <c r="B88" t="n">
-        <v>98081</v>
+        <v>95628</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12027,47 +12026,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>446069</v>
+        <v>446080</v>
       </c>
       <c r="R88" t="n">
-        <v>7026527</v>
+        <v>7026521</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12099,7 +12089,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12109,12 +12099,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12131,9 +12116,19 @@
           <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På mycket gammal granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12273,7 +12268,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121132935</v>
+        <v>121132944</v>
       </c>
       <c r="B90" t="n">
         <v>78601</v>
@@ -12313,10 +12308,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>446246</v>
+        <v>446279</v>
       </c>
       <c r="R90" t="n">
-        <v>7026518</v>
+        <v>7026455</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12351,6 +12346,11 @@
           <t>2024-03-03</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>40 cm lång bål</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12367,17 +12367,17 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12395,10 +12395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252824</v>
+        <v>121252815</v>
       </c>
       <c r="B91" t="n">
-        <v>77538</v>
+        <v>57504</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12411,34 +12411,43 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>446278</v>
+        <v>446189</v>
       </c>
       <c r="R91" t="n">
-        <v>7026536</v>
+        <v>7026651</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12470,7 +12479,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12480,7 +12489,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12494,22 +12503,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12527,10 +12521,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252826</v>
+        <v>121252837</v>
       </c>
       <c r="B92" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12543,21 +12537,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12567,10 +12561,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>446279</v>
+        <v>446201</v>
       </c>
       <c r="R92" t="n">
-        <v>7026520</v>
+        <v>7026410</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12602,7 +12596,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12612,7 +12606,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12626,7 +12620,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -12641,7 +12635,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12659,7 +12653,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252822</v>
+        <v>121252827</v>
       </c>
       <c r="B93" t="n">
         <v>78601</v>
@@ -12699,10 +12693,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>446284</v>
+        <v>446252</v>
       </c>
       <c r="R93" t="n">
-        <v>7026552</v>
+        <v>7026536</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12734,7 +12728,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12744,7 +12738,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12773,7 +12767,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12791,10 +12785,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121252821</v>
+        <v>121252803</v>
       </c>
       <c r="B94" t="n">
-        <v>78601</v>
+        <v>105171</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12803,25 +12797,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12831,10 +12825,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>446282</v>
+        <v>446013</v>
       </c>
       <c r="R94" t="n">
-        <v>7026592</v>
+        <v>7026516</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12866,7 +12860,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12876,7 +12870,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12890,22 +12884,12 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12923,10 +12907,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252815</v>
+        <v>121252821</v>
       </c>
       <c r="B95" t="n">
-        <v>57504</v>
+        <v>78601</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12939,43 +12923,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>446189</v>
+        <v>446282</v>
       </c>
       <c r="R95" t="n">
-        <v>7026651</v>
+        <v>7026592</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13007,7 +12982,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13017,7 +12992,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13031,7 +13006,22 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13049,10 +13039,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252820</v>
+        <v>121252808</v>
       </c>
       <c r="B96" t="n">
-        <v>74708</v>
+        <v>78635</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13065,34 +13055,43 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446258</v>
+        <v>446038</v>
       </c>
       <c r="R96" t="n">
-        <v>7026597</v>
+        <v>7026546</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13124,7 +13123,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13134,7 +13133,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13148,7 +13147,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -13163,7 +13162,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13181,10 +13180,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252837</v>
+        <v>121252800</v>
       </c>
       <c r="B97" t="n">
-        <v>77538</v>
+        <v>57351</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13197,34 +13196,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446201</v>
+        <v>446056</v>
       </c>
       <c r="R97" t="n">
-        <v>7026410</v>
+        <v>7026521</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13256,7 +13260,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13266,7 +13270,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13283,19 +13292,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13313,10 +13312,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252827</v>
+        <v>121252824</v>
       </c>
       <c r="B98" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13329,21 +13328,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13353,7 +13352,7 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446252</v>
+        <v>446278</v>
       </c>
       <c r="R98" t="n">
         <v>7026536</v>
@@ -13388,7 +13387,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13398,7 +13397,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13427,7 +13426,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13445,10 +13444,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121252818</v>
+        <v>121252813</v>
       </c>
       <c r="B99" t="n">
-        <v>74520</v>
+        <v>78601</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13457,25 +13456,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -13485,10 +13484,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>446209</v>
+        <v>446166</v>
       </c>
       <c r="R99" t="n">
-        <v>7026630</v>
+        <v>7026698</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13520,7 +13519,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13530,7 +13529,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13559,7 +13558,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13577,10 +13576,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121252838</v>
+        <v>121252810</v>
       </c>
       <c r="B100" t="n">
-        <v>74708</v>
+        <v>74694</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13589,25 +13588,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6440</v>
+        <v>306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13617,10 +13616,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>446201</v>
+        <v>446089</v>
       </c>
       <c r="R100" t="n">
-        <v>7026410</v>
+        <v>7026536</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13652,7 +13651,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13662,7 +13661,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13671,6 +13670,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13709,10 +13709,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252803</v>
+        <v>121252811</v>
       </c>
       <c r="B101" t="n">
-        <v>105171</v>
+        <v>90693</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13721,25 +13721,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -13749,10 +13749,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>446013</v>
+        <v>446106</v>
       </c>
       <c r="R101" t="n">
-        <v>7026516</v>
+        <v>7026528</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13808,12 +13808,22 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13831,7 +13841,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121252807</v>
+        <v>121252814</v>
       </c>
       <c r="B102" t="n">
         <v>78601</v>
@@ -13871,10 +13881,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>446038</v>
+        <v>446185</v>
       </c>
       <c r="R102" t="n">
-        <v>7026546</v>
+        <v>7026627</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13906,7 +13916,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13916,7 +13926,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13930,7 +13940,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13945,7 +13955,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13963,10 +13973,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252840</v>
+        <v>121252818</v>
       </c>
       <c r="B103" t="n">
-        <v>77538</v>
+        <v>74520</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13975,25 +13985,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -14006,7 +14016,7 @@
         <v>446209</v>
       </c>
       <c r="R103" t="n">
-        <v>7026394</v>
+        <v>7026630</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -14038,7 +14048,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14048,7 +14058,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14062,7 +14072,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -14077,7 +14087,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14095,10 +14105,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121252806</v>
+        <v>121252839</v>
       </c>
       <c r="B104" t="n">
-        <v>74520</v>
+        <v>90715</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14107,25 +14117,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6428</v>
+        <v>5432</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -14135,10 +14145,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>446038</v>
+        <v>446209</v>
       </c>
       <c r="R104" t="n">
-        <v>7026546</v>
+        <v>7026395</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14170,7 +14180,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14180,7 +14190,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14194,7 +14204,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -14209,7 +14219,7 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14227,7 +14237,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252814</v>
+        <v>121252822</v>
       </c>
       <c r="B105" t="n">
         <v>78601</v>
@@ -14267,10 +14277,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>446185</v>
+        <v>446284</v>
       </c>
       <c r="R105" t="n">
-        <v>7026627</v>
+        <v>7026552</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14302,7 +14312,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14312,7 +14322,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14326,7 +14336,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -14341,7 +14351,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14491,7 +14501,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121252823</v>
+        <v>121252826</v>
       </c>
       <c r="B107" t="n">
         <v>78601</v>
@@ -14531,10 +14541,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>446274</v>
+        <v>446279</v>
       </c>
       <c r="R107" t="n">
-        <v>7026540</v>
+        <v>7026520</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14566,7 +14576,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14576,7 +14586,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14605,7 +14615,7 @@
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14623,10 +14633,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252819</v>
+        <v>121252807</v>
       </c>
       <c r="B108" t="n">
-        <v>77538</v>
+        <v>78601</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14639,21 +14649,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14663,10 +14673,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>446258</v>
+        <v>446038</v>
       </c>
       <c r="R108" t="n">
-        <v>7026597</v>
+        <v>7026546</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14698,7 +14708,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14708,7 +14718,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14722,7 +14732,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -14737,7 +14747,7 @@
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14755,10 +14765,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252800</v>
+        <v>121252820</v>
       </c>
       <c r="B109" t="n">
-        <v>57351</v>
+        <v>74708</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14771,39 +14781,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446056</v>
+        <v>446258</v>
       </c>
       <c r="R109" t="n">
-        <v>7026521</v>
+        <v>7026597</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14835,7 +14840,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14845,12 +14850,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14867,9 +14867,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14887,10 +14897,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252808</v>
+        <v>121252802</v>
       </c>
       <c r="B110" t="n">
-        <v>78635</v>
+        <v>90693</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14903,43 +14913,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>185</v>
+        <v>1108</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>446038</v>
+        <v>445982</v>
       </c>
       <c r="R110" t="n">
-        <v>7026546</v>
+        <v>7026514</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14971,7 +14972,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14981,7 +14982,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14995,7 +14996,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -15010,7 +15011,7 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15028,10 +15029,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252811</v>
+        <v>121252819</v>
       </c>
       <c r="B111" t="n">
-        <v>90693</v>
+        <v>77538</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15044,21 +15045,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -15068,10 +15069,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446106</v>
+        <v>446258</v>
       </c>
       <c r="R111" t="n">
-        <v>7026528</v>
+        <v>7026597</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15103,7 +15104,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15113,7 +15114,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15127,7 +15128,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -15142,7 +15143,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15160,10 +15161,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121252835</v>
+        <v>121252823</v>
       </c>
       <c r="B112" t="n">
-        <v>77985</v>
+        <v>78601</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15176,21 +15177,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -15200,10 +15201,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>446209</v>
+        <v>446274</v>
       </c>
       <c r="R112" t="n">
-        <v>7026444</v>
+        <v>7026540</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15235,7 +15236,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -15245,7 +15246,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15259,22 +15260,22 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>I gammal sumpskog/myr</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15292,10 +15293,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121252812</v>
+        <v>121252835</v>
       </c>
       <c r="B113" t="n">
-        <v>78601</v>
+        <v>77985</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15308,21 +15309,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -15332,10 +15333,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>446185</v>
+        <v>446209</v>
       </c>
       <c r="R113" t="n">
-        <v>7026655</v>
+        <v>7026444</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15367,7 +15368,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -15377,7 +15378,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15391,22 +15392,22 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal sumpskog/myr</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15424,10 +15425,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121252825</v>
+        <v>121252836</v>
       </c>
       <c r="B114" t="n">
-        <v>78857</v>
+        <v>78601</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -15436,25 +15437,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -15464,10 +15465,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>446278</v>
+        <v>446201</v>
       </c>
       <c r="R114" t="n">
-        <v>7026536</v>
+        <v>7026410</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15499,7 +15500,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -15509,7 +15510,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15523,7 +15524,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -15538,7 +15539,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15556,10 +15557,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252817</v>
+        <v>121252809</v>
       </c>
       <c r="B115" t="n">
-        <v>74692</v>
+        <v>77538</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15568,25 +15569,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15596,10 +15597,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446209</v>
+        <v>446044</v>
       </c>
       <c r="R115" t="n">
-        <v>7026630</v>
+        <v>7026549</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15631,7 +15632,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15641,7 +15642,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15655,7 +15656,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -15670,7 +15671,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15688,10 +15689,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252804</v>
+        <v>121252840</v>
       </c>
       <c r="B116" t="n">
-        <v>97094</v>
+        <v>77538</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15700,25 +15701,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221063</v>
+        <v>228579</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15728,10 +15729,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446013</v>
+        <v>446209</v>
       </c>
       <c r="R116" t="n">
-        <v>7026514</v>
+        <v>7026394</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15763,7 +15764,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15773,7 +15774,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15787,12 +15788,22 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid dike</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15810,10 +15821,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252810</v>
+        <v>121252838</v>
       </c>
       <c r="B117" t="n">
-        <v>74694</v>
+        <v>74708</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15822,25 +15833,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>306</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15850,10 +15861,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446089</v>
+        <v>446201</v>
       </c>
       <c r="R117" t="n">
-        <v>7026536</v>
+        <v>7026410</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15885,7 +15896,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15895,7 +15906,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15904,7 +15915,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -15925,7 +15935,7 @@
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15943,10 +15953,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252802</v>
+        <v>121252830</v>
       </c>
       <c r="B118" t="n">
-        <v>90693</v>
+        <v>74708</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15959,21 +15969,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15983,10 +15993,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445982</v>
+        <v>446252</v>
       </c>
       <c r="R118" t="n">
-        <v>7026514</v>
+        <v>7026536</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16018,7 +16028,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16028,7 +16038,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16042,7 +16052,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -16057,7 +16067,7 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16075,10 +16085,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252830</v>
+        <v>121252825</v>
       </c>
       <c r="B119" t="n">
-        <v>74708</v>
+        <v>78857</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16087,25 +16097,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6440</v>
+        <v>6459</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -16115,7 +16125,7 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446252</v>
+        <v>446278</v>
       </c>
       <c r="R119" t="n">
         <v>7026536</v>
@@ -16150,7 +16160,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16160,7 +16170,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16189,7 +16199,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16207,10 +16217,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121252833</v>
+        <v>121252806</v>
       </c>
       <c r="B120" t="n">
-        <v>78601</v>
+        <v>74520</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16219,47 +16229,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446233</v>
+        <v>446038</v>
       </c>
       <c r="R120" t="n">
-        <v>7026512</v>
+        <v>7026546</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16291,7 +16292,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -16301,12 +16302,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16320,7 +16316,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -16335,7 +16331,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16353,10 +16349,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121252839</v>
+        <v>121252833</v>
       </c>
       <c r="B121" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -16369,34 +16365,43 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>446209</v>
+        <v>446233</v>
       </c>
       <c r="R121" t="n">
-        <v>7026395</v>
+        <v>7026512</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16428,7 +16433,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -16438,7 +16443,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16452,7 +16462,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -16467,7 +16477,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16485,7 +16495,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252836</v>
+        <v>121252812</v>
       </c>
       <c r="B122" t="n">
         <v>78601</v>
@@ -16525,10 +16535,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446201</v>
+        <v>446185</v>
       </c>
       <c r="R122" t="n">
-        <v>7026410</v>
+        <v>7026655</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16560,7 +16570,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16570,7 +16580,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16584,7 +16594,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -16599,7 +16609,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16617,10 +16627,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252813</v>
+        <v>121252817</v>
       </c>
       <c r="B123" t="n">
-        <v>78601</v>
+        <v>74692</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16629,25 +16639,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16657,10 +16667,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446166</v>
+        <v>446209</v>
       </c>
       <c r="R123" t="n">
-        <v>7026698</v>
+        <v>7026630</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16692,7 +16702,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16702,7 +16712,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16731,7 +16741,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -16749,10 +16759,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252809</v>
+        <v>121252804</v>
       </c>
       <c r="B124" t="n">
-        <v>77538</v>
+        <v>97094</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16761,25 +16771,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228579</v>
+        <v>221063</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -16789,10 +16799,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>446044</v>
+        <v>446013</v>
       </c>
       <c r="R124" t="n">
-        <v>7026549</v>
+        <v>7026514</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16824,7 +16834,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16834,7 +16844,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16848,22 +16858,12 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -5888,10 +5888,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121134858</v>
+        <v>121134544</v>
       </c>
       <c r="B41" t="n">
-        <v>90715</v>
+        <v>90697</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5904,21 +5904,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446092</v>
+        <v>446005</v>
       </c>
       <c r="R41" t="n">
-        <v>7026520</v>
+        <v>7026502</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5958,22 +5958,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6013,14 +6013,14 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121134866</v>
+        <v>121134858</v>
       </c>
       <c r="B42" t="n">
         <v>90715</v>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446218</v>
+        <v>446092</v>
       </c>
       <c r="R42" t="n">
-        <v>7026544</v>
+        <v>7026520</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6152,10 +6152,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121134544</v>
+        <v>121134866</v>
       </c>
       <c r="B43" t="n">
-        <v>90697</v>
+        <v>90715</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6168,21 +6168,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446005</v>
+        <v>446218</v>
       </c>
       <c r="R43" t="n">
-        <v>7026502</v>
+        <v>7026544</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6222,22 +6222,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6416,10 +6416,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121134535</v>
+        <v>121134864</v>
       </c>
       <c r="B45" t="n">
-        <v>78764</v>
+        <v>74708</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6428,47 +6428,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446119</v>
+        <v>446203</v>
       </c>
       <c r="R45" t="n">
-        <v>7026442</v>
+        <v>7026536</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6495,27 +6486,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:41</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Samma som sedd tidigare i år</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6529,7 +6515,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6544,7 +6530,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6555,17 +6541,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121134864</v>
+        <v>121134535</v>
       </c>
       <c r="B46" t="n">
-        <v>74708</v>
+        <v>78764</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6574,38 +6560,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>446203</v>
+        <v>446119</v>
       </c>
       <c r="R46" t="n">
-        <v>7026536</v>
+        <v>7026442</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6632,22 +6627,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Samma som sedd tidigare i år</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6958,10 +6958,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121134870</v>
+        <v>121132949</v>
       </c>
       <c r="B49" t="n">
-        <v>91137</v>
+        <v>78601</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6970,38 +6970,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446262</v>
+        <v>446118</v>
       </c>
       <c r="R49" t="n">
-        <v>7026488</v>
+        <v>7026441</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7028,22 +7037,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>7 bålar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7057,7 +7061,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7072,7 +7076,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7212,10 +7216,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121132949</v>
+        <v>121134870</v>
       </c>
       <c r="B51" t="n">
-        <v>78601</v>
+        <v>91137</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7224,47 +7228,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446118</v>
+        <v>446262</v>
       </c>
       <c r="R51" t="n">
-        <v>7026441</v>
+        <v>7026488</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7291,17 +7286,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>7 bålar</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7348,10 +7348,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121134871</v>
+        <v>121134557</v>
       </c>
       <c r="B52" t="n">
-        <v>74520</v>
+        <v>74699</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7360,25 +7360,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6428</v>
+        <v>492</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446269</v>
+        <v>446026</v>
       </c>
       <c r="R52" t="n">
-        <v>7026478</v>
+        <v>7026520</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7418,22 +7418,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7447,22 +7447,22 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121134557</v>
+        <v>121134852</v>
       </c>
       <c r="B53" t="n">
-        <v>74699</v>
+        <v>90711</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7492,25 +7492,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>492</v>
+        <v>1204</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446026</v>
+        <v>445963</v>
       </c>
       <c r="R53" t="n">
-        <v>7026520</v>
+        <v>7026504</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7550,22 +7550,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7579,22 +7579,22 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7605,17 +7605,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121134852</v>
+        <v>121134871</v>
       </c>
       <c r="B54" t="n">
-        <v>90711</v>
+        <v>74520</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7624,25 +7624,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1204</v>
+        <v>6428</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7652,10 +7652,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445963</v>
+        <v>446269</v>
       </c>
       <c r="R54" t="n">
-        <v>7026504</v>
+        <v>7026478</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8791,10 +8791,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121134537</v>
+        <v>121134539</v>
       </c>
       <c r="B63" t="n">
-        <v>74692</v>
+        <v>74713</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8803,25 +8803,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6439</v>
+        <v>1467</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>446153</v>
+        <v>446088</v>
       </c>
       <c r="R63" t="n">
-        <v>7026500</v>
+        <v>7026528</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8895,17 +8895,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>På björkhögstubbe # Betula pubescens</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8923,10 +8923,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121134538</v>
+        <v>121134537</v>
       </c>
       <c r="B64" t="n">
-        <v>105171</v>
+        <v>74692</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8939,21 +8939,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221725</v>
+        <v>6439</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8963,10 +8963,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>446142</v>
+        <v>446153</v>
       </c>
       <c r="R64" t="n">
-        <v>7026514</v>
+        <v>7026500</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9025,9 +9025,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På björkhögstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9045,10 +9055,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121134539</v>
+        <v>121134538</v>
       </c>
       <c r="B65" t="n">
-        <v>74713</v>
+        <v>105171</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9057,25 +9067,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1467</v>
+        <v>221725</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9085,10 +9095,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>446088</v>
+        <v>446142</v>
       </c>
       <c r="R65" t="n">
-        <v>7026528</v>
+        <v>7026514</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9120,7 +9130,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9130,7 +9140,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9147,19 +9157,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121134541</v>
+        <v>121134545</v>
       </c>
       <c r="B69" t="n">
-        <v>74700</v>
+        <v>78601</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9579,34 +9579,43 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>446088</v>
+        <v>445987</v>
       </c>
       <c r="R69" t="n">
-        <v>7026528</v>
+        <v>7026510</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9638,7 +9647,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9648,7 +9657,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>10 bålar, den längsta 30 cm</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9677,7 +9691,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9695,10 +9709,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121134877</v>
+        <v>121134869</v>
       </c>
       <c r="B70" t="n">
-        <v>77538</v>
+        <v>90697</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9711,21 +9725,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9735,10 +9749,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>446271</v>
+        <v>446262</v>
       </c>
       <c r="R70" t="n">
-        <v>7026473</v>
+        <v>7026488</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9770,7 +9784,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9780,7 +9794,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9809,7 +9823,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9827,10 +9841,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121134867</v>
+        <v>121134541</v>
       </c>
       <c r="B71" t="n">
-        <v>77538</v>
+        <v>74700</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9843,21 +9857,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9867,10 +9881,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>446244</v>
+        <v>446088</v>
       </c>
       <c r="R71" t="n">
-        <v>7026516</v>
+        <v>7026528</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9897,22 +9911,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9926,7 +9940,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9941,7 +9955,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9952,17 +9966,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121134869</v>
+        <v>121132926</v>
       </c>
       <c r="B72" t="n">
-        <v>90697</v>
+        <v>56563</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9971,25 +9985,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9999,10 +10013,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>446262</v>
+        <v>446305</v>
       </c>
       <c r="R72" t="n">
-        <v>7026488</v>
+        <v>7026607</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10029,22 +10043,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>uppflog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10058,22 +10067,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>På granlåga # Picea abies</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10091,10 +10085,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121134545</v>
+        <v>121134877</v>
       </c>
       <c r="B73" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10107,43 +10101,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445987</v>
+        <v>446271</v>
       </c>
       <c r="R73" t="n">
-        <v>7026510</v>
+        <v>7026473</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10170,27 +10155,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>10 bålar, den längsta 30 cm</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10204,7 +10184,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10219,7 +10199,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10230,17 +10210,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121132926</v>
+        <v>121134867</v>
       </c>
       <c r="B74" t="n">
-        <v>56563</v>
+        <v>77538</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10249,25 +10229,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100138</v>
+        <v>228579</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10277,10 +10257,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>446305</v>
+        <v>446244</v>
       </c>
       <c r="R74" t="n">
-        <v>7026607</v>
+        <v>7026516</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10307,17 +10287,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>uppflog</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10331,7 +10316,22 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -12014,10 +12014,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121134542</v>
+        <v>121132948</v>
       </c>
       <c r="B88" t="n">
-        <v>95628</v>
+        <v>77538</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12030,21 +12030,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>228579</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -12054,10 +12054,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>446080</v>
+        <v>446111</v>
       </c>
       <c r="R88" t="n">
-        <v>7026521</v>
+        <v>7026483</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12084,22 +12084,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>17:04</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>17:04</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12113,7 +12103,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -12128,7 +12118,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>På mycket gammal granlåga # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12139,17 +12129,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121132948</v>
+        <v>121134542</v>
       </c>
       <c r="B89" t="n">
-        <v>77538</v>
+        <v>95628</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12162,21 +12152,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228579</v>
+        <v>53</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12186,10 +12176,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>446111</v>
+        <v>446080</v>
       </c>
       <c r="R89" t="n">
-        <v>7026483</v>
+        <v>7026521</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12216,12 +12206,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På mycket gammal granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -13709,10 +13709,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252811</v>
+        <v>121252814</v>
       </c>
       <c r="B101" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13725,21 +13725,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -13749,10 +13749,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>446106</v>
+        <v>446185</v>
       </c>
       <c r="R101" t="n">
-        <v>7026528</v>
+        <v>7026627</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13841,10 +13841,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121252814</v>
+        <v>121252818</v>
       </c>
       <c r="B102" t="n">
-        <v>78601</v>
+        <v>74520</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13853,25 +13853,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>446185</v>
+        <v>446209</v>
       </c>
       <c r="R102" t="n">
-        <v>7026627</v>
+        <v>7026630</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13973,10 +13973,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252818</v>
+        <v>121252811</v>
       </c>
       <c r="B103" t="n">
-        <v>74520</v>
+        <v>90693</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13985,25 +13985,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6428</v>
+        <v>1108</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -14013,10 +14013,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>446209</v>
+        <v>446106</v>
       </c>
       <c r="R103" t="n">
-        <v>7026630</v>
+        <v>7026528</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>i gammal granskog</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -3554,7 +3554,7 @@
         <v>121117416</v>
       </c>
       <c r="B23" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121117375</v>
+        <v>121117887</v>
       </c>
       <c r="B24" t="n">
-        <v>77538</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3693,34 +3693,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svedaun, Svedaun, Jmt</t>
+          <t>Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445930</v>
+        <v>446262</v>
       </c>
       <c r="R24" t="n">
-        <v>7026568</v>
+        <v>7026371</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1 stor garnlav</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121117063</v>
+        <v>121117224</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3839,14 +3839,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
+          <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446063</v>
+        <v>446032</v>
       </c>
       <c r="R25" t="n">
-        <v>7026497</v>
+        <v>7026520</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3888,12 +3888,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3920,10 +3915,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121117887</v>
+        <v>121117375</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>77541</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3936,34 +3931,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svedaunsmyren, Jmt</t>
+          <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446262</v>
+        <v>445930</v>
       </c>
       <c r="R26" t="n">
-        <v>7026371</v>
+        <v>7026568</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3995,7 +3990,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4005,12 +4000,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 stor garnlav</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4030,17 +4025,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121117224</v>
+        <v>121117063</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4072,7 +4067,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4082,14 +4077,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svedaun, Svedaun, Jmt</t>
+          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446032</v>
+        <v>446063</v>
       </c>
       <c r="R27" t="n">
-        <v>7026520</v>
+        <v>7026497</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4121,7 +4116,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4131,7 +4126,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121132927</v>
+        <v>121134548</v>
       </c>
       <c r="B28" t="n">
-        <v>78601</v>
+        <v>88031</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446305</v>
+        <v>445938</v>
       </c>
       <c r="R28" t="n">
-        <v>7026607</v>
+        <v>7026514</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4228,17 +4228,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>60 cm lång bål</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4252,22 +4257,22 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
+          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4278,17 +4283,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121134860</v>
+        <v>121134851</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4301,43 +4306,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446170</v>
+        <v>445959</v>
       </c>
       <c r="R29" t="n">
-        <v>7026558</v>
+        <v>7026504</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4369,7 +4365,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4379,7 +4375,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4393,7 +4389,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4408,7 +4404,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4426,10 +4422,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121132928</v>
+        <v>121134555</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4438,47 +4434,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446290</v>
+        <v>446030</v>
       </c>
       <c r="R30" t="n">
-        <v>7026577</v>
+        <v>7026523</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4505,17 +4492,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>20 bålar</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4529,7 +4521,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>i gammal gles barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4544,7 +4536,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
+          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4555,17 +4547,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121132950</v>
+        <v>121134543</v>
       </c>
       <c r="B31" t="n">
-        <v>78764</v>
+        <v>98094</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4578,31 +4570,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1249</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4611,10 +4603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446118</v>
+        <v>446069</v>
       </c>
       <c r="R31" t="n">
-        <v>7026441</v>
+        <v>7026527</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4641,17 +4633,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 bål</t>
+          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4665,22 +4667,12 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4691,17 +4683,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121134875</v>
+        <v>121132931</v>
       </c>
       <c r="B32" t="n">
-        <v>74708</v>
+        <v>74710</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4738,10 +4730,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446269</v>
+        <v>446284</v>
       </c>
       <c r="R32" t="n">
-        <v>7026478</v>
+        <v>7026556</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4768,22 +4760,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:39</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:39</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4797,7 +4779,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4812,7 +4794,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4830,10 +4812,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121134880</v>
+        <v>121132943</v>
       </c>
       <c r="B33" t="n">
-        <v>56563</v>
+        <v>74710</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4842,37 +4824,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
@@ -4882,7 +4855,7 @@
         <v>446259</v>
       </c>
       <c r="R33" t="n">
-        <v>7026406</v>
+        <v>7026469</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4909,27 +4882,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Satt i gammal gran</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4943,7 +4901,22 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4961,10 +4934,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121134549</v>
+        <v>121134556</v>
       </c>
       <c r="B34" t="n">
-        <v>74708</v>
+        <v>74715</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4977,21 +4950,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -5001,10 +4974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445936</v>
+        <v>446026</v>
       </c>
       <c r="R34" t="n">
-        <v>7026522</v>
+        <v>7026520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5036,7 +5009,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5046,7 +5019,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5065,17 +5038,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5093,10 +5066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121134543</v>
+        <v>121132936</v>
       </c>
       <c r="B35" t="n">
-        <v>98081</v>
+        <v>77541</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5105,47 +5078,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446069</v>
+        <v>446254</v>
       </c>
       <c r="R35" t="n">
-        <v>7026527</v>
+        <v>7026486</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5172,27 +5136,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5206,12 +5155,22 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5222,17 +5181,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121134553</v>
+        <v>121132949</v>
       </c>
       <c r="B36" t="n">
-        <v>74708</v>
+        <v>78604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5245,34 +5204,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445925</v>
+        <v>446118</v>
       </c>
       <c r="R36" t="n">
-        <v>7026580</v>
+        <v>7026441</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5299,22 +5267,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>7 bålar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5328,7 +5291,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5343,7 +5306,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5354,17 +5317,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121134552</v>
+        <v>121132944</v>
       </c>
       <c r="B37" t="n">
-        <v>77538</v>
+        <v>78604</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5377,21 +5340,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5401,10 +5364,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445924</v>
+        <v>446279</v>
       </c>
       <c r="R37" t="n">
-        <v>7026587</v>
+        <v>7026455</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5431,22 +5394,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>40 cm lång bål</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5460,22 +5418,22 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5486,17 +5444,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121132936</v>
+        <v>121134862</v>
       </c>
       <c r="B38" t="n">
-        <v>77538</v>
+        <v>74710</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5509,21 +5467,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5533,10 +5491,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446254</v>
+        <v>446197</v>
       </c>
       <c r="R38" t="n">
-        <v>7026486</v>
+        <v>7026538</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5563,12 +5521,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5582,7 +5550,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5597,7 +5565,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5615,10 +5583,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121134865</v>
+        <v>121134880</v>
       </c>
       <c r="B39" t="n">
-        <v>78601</v>
+        <v>56563</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5627,35 +5595,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5664,10 +5632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446213</v>
+        <v>446259</v>
       </c>
       <c r="R39" t="n">
-        <v>7026555</v>
+        <v>7026406</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5699,7 +5667,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5709,7 +5677,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Satt i gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5723,22 +5696,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5756,10 +5714,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121134536</v>
+        <v>121132926</v>
       </c>
       <c r="B40" t="n">
-        <v>90693</v>
+        <v>56563</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5768,25 +5726,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5796,10 +5754,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446164</v>
+        <v>446305</v>
       </c>
       <c r="R40" t="n">
-        <v>7026463</v>
+        <v>7026607</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5826,22 +5784,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>uppflog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5855,22 +5808,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>På död gran # Picea abies</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5881,17 +5819,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121134544</v>
+        <v>121134535</v>
       </c>
       <c r="B41" t="n">
-        <v>90697</v>
+        <v>78767</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5900,38 +5838,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446005</v>
+        <v>446119</v>
       </c>
       <c r="R41" t="n">
-        <v>7026502</v>
+        <v>7026442</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5963,7 +5910,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5973,7 +5920,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Samma som sedd tidigare i år</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6002,7 +5954,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6020,10 +5972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121134858</v>
+        <v>121134875</v>
       </c>
       <c r="B42" t="n">
-        <v>90715</v>
+        <v>74710</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6036,21 +5988,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6060,10 +6012,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446092</v>
+        <v>446269</v>
       </c>
       <c r="R42" t="n">
-        <v>7026520</v>
+        <v>7026478</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6095,7 +6047,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6105,7 +6057,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6119,7 +6071,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -6134,7 +6086,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6152,10 +6104,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121134866</v>
+        <v>121134536</v>
       </c>
       <c r="B43" t="n">
-        <v>90715</v>
+        <v>90705</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6168,21 +6120,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6192,10 +6144,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446218</v>
+        <v>446164</v>
       </c>
       <c r="R43" t="n">
-        <v>7026544</v>
+        <v>7026463</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6222,22 +6174,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6251,7 +6203,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6266,7 +6218,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6277,17 +6229,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121134868</v>
+        <v>121134849</v>
       </c>
       <c r="B44" t="n">
-        <v>78601</v>
+        <v>91149</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6296,25 +6248,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6324,10 +6276,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446262</v>
+        <v>445948</v>
       </c>
       <c r="R44" t="n">
-        <v>7026488</v>
+        <v>7026487</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6359,7 +6311,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6369,7 +6321,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6383,7 +6335,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6398,7 +6350,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På grov granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6416,10 +6368,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121134864</v>
+        <v>121134545</v>
       </c>
       <c r="B45" t="n">
-        <v>74708</v>
+        <v>78604</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6432,34 +6384,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446203</v>
+        <v>445987</v>
       </c>
       <c r="R45" t="n">
-        <v>7026536</v>
+        <v>7026510</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6486,22 +6447,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>10 bålar, den längsta 30 cm</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6515,7 +6481,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6530,7 +6496,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6541,17 +6507,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121134535</v>
+        <v>121134861</v>
       </c>
       <c r="B46" t="n">
-        <v>78764</v>
+        <v>77541</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6560,47 +6526,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>446119</v>
+        <v>446197</v>
       </c>
       <c r="R46" t="n">
-        <v>7026442</v>
+        <v>7026538</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6627,27 +6584,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:41</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Samma som sedd tidigare i år</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6661,7 +6613,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6676,7 +6628,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6687,17 +6639,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121134861</v>
+        <v>121134858</v>
       </c>
       <c r="B47" t="n">
-        <v>77538</v>
+        <v>90727</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6710,21 +6662,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6734,10 +6686,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>446197</v>
+        <v>446092</v>
       </c>
       <c r="R47" t="n">
-        <v>7026538</v>
+        <v>7026520</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6769,7 +6721,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6779,7 +6731,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6808,7 +6760,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6826,10 +6778,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121134851</v>
+        <v>121134544</v>
       </c>
       <c r="B48" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6866,10 +6818,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445959</v>
+        <v>446005</v>
       </c>
       <c r="R48" t="n">
-        <v>7026504</v>
+        <v>7026502</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6896,22 +6848,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6925,7 +6877,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6951,17 +6903,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121132949</v>
+        <v>121134866</v>
       </c>
       <c r="B49" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6974,43 +6926,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446118</v>
+        <v>446218</v>
       </c>
       <c r="R49" t="n">
-        <v>7026441</v>
+        <v>7026544</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7037,17 +6980,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>7 bålar</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7061,7 +7009,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7076,7 +7024,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7094,10 +7042,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121132945</v>
+        <v>121134868</v>
       </c>
       <c r="B50" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7110,21 +7058,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7134,10 +7082,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446220</v>
+        <v>446262</v>
       </c>
       <c r="R50" t="n">
-        <v>7026528</v>
+        <v>7026488</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7164,12 +7112,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7183,7 +7141,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7198,7 +7156,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>på gammal dubbelgran # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7216,10 +7174,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121134870</v>
+        <v>121134860</v>
       </c>
       <c r="B51" t="n">
-        <v>91137</v>
+        <v>78604</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7228,38 +7186,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446262</v>
+        <v>446170</v>
       </c>
       <c r="R51" t="n">
-        <v>7026488</v>
+        <v>7026558</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7291,7 +7258,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7301,7 +7268,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7315,7 +7282,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7330,7 +7297,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7348,10 +7315,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121134557</v>
+        <v>121134855</v>
       </c>
       <c r="B52" t="n">
-        <v>74699</v>
+        <v>78604</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7360,25 +7327,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7388,10 +7355,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446026</v>
+        <v>446045</v>
       </c>
       <c r="R52" t="n">
-        <v>7026520</v>
+        <v>7026526</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7418,22 +7385,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7447,22 +7414,22 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7473,17 +7440,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121134852</v>
+        <v>121134552</v>
       </c>
       <c r="B53" t="n">
-        <v>90711</v>
+        <v>77541</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7496,21 +7463,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1204</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7520,10 +7487,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445963</v>
+        <v>445924</v>
       </c>
       <c r="R53" t="n">
-        <v>7026504</v>
+        <v>7026587</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7550,22 +7517,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7579,7 +7546,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -7594,7 +7561,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7605,17 +7572,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121134871</v>
+        <v>121134850</v>
       </c>
       <c r="B54" t="n">
-        <v>74520</v>
+        <v>91642</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7628,21 +7595,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6428</v>
+        <v>4769</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7652,10 +7619,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446269</v>
+        <v>445960</v>
       </c>
       <c r="R54" t="n">
-        <v>7026478</v>
+        <v>7026492</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7687,7 +7654,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7697,7 +7664,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7711,22 +7678,12 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7744,10 +7701,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121134548</v>
+        <v>121134551</v>
       </c>
       <c r="B55" t="n">
-        <v>88024</v>
+        <v>78604</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7760,21 +7717,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7784,10 +7741,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445938</v>
+        <v>445899</v>
       </c>
       <c r="R55" t="n">
-        <v>7026514</v>
+        <v>7026589</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7819,7 +7776,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7829,7 +7786,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7843,7 +7800,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -7858,7 +7815,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7879,7 +7836,7 @@
         <v>121134873</v>
       </c>
       <c r="B56" t="n">
-        <v>77538</v>
+        <v>77541</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8008,10 +7965,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121134540</v>
+        <v>121134878</v>
       </c>
       <c r="B57" t="n">
-        <v>74694</v>
+        <v>78604</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8020,38 +7977,47 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446088</v>
+        <v>446262</v>
       </c>
       <c r="R57" t="n">
-        <v>7026528</v>
+        <v>7026436</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8078,22 +8044,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8102,13 +8068,12 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -8123,7 +8088,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8134,17 +8099,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121134863</v>
+        <v>121134877</v>
       </c>
       <c r="B58" t="n">
-        <v>78601</v>
+        <v>77541</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8157,21 +8122,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8181,10 +8146,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446203</v>
+        <v>446271</v>
       </c>
       <c r="R58" t="n">
-        <v>7026536</v>
+        <v>7026473</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8216,7 +8181,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8226,7 +8191,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8240,7 +8205,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -8255,7 +8220,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8273,10 +8238,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121134859</v>
+        <v>121134863</v>
       </c>
       <c r="B59" t="n">
-        <v>74708</v>
+        <v>78604</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8289,21 +8254,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8313,10 +8278,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446158</v>
+        <v>446203</v>
       </c>
       <c r="R59" t="n">
-        <v>7026570</v>
+        <v>7026536</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8348,7 +8313,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8358,7 +8323,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8387,7 +8352,7 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8405,10 +8370,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121132930</v>
+        <v>121134857</v>
       </c>
       <c r="B60" t="n">
-        <v>77538</v>
+        <v>78604</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8421,21 +8386,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8445,10 +8410,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446284</v>
+        <v>446075</v>
       </c>
       <c r="R60" t="n">
-        <v>7026556</v>
+        <v>7026515</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8475,12 +8440,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8494,7 +8469,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8509,7 +8484,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8527,10 +8502,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121134556</v>
+        <v>121134553</v>
       </c>
       <c r="B61" t="n">
-        <v>74713</v>
+        <v>74710</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8543,21 +8518,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8567,10 +8542,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>446026</v>
+        <v>445925</v>
       </c>
       <c r="R61" t="n">
-        <v>7026520</v>
+        <v>7026580</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8602,7 +8577,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8612,7 +8587,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8626,22 +8601,22 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8659,10 +8634,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121134855</v>
+        <v>121134870</v>
       </c>
       <c r="B62" t="n">
-        <v>78601</v>
+        <v>91149</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8671,25 +8646,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8699,10 +8674,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>446045</v>
+        <v>446262</v>
       </c>
       <c r="R62" t="n">
-        <v>7026526</v>
+        <v>7026488</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8734,7 +8709,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8744,7 +8719,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8758,7 +8733,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8773,7 +8748,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8791,10 +8766,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121134539</v>
+        <v>121134557</v>
       </c>
       <c r="B63" t="n">
-        <v>74713</v>
+        <v>74701</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8803,25 +8778,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1467</v>
+        <v>492</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8831,10 +8806,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>446088</v>
+        <v>446026</v>
       </c>
       <c r="R63" t="n">
-        <v>7026528</v>
+        <v>7026520</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8866,7 +8841,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8876,7 +8851,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8895,17 +8870,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8923,10 +8898,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121134537</v>
+        <v>121132932</v>
       </c>
       <c r="B64" t="n">
-        <v>74692</v>
+        <v>78604</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8935,25 +8910,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8963,10 +8938,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>446153</v>
+        <v>446284</v>
       </c>
       <c r="R64" t="n">
-        <v>7026500</v>
+        <v>7026556</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8993,22 +8968,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9022,22 +8987,22 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>På björkhögstubbe # Betula pubescens</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9048,17 +9013,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121134538</v>
+        <v>121134865</v>
       </c>
       <c r="B65" t="n">
-        <v>105171</v>
+        <v>78604</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9067,38 +9032,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>446142</v>
+        <v>446213</v>
       </c>
       <c r="R65" t="n">
-        <v>7026514</v>
+        <v>7026555</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9125,22 +9099,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9154,12 +9128,22 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9170,17 +9154,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121132931</v>
+        <v>121134546</v>
       </c>
       <c r="B66" t="n">
-        <v>74708</v>
+        <v>77541</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9193,21 +9177,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9217,10 +9201,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>446284</v>
+        <v>445987</v>
       </c>
       <c r="R66" t="n">
-        <v>7026556</v>
+        <v>7026512</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9247,12 +9231,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9266,7 +9260,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9281,7 +9275,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9292,17 +9286,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121134555</v>
+        <v>121134538</v>
       </c>
       <c r="B67" t="n">
-        <v>90662</v>
+        <v>105184</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9315,21 +9309,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9339,10 +9333,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>446030</v>
+        <v>446142</v>
       </c>
       <c r="R67" t="n">
-        <v>7026523</v>
+        <v>7026514</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9374,7 +9368,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9384,7 +9378,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9401,19 +9395,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9431,10 +9415,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121134546</v>
+        <v>121134541</v>
       </c>
       <c r="B68" t="n">
-        <v>77538</v>
+        <v>74702</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9447,21 +9431,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9471,10 +9455,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445987</v>
+        <v>446088</v>
       </c>
       <c r="R68" t="n">
-        <v>7026512</v>
+        <v>7026528</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9506,7 +9490,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9516,7 +9500,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9545,7 +9529,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9563,10 +9547,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121134545</v>
+        <v>121132950</v>
       </c>
       <c r="B69" t="n">
-        <v>78601</v>
+        <v>78767</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9575,30 +9559,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9612,10 +9596,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445987</v>
+        <v>446118</v>
       </c>
       <c r="R69" t="n">
-        <v>7026510</v>
+        <v>7026441</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9642,27 +9626,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>10 bålar, den längsta 30 cm</t>
+          <t>1 bål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9676,7 +9650,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9691,7 +9665,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9702,17 +9676,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121134869</v>
+        <v>121134550</v>
       </c>
       <c r="B70" t="n">
-        <v>90697</v>
+        <v>90480</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9721,25 +9695,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9749,10 +9723,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>446262</v>
+        <v>445911</v>
       </c>
       <c r="R70" t="n">
-        <v>7026488</v>
+        <v>7026564</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9779,22 +9753,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9808,22 +9782,12 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal barrblandskog, sumpskog/myr</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9834,17 +9798,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121134541</v>
+        <v>121134859</v>
       </c>
       <c r="B71" t="n">
-        <v>74700</v>
+        <v>74710</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9857,21 +9821,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9881,10 +9845,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>446088</v>
+        <v>446158</v>
       </c>
       <c r="R71" t="n">
-        <v>7026528</v>
+        <v>7026570</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9911,22 +9875,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9940,7 +9904,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9955,7 +9919,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9966,17 +9930,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121132926</v>
+        <v>121132935</v>
       </c>
       <c r="B72" t="n">
-        <v>56563</v>
+        <v>78604</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9985,25 +9949,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10013,10 +9977,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>446305</v>
+        <v>446246</v>
       </c>
       <c r="R72" t="n">
-        <v>7026607</v>
+        <v>7026518</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10051,11 +10015,6 @@
           <t>2024-03-03</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>uppflog</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -10067,7 +10026,22 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10085,10 +10059,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121134877</v>
+        <v>121134869</v>
       </c>
       <c r="B73" t="n">
-        <v>77538</v>
+        <v>90709</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10101,21 +10075,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10125,10 +10099,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>446271</v>
+        <v>446262</v>
       </c>
       <c r="R73" t="n">
-        <v>7026473</v>
+        <v>7026488</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10160,7 +10134,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10170,7 +10144,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10199,7 +10173,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10217,10 +10191,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121134867</v>
+        <v>121134852</v>
       </c>
       <c r="B74" t="n">
-        <v>77538</v>
+        <v>90723</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10233,21 +10207,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228579</v>
+        <v>1204</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10257,10 +10231,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>446244</v>
+        <v>445963</v>
       </c>
       <c r="R74" t="n">
-        <v>7026516</v>
+        <v>7026504</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10292,7 +10266,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10302,7 +10276,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10316,7 +10290,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -10331,7 +10305,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10349,10 +10323,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121134849</v>
+        <v>121134549</v>
       </c>
       <c r="B75" t="n">
-        <v>91137</v>
+        <v>74710</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10361,25 +10335,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10389,10 +10363,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445948</v>
+        <v>445936</v>
       </c>
       <c r="R75" t="n">
-        <v>7026487</v>
+        <v>7026522</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10419,22 +10393,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10448,7 +10422,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -10463,7 +10437,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>På grov granlåga # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10474,17 +10448,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121134550</v>
+        <v>121132928</v>
       </c>
       <c r="B76" t="n">
-        <v>90468</v>
+        <v>78604</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10493,38 +10467,47 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3215</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445911</v>
+        <v>446290</v>
       </c>
       <c r="R76" t="n">
-        <v>7026564</v>
+        <v>7026577</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10551,22 +10534,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>20 bålar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10580,12 +10558,22 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog, sumpskog/myr</t>
+          <t>i gammal gles barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10596,17 +10584,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121134850</v>
+        <v>121134537</v>
       </c>
       <c r="B77" t="n">
-        <v>91630</v>
+        <v>74694</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10619,21 +10607,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4769</v>
+        <v>6439</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10643,10 +10631,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445960</v>
+        <v>446153</v>
       </c>
       <c r="R77" t="n">
-        <v>7026492</v>
+        <v>7026500</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10673,22 +10661,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10702,12 +10690,22 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På björkhögstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10718,17 +10716,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121134853</v>
+        <v>121134867</v>
       </c>
       <c r="B78" t="n">
-        <v>74699</v>
+        <v>77541</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10737,25 +10735,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>492</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10765,10 +10763,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445965</v>
+        <v>446244</v>
       </c>
       <c r="R78" t="n">
-        <v>7026512</v>
+        <v>7026516</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10800,7 +10798,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10810,7 +10808,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10824,7 +10822,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -10839,7 +10837,7 @@
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10857,10 +10855,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121134558</v>
+        <v>121132934</v>
       </c>
       <c r="B79" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10897,10 +10895,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>446050</v>
+        <v>446253</v>
       </c>
       <c r="R79" t="n">
-        <v>7026501</v>
+        <v>7026514</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10927,22 +10925,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10956,7 +10944,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>I gles gammal gransumpskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -10971,7 +10959,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10982,17 +10970,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121134551</v>
+        <v>121132927</v>
       </c>
       <c r="B80" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11029,10 +11017,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445899</v>
+        <v>446305</v>
       </c>
       <c r="R80" t="n">
-        <v>7026589</v>
+        <v>7026607</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11059,22 +11047,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>60 cm lång bål</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11088,22 +11071,22 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11114,17 +11097,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121132935</v>
+        <v>121132948</v>
       </c>
       <c r="B81" t="n">
-        <v>78601</v>
+        <v>77541</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11137,21 +11120,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11161,10 +11144,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>446246</v>
+        <v>446111</v>
       </c>
       <c r="R81" t="n">
-        <v>7026518</v>
+        <v>7026483</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11210,7 +11193,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -11225,7 +11208,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11243,10 +11226,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121134862</v>
+        <v>121134542</v>
       </c>
       <c r="B82" t="n">
-        <v>74708</v>
+        <v>95641</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11259,21 +11242,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11283,10 +11266,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>446197</v>
+        <v>446080</v>
       </c>
       <c r="R82" t="n">
-        <v>7026538</v>
+        <v>7026521</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11313,22 +11296,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11342,7 +11325,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -11357,7 +11340,7 @@
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På mycket gammal granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11368,17 +11351,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121134857</v>
+        <v>121132945</v>
       </c>
       <c r="B83" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11391,21 +11374,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -11415,10 +11398,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>446075</v>
+        <v>446220</v>
       </c>
       <c r="R83" t="n">
-        <v>7026515</v>
+        <v>7026528</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11445,22 +11428,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11474,7 +11447,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -11489,7 +11462,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>på gammal dubbelgran # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11507,10 +11480,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121132943</v>
+        <v>121134539</v>
       </c>
       <c r="B84" t="n">
-        <v>74708</v>
+        <v>74715</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11523,21 +11496,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11547,10 +11520,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>446259</v>
+        <v>446088</v>
       </c>
       <c r="R84" t="n">
-        <v>7026469</v>
+        <v>7026528</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11577,12 +11550,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11596,7 +11579,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11611,7 +11594,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11622,17 +11605,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121134878</v>
+        <v>121134558</v>
       </c>
       <c r="B85" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11662,26 +11645,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>446262</v>
+        <v>446050</v>
       </c>
       <c r="R85" t="n">
-        <v>7026436</v>
+        <v>7026501</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11708,22 +11682,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11737,7 +11711,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gles gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
@@ -11752,7 +11726,7 @@
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11763,17 +11737,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121132934</v>
+        <v>121134871</v>
       </c>
       <c r="B86" t="n">
-        <v>78601</v>
+        <v>74522</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11782,25 +11756,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11810,10 +11784,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>446253</v>
+        <v>446269</v>
       </c>
       <c r="R86" t="n">
-        <v>7026514</v>
+        <v>7026478</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11840,12 +11814,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11859,7 +11843,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -11874,7 +11858,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11892,10 +11876,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121132932</v>
+        <v>121132930</v>
       </c>
       <c r="B87" t="n">
-        <v>78601</v>
+        <v>77541</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11908,21 +11892,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -12014,10 +11998,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121132948</v>
+        <v>121134853</v>
       </c>
       <c r="B88" t="n">
-        <v>77538</v>
+        <v>74701</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12026,25 +12010,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228579</v>
+        <v>492</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -12054,10 +12038,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>446111</v>
+        <v>445965</v>
       </c>
       <c r="R88" t="n">
-        <v>7026483</v>
+        <v>7026512</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12084,12 +12068,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12103,7 +12097,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -12118,7 +12112,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12136,10 +12130,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121134542</v>
+        <v>121134540</v>
       </c>
       <c r="B89" t="n">
-        <v>95628</v>
+        <v>74696</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12148,25 +12142,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12176,10 +12170,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>446080</v>
+        <v>446088</v>
       </c>
       <c r="R89" t="n">
-        <v>7026521</v>
+        <v>7026528</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12211,7 +12205,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -12221,7 +12215,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12230,12 +12224,13 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -12250,7 +12245,7 @@
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>På mycket gammal granlåga # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12268,10 +12263,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121132944</v>
+        <v>121134864</v>
       </c>
       <c r="B90" t="n">
-        <v>78601</v>
+        <v>74710</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12284,21 +12279,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12308,10 +12303,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>446279</v>
+        <v>446203</v>
       </c>
       <c r="R90" t="n">
-        <v>7026455</v>
+        <v>7026536</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12338,17 +12333,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>40 cm lång bål</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12362,22 +12362,22 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12395,10 +12395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252815</v>
+        <v>121252817</v>
       </c>
       <c r="B91" t="n">
-        <v>57504</v>
+        <v>74694</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12407,47 +12407,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>446189</v>
+        <v>446209</v>
       </c>
       <c r="R91" t="n">
-        <v>7026651</v>
+        <v>7026630</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12504,6 +12495,21 @@
       <c r="AI91" t="inlineStr">
         <is>
           <t>I gammal gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12521,10 +12527,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252837</v>
+        <v>121252838</v>
       </c>
       <c r="B92" t="n">
-        <v>77538</v>
+        <v>74710</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12537,21 +12543,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12596,7 +12602,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12606,7 +12612,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12653,10 +12659,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252827</v>
+        <v>121252822</v>
       </c>
       <c r="B93" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12693,10 +12699,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>446252</v>
+        <v>446284</v>
       </c>
       <c r="R93" t="n">
-        <v>7026536</v>
+        <v>7026552</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12728,7 +12734,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12738,7 +12744,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12767,7 +12773,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12785,10 +12791,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121252803</v>
+        <v>121252827</v>
       </c>
       <c r="B94" t="n">
-        <v>105171</v>
+        <v>78604</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12797,25 +12803,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12825,10 +12831,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>446013</v>
+        <v>446252</v>
       </c>
       <c r="R94" t="n">
-        <v>7026516</v>
+        <v>7026536</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12860,7 +12866,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12870,7 +12876,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12884,12 +12890,22 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12907,10 +12923,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252821</v>
+        <v>121252840</v>
       </c>
       <c r="B95" t="n">
-        <v>78601</v>
+        <v>77541</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12923,21 +12939,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12947,10 +12963,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>446282</v>
+        <v>446209</v>
       </c>
       <c r="R95" t="n">
-        <v>7026592</v>
+        <v>7026394</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12982,7 +12998,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12992,7 +13008,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13006,7 +13022,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -13021,7 +13037,7 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13039,10 +13055,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252808</v>
+        <v>121252824</v>
       </c>
       <c r="B96" t="n">
-        <v>78635</v>
+        <v>77541</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13055,43 +13071,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>228579</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446038</v>
+        <v>446278</v>
       </c>
       <c r="R96" t="n">
-        <v>7026546</v>
+        <v>7026536</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13123,7 +13130,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13133,7 +13140,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13147,7 +13154,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -13162,7 +13169,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13180,10 +13187,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252800</v>
+        <v>121252818</v>
       </c>
       <c r="B97" t="n">
-        <v>57351</v>
+        <v>74522</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13192,43 +13199,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446056</v>
+        <v>446209</v>
       </c>
       <c r="R97" t="n">
-        <v>7026521</v>
+        <v>7026630</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13260,7 +13262,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13270,12 +13272,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13289,12 +13286,22 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13312,10 +13319,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252824</v>
+        <v>121252821</v>
       </c>
       <c r="B98" t="n">
-        <v>77538</v>
+        <v>78604</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13328,21 +13335,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13352,10 +13359,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446278</v>
+        <v>446282</v>
       </c>
       <c r="R98" t="n">
-        <v>7026536</v>
+        <v>7026592</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13387,7 +13394,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13397,7 +13404,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13426,7 +13433,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13444,10 +13451,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121252813</v>
+        <v>121252809</v>
       </c>
       <c r="B99" t="n">
-        <v>78601</v>
+        <v>77541</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13460,21 +13467,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -13484,10 +13491,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>446166</v>
+        <v>446044</v>
       </c>
       <c r="R99" t="n">
-        <v>7026698</v>
+        <v>7026549</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13519,7 +13526,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13529,7 +13536,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13543,7 +13550,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -13558,7 +13565,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13576,10 +13583,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121252810</v>
+        <v>121252803</v>
       </c>
       <c r="B100" t="n">
-        <v>74694</v>
+        <v>105184</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13592,21 +13599,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>306</v>
+        <v>221725</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13616,10 +13623,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>446089</v>
+        <v>446013</v>
       </c>
       <c r="R100" t="n">
-        <v>7026536</v>
+        <v>7026516</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13651,7 +13658,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13661,7 +13668,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13670,7 +13677,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -13679,19 +13685,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13709,10 +13705,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252814</v>
+        <v>121252826</v>
       </c>
       <c r="B101" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13749,10 +13745,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>446185</v>
+        <v>446279</v>
       </c>
       <c r="R101" t="n">
-        <v>7026627</v>
+        <v>7026520</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13784,7 +13780,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13794,7 +13790,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13808,7 +13804,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13823,7 +13819,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13841,10 +13837,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121252818</v>
+        <v>121252823</v>
       </c>
       <c r="B102" t="n">
-        <v>74520</v>
+        <v>78604</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13853,25 +13849,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13881,10 +13877,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>446209</v>
+        <v>446274</v>
       </c>
       <c r="R102" t="n">
-        <v>7026630</v>
+        <v>7026540</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13916,7 +13912,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13926,7 +13922,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13940,7 +13936,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13955,7 +13951,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13973,10 +13969,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252811</v>
+        <v>121252812</v>
       </c>
       <c r="B103" t="n">
-        <v>90693</v>
+        <v>78604</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13989,21 +13985,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -14013,10 +14009,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>446106</v>
+        <v>446185</v>
       </c>
       <c r="R103" t="n">
-        <v>7026528</v>
+        <v>7026655</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -14048,7 +14044,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14058,7 +14054,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14072,7 +14068,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -14087,7 +14083,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14105,10 +14101,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121252839</v>
+        <v>121252836</v>
       </c>
       <c r="B104" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14121,21 +14117,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -14145,10 +14141,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>446209</v>
+        <v>446201</v>
       </c>
       <c r="R104" t="n">
-        <v>7026395</v>
+        <v>7026410</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14180,7 +14176,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14190,7 +14186,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14204,7 +14200,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -14219,7 +14215,7 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14237,10 +14233,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252822</v>
+        <v>121252833</v>
       </c>
       <c r="B105" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14270,17 +14266,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>446284</v>
+        <v>446233</v>
       </c>
       <c r="R105" t="n">
-        <v>7026552</v>
+        <v>7026512</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14312,7 +14317,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14322,7 +14327,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14351,7 +14361,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14369,10 +14379,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121252801</v>
+        <v>121252825</v>
       </c>
       <c r="B106" t="n">
-        <v>91380</v>
+        <v>78860</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14385,21 +14395,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3298</v>
+        <v>6459</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -14409,10 +14419,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445969</v>
+        <v>446278</v>
       </c>
       <c r="R106" t="n">
-        <v>7026495</v>
+        <v>7026536</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14444,7 +14454,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14454,7 +14464,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14468,7 +14478,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -14483,7 +14493,7 @@
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14501,10 +14511,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121252826</v>
+        <v>121252811</v>
       </c>
       <c r="B107" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14517,21 +14527,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -14541,10 +14551,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>446279</v>
+        <v>446106</v>
       </c>
       <c r="R107" t="n">
-        <v>7026520</v>
+        <v>7026528</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14576,7 +14586,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14586,7 +14596,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14600,7 +14610,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>i gammal granskog</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -14615,7 +14625,7 @@
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14633,10 +14643,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252807</v>
+        <v>121252802</v>
       </c>
       <c r="B108" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14649,21 +14659,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14673,10 +14683,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>446038</v>
+        <v>445982</v>
       </c>
       <c r="R108" t="n">
-        <v>7026546</v>
+        <v>7026514</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14708,7 +14718,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14718,7 +14728,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14732,7 +14742,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -14747,7 +14757,7 @@
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14765,10 +14775,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252820</v>
+        <v>121252839</v>
       </c>
       <c r="B109" t="n">
-        <v>74708</v>
+        <v>90727</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14781,21 +14791,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14805,10 +14815,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446258</v>
+        <v>446209</v>
       </c>
       <c r="R109" t="n">
-        <v>7026597</v>
+        <v>7026395</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14840,7 +14850,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14850,7 +14860,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14864,7 +14874,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -14879,7 +14889,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14897,10 +14907,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252802</v>
+        <v>121252804</v>
       </c>
       <c r="B110" t="n">
-        <v>90693</v>
+        <v>97107</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14909,25 +14919,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1108</v>
+        <v>221063</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -14937,7 +14947,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445982</v>
+        <v>446013</v>
       </c>
       <c r="R110" t="n">
         <v>7026514</v>
@@ -14972,7 +14982,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14982,7 +14992,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14999,19 +15009,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15029,10 +15029,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252819</v>
+        <v>121252813</v>
       </c>
       <c r="B111" t="n">
-        <v>77538</v>
+        <v>78604</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15045,21 +15045,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -15069,10 +15069,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446258</v>
+        <v>446166</v>
       </c>
       <c r="R111" t="n">
-        <v>7026597</v>
+        <v>7026698</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15161,10 +15161,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121252823</v>
+        <v>121252808</v>
       </c>
       <c r="B112" t="n">
-        <v>78601</v>
+        <v>78638</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15177,34 +15177,43 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>446274</v>
+        <v>446038</v>
       </c>
       <c r="R112" t="n">
-        <v>7026540</v>
+        <v>7026546</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15236,7 +15245,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -15246,7 +15255,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15260,7 +15269,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -15275,7 +15284,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15293,10 +15302,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121252835</v>
+        <v>121252807</v>
       </c>
       <c r="B113" t="n">
-        <v>77985</v>
+        <v>78604</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15309,21 +15318,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -15333,10 +15342,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>446209</v>
+        <v>446038</v>
       </c>
       <c r="R113" t="n">
-        <v>7026444</v>
+        <v>7026546</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15368,7 +15377,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -15378,7 +15387,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15392,22 +15401,22 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>I gammal sumpskog/myr</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15425,10 +15434,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121252836</v>
+        <v>121252815</v>
       </c>
       <c r="B114" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -15441,34 +15450,43 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>446201</v>
+        <v>446189</v>
       </c>
       <c r="R114" t="n">
-        <v>7026410</v>
+        <v>7026651</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15500,7 +15518,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -15510,7 +15528,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15524,22 +15542,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15557,10 +15560,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252809</v>
+        <v>121252830</v>
       </c>
       <c r="B115" t="n">
-        <v>77538</v>
+        <v>74710</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15573,21 +15576,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15597,10 +15600,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446044</v>
+        <v>446252</v>
       </c>
       <c r="R115" t="n">
-        <v>7026549</v>
+        <v>7026536</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15632,7 +15635,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15642,7 +15645,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15656,7 +15659,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -15671,7 +15674,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15689,10 +15692,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252840</v>
+        <v>121252837</v>
       </c>
       <c r="B116" t="n">
-        <v>77538</v>
+        <v>77541</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15729,10 +15732,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446209</v>
+        <v>446201</v>
       </c>
       <c r="R116" t="n">
-        <v>7026394</v>
+        <v>7026410</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15764,7 +15767,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15774,7 +15777,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15788,7 +15791,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -15803,7 +15806,7 @@
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15821,10 +15824,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252838</v>
+        <v>121252835</v>
       </c>
       <c r="B117" t="n">
-        <v>74708</v>
+        <v>77988</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15837,21 +15840,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15861,10 +15864,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446201</v>
+        <v>446209</v>
       </c>
       <c r="R117" t="n">
-        <v>7026410</v>
+        <v>7026444</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15896,7 +15899,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15906,7 +15909,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15920,22 +15923,22 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal sumpskog/myr</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15953,10 +15956,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252830</v>
+        <v>121252819</v>
       </c>
       <c r="B118" t="n">
-        <v>74708</v>
+        <v>77541</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15969,21 +15972,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15993,10 +15996,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446252</v>
+        <v>446258</v>
       </c>
       <c r="R118" t="n">
-        <v>7026536</v>
+        <v>7026597</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16028,7 +16031,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16038,7 +16041,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16052,7 +16055,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -16067,7 +16070,7 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16085,10 +16088,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252825</v>
+        <v>121252814</v>
       </c>
       <c r="B119" t="n">
-        <v>78857</v>
+        <v>78604</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16097,25 +16100,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -16125,10 +16128,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446278</v>
+        <v>446185</v>
       </c>
       <c r="R119" t="n">
-        <v>7026536</v>
+        <v>7026627</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16160,7 +16163,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16170,7 +16173,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16184,7 +16187,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -16199,7 +16202,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16217,10 +16220,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121252806</v>
+        <v>121252820</v>
       </c>
       <c r="B120" t="n">
-        <v>74520</v>
+        <v>74710</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16229,25 +16232,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6428</v>
+        <v>6440</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -16257,10 +16260,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446038</v>
+        <v>446258</v>
       </c>
       <c r="R120" t="n">
-        <v>7026546</v>
+        <v>7026597</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16292,7 +16295,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -16302,7 +16305,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16316,7 +16319,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -16331,7 +16334,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16349,10 +16352,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121252833</v>
+        <v>121252801</v>
       </c>
       <c r="B121" t="n">
-        <v>78601</v>
+        <v>91392</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -16361,47 +16364,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>446233</v>
+        <v>445969</v>
       </c>
       <c r="R121" t="n">
-        <v>7026512</v>
+        <v>7026495</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16433,7 +16427,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -16443,12 +16437,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16462,7 +16451,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -16477,7 +16466,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16495,10 +16484,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252812</v>
+        <v>121252810</v>
       </c>
       <c r="B122" t="n">
-        <v>78601</v>
+        <v>74696</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -16507,25 +16496,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -16535,10 +16524,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446185</v>
+        <v>446089</v>
       </c>
       <c r="R122" t="n">
-        <v>7026655</v>
+        <v>7026536</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16570,7 +16559,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16580,7 +16569,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16589,12 +16578,13 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -16609,7 +16599,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16627,10 +16617,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252817</v>
+        <v>121252806</v>
       </c>
       <c r="B123" t="n">
-        <v>74692</v>
+        <v>74522</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16643,21 +16633,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6439</v>
+        <v>6428</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16667,10 +16657,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446209</v>
+        <v>446038</v>
       </c>
       <c r="R123" t="n">
-        <v>7026630</v>
+        <v>7026546</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16702,7 +16692,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16712,7 +16702,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16726,7 +16716,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -16741,7 +16731,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -16759,10 +16749,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252804</v>
+        <v>121252800</v>
       </c>
       <c r="B124" t="n">
-        <v>97094</v>
+        <v>57351</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16771,38 +16761,43 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221063</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>446013</v>
+        <v>446056</v>
       </c>
       <c r="R124" t="n">
-        <v>7026514</v>
+        <v>7026521</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16834,7 +16829,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16844,7 +16839,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3551,7 +3551,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121117416</v>
+        <v>121117887</v>
       </c>
       <c r="B23" t="n">
         <v>78604</v>
@@ -3584,26 +3584,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svedaun, Svedaun, Jmt</t>
+          <t>Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445930</v>
+        <v>446262</v>
       </c>
       <c r="R23" t="n">
-        <v>7026585</v>
+        <v>7026371</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3635,7 +3626,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3645,12 +3636,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 20, långa Gammal gran</t>
+          <t>1 stor garnlav</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3677,7 +3668,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121117887</v>
+        <v>121117416</v>
       </c>
       <c r="B24" t="n">
         <v>78604</v>
@@ -3710,17 +3701,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svedaunsmyren, Jmt</t>
+          <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446262</v>
+        <v>445930</v>
       </c>
       <c r="R24" t="n">
-        <v>7026371</v>
+        <v>7026585</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1 stor garnlav</t>
+          <t>Minst 20, långa Gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3908,17 +3908,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121117375</v>
+        <v>121117063</v>
       </c>
       <c r="B26" t="n">
-        <v>77541</v>
+        <v>78604</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3931,34 +3931,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svedaun, Svedaun, Jmt</t>
+          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445930</v>
+        <v>446063</v>
       </c>
       <c r="R26" t="n">
-        <v>7026568</v>
+        <v>7026497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3990,7 +3999,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4000,7 +4009,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4032,10 +4041,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121117063</v>
+        <v>121117375</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
+        <v>77541</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4048,43 +4057,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
+          <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446063</v>
+        <v>445930</v>
       </c>
       <c r="R27" t="n">
-        <v>7026497</v>
+        <v>7026568</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121134548</v>
+        <v>121134867</v>
       </c>
       <c r="B28" t="n">
-        <v>88031</v>
+        <v>77541</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445938</v>
+        <v>446244</v>
       </c>
       <c r="R28" t="n">
-        <v>7026514</v>
+        <v>7026516</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4228,22 +4228,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4283,17 +4283,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121134851</v>
+        <v>121134857</v>
       </c>
       <c r="B29" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445959</v>
+        <v>446075</v>
       </c>
       <c r="R29" t="n">
-        <v>7026504</v>
+        <v>7026515</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121134555</v>
+        <v>121134546</v>
       </c>
       <c r="B30" t="n">
-        <v>90674</v>
+        <v>77541</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4434,25 +4434,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4462,10 +4462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446030</v>
+        <v>445987</v>
       </c>
       <c r="R30" t="n">
-        <v>7026523</v>
+        <v>7026512</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4554,10 +4554,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121134543</v>
+        <v>121132934</v>
       </c>
       <c r="B31" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4566,47 +4566,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446069</v>
+        <v>446253</v>
       </c>
       <c r="R31" t="n">
-        <v>7026527</v>
+        <v>7026514</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4633,27 +4624,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4667,12 +4643,22 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4683,17 +4669,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121132931</v>
+        <v>121132948</v>
       </c>
       <c r="B32" t="n">
-        <v>74710</v>
+        <v>77541</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4706,21 +4692,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4730,10 +4716,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446284</v>
+        <v>446111</v>
       </c>
       <c r="R32" t="n">
-        <v>7026556</v>
+        <v>7026483</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4779,7 +4765,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4794,7 +4780,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4812,10 +4798,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121132943</v>
+        <v>121134542</v>
       </c>
       <c r="B33" t="n">
-        <v>74710</v>
+        <v>95642</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4828,21 +4814,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4852,10 +4838,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446259</v>
+        <v>446080</v>
       </c>
       <c r="R33" t="n">
-        <v>7026469</v>
+        <v>7026521</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4882,12 +4868,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4901,7 +4897,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4916,7 +4912,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
+          <t>På mycket gammal granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4927,17 +4923,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121134556</v>
+        <v>121134863</v>
       </c>
       <c r="B34" t="n">
-        <v>74715</v>
+        <v>78604</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4950,21 +4946,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4974,10 +4970,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446026</v>
+        <v>446203</v>
       </c>
       <c r="R34" t="n">
-        <v>7026520</v>
+        <v>7026536</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5004,22 +5000,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5033,22 +5029,22 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5059,17 +5055,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121132936</v>
+        <v>121134859</v>
       </c>
       <c r="B35" t="n">
-        <v>77541</v>
+        <v>74710</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5082,21 +5078,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5106,10 +5102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446254</v>
+        <v>446158</v>
       </c>
       <c r="R35" t="n">
-        <v>7026486</v>
+        <v>7026570</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5136,12 +5132,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5155,7 +5161,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5170,7 +5176,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5188,7 +5194,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121132949</v>
+        <v>121134855</v>
       </c>
       <c r="B36" t="n">
         <v>78604</v>
@@ -5221,26 +5227,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446118</v>
+        <v>446045</v>
       </c>
       <c r="R36" t="n">
-        <v>7026441</v>
+        <v>7026526</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5267,17 +5264,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>7 bålar</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5291,7 +5293,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5306,7 +5308,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5324,7 +5326,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121132944</v>
+        <v>121134865</v>
       </c>
       <c r="B37" t="n">
         <v>78604</v>
@@ -5357,17 +5359,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446279</v>
+        <v>446213</v>
       </c>
       <c r="R37" t="n">
-        <v>7026455</v>
+        <v>7026555</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5394,17 +5405,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>40 cm lång bål</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5418,22 +5434,22 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
+          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5451,10 +5467,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121134862</v>
+        <v>121134853</v>
       </c>
       <c r="B38" t="n">
-        <v>74710</v>
+        <v>74701</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5463,25 +5479,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5491,10 +5507,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446197</v>
+        <v>445965</v>
       </c>
       <c r="R38" t="n">
-        <v>7026538</v>
+        <v>7026512</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5526,7 +5542,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5536,7 +5552,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5550,7 +5566,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5565,7 +5581,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5583,10 +5599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121134880</v>
+        <v>121134873</v>
       </c>
       <c r="B39" t="n">
-        <v>56563</v>
+        <v>77541</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5595,47 +5611,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446259</v>
+        <v>446269</v>
       </c>
       <c r="R39" t="n">
-        <v>7026406</v>
+        <v>7026478</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5667,7 +5674,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5677,12 +5684,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Satt i gammal gran</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5696,7 +5698,22 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5714,10 +5731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121132926</v>
+        <v>121134555</v>
       </c>
       <c r="B40" t="n">
-        <v>56563</v>
+        <v>90675</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5730,21 +5747,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5754,10 +5771,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446305</v>
+        <v>446030</v>
       </c>
       <c r="R40" t="n">
-        <v>7026607</v>
+        <v>7026523</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5784,17 +5801,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>uppflog</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5808,7 +5830,22 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5819,17 +5856,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121134535</v>
+        <v>121134877</v>
       </c>
       <c r="B41" t="n">
-        <v>78767</v>
+        <v>77541</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5838,47 +5875,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446119</v>
+        <v>446271</v>
       </c>
       <c r="R41" t="n">
-        <v>7026442</v>
+        <v>7026473</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5905,27 +5933,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:41</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Samma som sedd tidigare i år</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5939,7 +5962,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5954,7 +5977,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5965,17 +5988,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121134875</v>
+        <v>121134540</v>
       </c>
       <c r="B42" t="n">
-        <v>74710</v>
+        <v>74696</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5984,25 +6007,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6012,10 +6035,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446269</v>
+        <v>446088</v>
       </c>
       <c r="R42" t="n">
-        <v>7026478</v>
+        <v>7026528</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6042,22 +6065,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6066,12 +6089,13 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -6086,7 +6110,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6097,17 +6121,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121134536</v>
+        <v>121134864</v>
       </c>
       <c r="B43" t="n">
-        <v>90705</v>
+        <v>74710</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6120,21 +6144,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6144,10 +6168,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446164</v>
+        <v>446203</v>
       </c>
       <c r="R43" t="n">
-        <v>7026463</v>
+        <v>7026536</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6174,22 +6198,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6203,7 +6227,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6218,7 +6242,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>På död gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6229,17 +6253,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121134849</v>
+        <v>121134880</v>
       </c>
       <c r="B44" t="n">
-        <v>91149</v>
+        <v>56563</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6248,38 +6272,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445948</v>
+        <v>446259</v>
       </c>
       <c r="R44" t="n">
-        <v>7026487</v>
+        <v>7026406</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6311,7 +6344,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6321,7 +6354,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Satt i gammal gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6335,22 +6373,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>På grov granlåga # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6368,10 +6391,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121134545</v>
+        <v>121132945</v>
       </c>
       <c r="B45" t="n">
-        <v>78604</v>
+        <v>90728</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6384,43 +6407,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445987</v>
+        <v>446220</v>
       </c>
       <c r="R45" t="n">
-        <v>7026510</v>
+        <v>7026528</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6447,27 +6461,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>10 bålar, den längsta 30 cm</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6481,7 +6480,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6496,7 +6495,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>på gammal dubbelgran # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6507,7 +6506,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6646,10 +6645,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121134858</v>
+        <v>121134852</v>
       </c>
       <c r="B47" t="n">
-        <v>90727</v>
+        <v>90724</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6662,21 +6661,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6686,10 +6685,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>446092</v>
+        <v>445963</v>
       </c>
       <c r="R47" t="n">
-        <v>7026520</v>
+        <v>7026504</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6721,7 +6720,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6731,7 +6730,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6745,7 +6744,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6760,7 +6759,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6778,10 +6777,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121134544</v>
+        <v>121132930</v>
       </c>
       <c r="B48" t="n">
-        <v>90709</v>
+        <v>77541</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6794,21 +6793,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6818,10 +6817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>446005</v>
+        <v>446284</v>
       </c>
       <c r="R48" t="n">
-        <v>7026502</v>
+        <v>7026556</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6848,22 +6847,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6877,7 +6866,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6892,7 +6881,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6903,17 +6892,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121134866</v>
+        <v>121134860</v>
       </c>
       <c r="B49" t="n">
-        <v>90727</v>
+        <v>78604</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6926,34 +6915,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446218</v>
+        <v>446170</v>
       </c>
       <c r="R49" t="n">
-        <v>7026544</v>
+        <v>7026558</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6985,7 +6983,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6995,7 +6993,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7024,7 +7022,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7042,7 +7040,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121134868</v>
+        <v>121132949</v>
       </c>
       <c r="B50" t="n">
         <v>78604</v>
@@ -7075,17 +7073,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446262</v>
+        <v>446118</v>
       </c>
       <c r="R50" t="n">
-        <v>7026488</v>
+        <v>7026441</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7112,22 +7119,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>7 bålar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7141,7 +7143,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7156,7 +7158,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7174,7 +7176,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121134860</v>
+        <v>121134868</v>
       </c>
       <c r="B51" t="n">
         <v>78604</v>
@@ -7207,26 +7209,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446170</v>
+        <v>446262</v>
       </c>
       <c r="R51" t="n">
-        <v>7026558</v>
+        <v>7026488</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7258,7 +7251,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7268,7 +7261,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7282,7 +7275,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7297,7 +7290,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7315,10 +7308,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121134855</v>
+        <v>121134535</v>
       </c>
       <c r="B52" t="n">
-        <v>78604</v>
+        <v>78767</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7327,38 +7320,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446045</v>
+        <v>446119</v>
       </c>
       <c r="R52" t="n">
-        <v>7026526</v>
+        <v>7026442</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7385,22 +7387,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Samma som sedd tidigare i år</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7414,7 +7421,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -7429,7 +7436,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7440,17 +7447,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121134552</v>
+        <v>121134556</v>
       </c>
       <c r="B53" t="n">
-        <v>77541</v>
+        <v>74715</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7463,21 +7470,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>1467</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7487,10 +7494,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445924</v>
+        <v>446026</v>
       </c>
       <c r="R53" t="n">
-        <v>7026587</v>
+        <v>7026520</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7522,7 +7529,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7532,7 +7539,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7546,22 +7553,22 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7579,10 +7586,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121134850</v>
+        <v>121134849</v>
       </c>
       <c r="B54" t="n">
-        <v>91642</v>
+        <v>91150</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7591,25 +7598,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7619,10 +7626,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445960</v>
+        <v>445948</v>
       </c>
       <c r="R54" t="n">
-        <v>7026492</v>
+        <v>7026487</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7654,7 +7661,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7664,7 +7671,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7681,9 +7688,19 @@
           <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På grov granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7701,10 +7718,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121134551</v>
+        <v>121134862</v>
       </c>
       <c r="B55" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7717,21 +7734,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7741,10 +7758,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445899</v>
+        <v>446197</v>
       </c>
       <c r="R55" t="n">
-        <v>7026589</v>
+        <v>7026538</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7771,22 +7788,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7800,7 +7817,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -7815,7 +7832,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7826,17 +7843,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121134873</v>
+        <v>121134541</v>
       </c>
       <c r="B56" t="n">
-        <v>77541</v>
+        <v>74702</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7849,21 +7866,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7873,10 +7890,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446269</v>
+        <v>446088</v>
       </c>
       <c r="R56" t="n">
-        <v>7026478</v>
+        <v>7026528</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7903,22 +7920,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7932,7 +7949,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -7947,7 +7964,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7958,17 +7975,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121134878</v>
+        <v>121132943</v>
       </c>
       <c r="B57" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7981,43 +7998,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446262</v>
+        <v>446259</v>
       </c>
       <c r="R57" t="n">
-        <v>7026436</v>
+        <v>7026469</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8044,22 +8052,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8073,7 +8071,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -8088,7 +8086,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8106,7 +8104,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121134877</v>
+        <v>121132936</v>
       </c>
       <c r="B58" t="n">
         <v>77541</v>
@@ -8146,10 +8144,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446271</v>
+        <v>446254</v>
       </c>
       <c r="R58" t="n">
-        <v>7026473</v>
+        <v>7026486</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8176,22 +8174,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8205,7 +8193,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -8220,7 +8208,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8238,10 +8226,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121134863</v>
+        <v>121134858</v>
       </c>
       <c r="B59" t="n">
-        <v>78604</v>
+        <v>90728</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8254,21 +8242,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8278,10 +8266,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446203</v>
+        <v>446092</v>
       </c>
       <c r="R59" t="n">
-        <v>7026536</v>
+        <v>7026520</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8313,7 +8301,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8323,7 +8311,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8352,7 +8340,7 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8370,10 +8358,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121134857</v>
+        <v>121134549</v>
       </c>
       <c r="B60" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8386,21 +8374,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8410,10 +8398,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446075</v>
+        <v>445936</v>
       </c>
       <c r="R60" t="n">
-        <v>7026515</v>
+        <v>7026522</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8440,22 +8428,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8469,7 +8457,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8484,7 +8472,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8495,17 +8483,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121134553</v>
+        <v>121132950</v>
       </c>
       <c r="B61" t="n">
-        <v>74710</v>
+        <v>78767</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8514,38 +8502,47 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445925</v>
+        <v>446118</v>
       </c>
       <c r="R61" t="n">
-        <v>7026580</v>
+        <v>7026441</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8572,22 +8569,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>1 bål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8601,7 +8593,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8616,7 +8608,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8627,17 +8619,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121134870</v>
+        <v>121132932</v>
       </c>
       <c r="B62" t="n">
-        <v>91149</v>
+        <v>78604</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8646,25 +8638,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8674,10 +8666,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>446262</v>
+        <v>446284</v>
       </c>
       <c r="R62" t="n">
-        <v>7026488</v>
+        <v>7026556</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8704,22 +8696,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8733,7 +8715,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8748,7 +8730,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8766,10 +8748,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121134557</v>
+        <v>121134851</v>
       </c>
       <c r="B63" t="n">
-        <v>74701</v>
+        <v>90710</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8778,25 +8760,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8806,10 +8788,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>446026</v>
+        <v>445959</v>
       </c>
       <c r="R63" t="n">
-        <v>7026520</v>
+        <v>7026504</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8836,22 +8818,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8865,22 +8847,22 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8891,14 +8873,14 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121132932</v>
+        <v>121132927</v>
       </c>
       <c r="B64" t="n">
         <v>78604</v>
@@ -8938,10 +8920,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>446284</v>
+        <v>446305</v>
       </c>
       <c r="R64" t="n">
-        <v>7026556</v>
+        <v>7026607</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8976,6 +8958,11 @@
           <t>2024-03-03</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>60 cm lång bål</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8987,22 +8974,22 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9020,7 +9007,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121134865</v>
+        <v>121132944</v>
       </c>
       <c r="B65" t="n">
         <v>78604</v>
@@ -9053,26 +9040,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>446213</v>
+        <v>446279</v>
       </c>
       <c r="R65" t="n">
-        <v>7026555</v>
+        <v>7026455</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9099,22 +9077,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>40 cm lång bål</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9128,22 +9101,22 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
+          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9161,10 +9134,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121134546</v>
+        <v>121134875</v>
       </c>
       <c r="B66" t="n">
-        <v>77541</v>
+        <v>74710</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9177,21 +9150,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9201,10 +9174,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445987</v>
+        <v>446269</v>
       </c>
       <c r="R66" t="n">
-        <v>7026512</v>
+        <v>7026478</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9231,22 +9204,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9260,7 +9233,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9275,7 +9248,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9286,17 +9259,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121134538</v>
+        <v>121134552</v>
       </c>
       <c r="B67" t="n">
-        <v>105184</v>
+        <v>77541</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9305,25 +9278,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221725</v>
+        <v>228579</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9333,10 +9306,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>446142</v>
+        <v>445924</v>
       </c>
       <c r="R67" t="n">
-        <v>7026514</v>
+        <v>7026587</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9368,7 +9341,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9378,7 +9351,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9392,12 +9365,22 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9415,10 +9398,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121134541</v>
+        <v>121132926</v>
       </c>
       <c r="B68" t="n">
-        <v>74702</v>
+        <v>56563</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9427,25 +9410,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>308</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9455,10 +9438,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>446088</v>
+        <v>446305</v>
       </c>
       <c r="R68" t="n">
-        <v>7026528</v>
+        <v>7026607</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9485,22 +9468,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>uppflog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9514,22 +9492,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9540,17 +9503,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121132950</v>
+        <v>121134536</v>
       </c>
       <c r="B69" t="n">
-        <v>78767</v>
+        <v>90706</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9559,47 +9522,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1249</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>446118</v>
+        <v>446164</v>
       </c>
       <c r="R69" t="n">
-        <v>7026441</v>
+        <v>7026463</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9626,17 +9580,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>1 bål</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9650,7 +9609,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9665,7 +9624,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9676,17 +9635,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121134550</v>
+        <v>121134869</v>
       </c>
       <c r="B70" t="n">
-        <v>90480</v>
+        <v>90710</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9695,25 +9654,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9723,10 +9682,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445911</v>
+        <v>446262</v>
       </c>
       <c r="R70" t="n">
-        <v>7026564</v>
+        <v>7026488</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9753,22 +9712,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9782,12 +9741,22 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog, sumpskog/myr</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9798,17 +9767,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121134859</v>
+        <v>121134550</v>
       </c>
       <c r="B71" t="n">
-        <v>74710</v>
+        <v>90481</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9817,25 +9786,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>3215</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9845,10 +9814,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>446158</v>
+        <v>445911</v>
       </c>
       <c r="R71" t="n">
-        <v>7026570</v>
+        <v>7026564</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9875,22 +9844,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9904,22 +9873,12 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal barrblandskog, sumpskog/myr</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9930,14 +9889,14 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121132935</v>
+        <v>121134551</v>
       </c>
       <c r="B72" t="n">
         <v>78604</v>
@@ -9977,10 +9936,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>446246</v>
+        <v>445899</v>
       </c>
       <c r="R72" t="n">
-        <v>7026518</v>
+        <v>7026589</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10007,12 +9966,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10026,7 +9995,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -10041,7 +10010,7 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10052,17 +10021,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121134869</v>
+        <v>121134866</v>
       </c>
       <c r="B73" t="n">
-        <v>90709</v>
+        <v>90728</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10075,21 +10044,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10099,10 +10068,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>446262</v>
+        <v>446218</v>
       </c>
       <c r="R73" t="n">
-        <v>7026488</v>
+        <v>7026544</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10134,7 +10103,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10144,7 +10113,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10158,7 +10127,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10173,7 +10142,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10191,10 +10160,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121134852</v>
+        <v>121134878</v>
       </c>
       <c r="B74" t="n">
-        <v>90723</v>
+        <v>78604</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10207,34 +10176,43 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445963</v>
+        <v>446262</v>
       </c>
       <c r="R74" t="n">
-        <v>7026504</v>
+        <v>7026436</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10266,7 +10244,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10276,7 +10254,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10290,7 +10268,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -10305,7 +10283,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10323,10 +10301,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121134549</v>
+        <v>121132935</v>
       </c>
       <c r="B75" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10339,21 +10317,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10363,10 +10341,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445936</v>
+        <v>446246</v>
       </c>
       <c r="R75" t="n">
-        <v>7026522</v>
+        <v>7026518</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10393,22 +10371,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10422,7 +10390,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -10437,7 +10405,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10448,17 +10416,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121132928</v>
+        <v>121134544</v>
       </c>
       <c r="B76" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10471,43 +10439,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>446290</v>
+        <v>446005</v>
       </c>
       <c r="R76" t="n">
-        <v>7026577</v>
+        <v>7026502</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10534,17 +10493,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>20 bålar</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10558,7 +10522,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>i gammal gles barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
@@ -10573,7 +10537,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10584,17 +10548,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121134537</v>
+        <v>121134548</v>
       </c>
       <c r="B77" t="n">
-        <v>74694</v>
+        <v>88031</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10603,25 +10567,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6439</v>
+        <v>510</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10631,10 +10595,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>446153</v>
+        <v>445938</v>
       </c>
       <c r="R77" t="n">
-        <v>7026500</v>
+        <v>7026514</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10666,7 +10630,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10676,7 +10640,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10695,17 +10659,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>På björkhögstubbe # Betula pubescens</t>
+          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10723,10 +10687,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121134867</v>
+        <v>121134539</v>
       </c>
       <c r="B78" t="n">
-        <v>77541</v>
+        <v>74715</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10739,21 +10703,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>1467</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10763,10 +10727,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>446244</v>
+        <v>446088</v>
       </c>
       <c r="R78" t="n">
-        <v>7026516</v>
+        <v>7026528</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10793,22 +10757,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10822,7 +10786,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -10837,7 +10801,7 @@
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10848,17 +10812,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121132934</v>
+        <v>121134850</v>
       </c>
       <c r="B79" t="n">
-        <v>78604</v>
+        <v>91643</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10867,25 +10831,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10895,10 +10859,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>446253</v>
+        <v>445960</v>
       </c>
       <c r="R79" t="n">
-        <v>7026514</v>
+        <v>7026492</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10925,12 +10889,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10944,22 +10918,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10977,10 +10941,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121132927</v>
+        <v>121134543</v>
       </c>
       <c r="B80" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10989,38 +10953,47 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>446305</v>
+        <v>446069</v>
       </c>
       <c r="R80" t="n">
-        <v>7026607</v>
+        <v>7026527</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11047,17 +11020,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>60 cm lång bål</t>
+          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11071,22 +11054,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11097,17 +11070,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121132948</v>
+        <v>121134553</v>
       </c>
       <c r="B81" t="n">
-        <v>77541</v>
+        <v>74710</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11120,21 +11093,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11144,10 +11117,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>446111</v>
+        <v>445925</v>
       </c>
       <c r="R81" t="n">
-        <v>7026483</v>
+        <v>7026580</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11174,12 +11147,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11193,7 +11176,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -11208,7 +11191,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11219,17 +11202,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121134542</v>
+        <v>121134557</v>
       </c>
       <c r="B82" t="n">
-        <v>95641</v>
+        <v>74701</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11238,25 +11221,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>492</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11266,10 +11249,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>446080</v>
+        <v>446026</v>
       </c>
       <c r="R82" t="n">
-        <v>7026521</v>
+        <v>7026520</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11301,7 +11284,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11311,7 +11294,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11325,22 +11308,22 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>På mycket gammal granlåga # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11358,10 +11341,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121132945</v>
+        <v>121134871</v>
       </c>
       <c r="B83" t="n">
-        <v>90727</v>
+        <v>74522</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11370,25 +11353,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6428</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -11398,10 +11381,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>446220</v>
+        <v>446269</v>
       </c>
       <c r="R83" t="n">
-        <v>7026528</v>
+        <v>7026478</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11428,12 +11411,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11447,7 +11440,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -11462,7 +11455,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>på gammal dubbelgran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11480,10 +11473,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121134539</v>
+        <v>121134537</v>
       </c>
       <c r="B84" t="n">
-        <v>74715</v>
+        <v>74694</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11492,25 +11485,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1467</v>
+        <v>6439</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11520,10 +11513,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>446088</v>
+        <v>446153</v>
       </c>
       <c r="R84" t="n">
-        <v>7026528</v>
+        <v>7026500</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11555,7 +11548,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11565,7 +11558,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11584,17 +11577,17 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På björkhögstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11744,10 +11737,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121134871</v>
+        <v>121132928</v>
       </c>
       <c r="B86" t="n">
-        <v>74522</v>
+        <v>78604</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11756,38 +11749,47 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>446269</v>
+        <v>446290</v>
       </c>
       <c r="R86" t="n">
-        <v>7026478</v>
+        <v>7026577</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11814,22 +11816,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>20 bålar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11843,7 +11840,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -11858,7 +11855,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11876,10 +11873,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121132930</v>
+        <v>121132931</v>
       </c>
       <c r="B87" t="n">
-        <v>77541</v>
+        <v>74710</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11892,21 +11889,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11998,10 +11995,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121134853</v>
+        <v>121134538</v>
       </c>
       <c r="B88" t="n">
-        <v>74701</v>
+        <v>105185</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12010,25 +12007,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>492</v>
+        <v>221725</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -12038,10 +12035,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445965</v>
+        <v>446142</v>
       </c>
       <c r="R88" t="n">
-        <v>7026512</v>
+        <v>7026514</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12068,22 +12065,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12097,22 +12094,12 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12123,17 +12110,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121134540</v>
+        <v>121134870</v>
       </c>
       <c r="B89" t="n">
-        <v>74696</v>
+        <v>91150</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12142,25 +12129,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>306</v>
+        <v>1209</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12170,10 +12157,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>446088</v>
+        <v>446262</v>
       </c>
       <c r="R89" t="n">
-        <v>7026528</v>
+        <v>7026488</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12200,22 +12187,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12224,13 +12211,12 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -12245,7 +12231,7 @@
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12256,17 +12242,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121134864</v>
+        <v>121134545</v>
       </c>
       <c r="B90" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12279,34 +12265,43 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>446203</v>
+        <v>445987</v>
       </c>
       <c r="R90" t="n">
-        <v>7026536</v>
+        <v>7026510</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12333,22 +12328,27 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>10 bålar, den längsta 30 cm</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12388,17 +12388,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252817</v>
+        <v>121252824</v>
       </c>
       <c r="B91" t="n">
-        <v>74694</v>
+        <v>77541</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12407,25 +12407,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>446209</v>
+        <v>446278</v>
       </c>
       <c r="R91" t="n">
-        <v>7026630</v>
+        <v>7026536</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12527,10 +12527,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252838</v>
+        <v>121252810</v>
       </c>
       <c r="B92" t="n">
-        <v>74710</v>
+        <v>74696</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12539,25 +12539,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>446201</v>
+        <v>446089</v>
       </c>
       <c r="R92" t="n">
-        <v>7026410</v>
+        <v>7026536</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12621,6 +12621,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -12641,7 +12642,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12659,10 +12660,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252822</v>
+        <v>121252839</v>
       </c>
       <c r="B93" t="n">
-        <v>78604</v>
+        <v>90728</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12675,21 +12676,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12699,10 +12700,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>446284</v>
+        <v>446209</v>
       </c>
       <c r="R93" t="n">
-        <v>7026552</v>
+        <v>7026395</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12734,7 +12735,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12744,7 +12745,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12758,7 +12759,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -12773,7 +12774,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12791,7 +12792,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121252827</v>
+        <v>121252812</v>
       </c>
       <c r="B94" t="n">
         <v>78604</v>
@@ -12831,10 +12832,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>446252</v>
+        <v>446185</v>
       </c>
       <c r="R94" t="n">
-        <v>7026536</v>
+        <v>7026655</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12866,7 +12867,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12876,7 +12877,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12890,7 +12891,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -12905,7 +12906,7 @@
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12923,10 +12924,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252840</v>
+        <v>121252815</v>
       </c>
       <c r="B95" t="n">
-        <v>77541</v>
+        <v>57504</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12939,34 +12940,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>446209</v>
+        <v>446189</v>
       </c>
       <c r="R95" t="n">
-        <v>7026394</v>
+        <v>7026651</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12998,7 +13008,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13008,7 +13018,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13022,22 +13032,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13055,10 +13050,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252824</v>
+        <v>121252808</v>
       </c>
       <c r="B96" t="n">
-        <v>77541</v>
+        <v>78638</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13071,34 +13066,43 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228579</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446278</v>
+        <v>446038</v>
       </c>
       <c r="R96" t="n">
-        <v>7026536</v>
+        <v>7026546</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13130,7 +13134,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13140,7 +13144,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13154,7 +13158,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -13169,7 +13173,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13187,10 +13191,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252818</v>
+        <v>121252809</v>
       </c>
       <c r="B97" t="n">
-        <v>74522</v>
+        <v>77541</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13199,25 +13203,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -13227,10 +13231,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446209</v>
+        <v>446044</v>
       </c>
       <c r="R97" t="n">
-        <v>7026630</v>
+        <v>7026549</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13262,7 +13266,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13272,7 +13276,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13286,7 +13290,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -13301,7 +13305,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13319,10 +13323,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252821</v>
+        <v>121252838</v>
       </c>
       <c r="B98" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13335,21 +13339,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13359,10 +13363,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446282</v>
+        <v>446201</v>
       </c>
       <c r="R98" t="n">
-        <v>7026592</v>
+        <v>7026410</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13394,7 +13398,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13404,7 +13408,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13418,7 +13422,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -13433,7 +13437,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13451,7 +13455,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121252809</v>
+        <v>121252837</v>
       </c>
       <c r="B99" t="n">
         <v>77541</v>
@@ -13491,10 +13495,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>446044</v>
+        <v>446201</v>
       </c>
       <c r="R99" t="n">
-        <v>7026549</v>
+        <v>7026410</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13526,7 +13530,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13536,7 +13540,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13550,7 +13554,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -13565,7 +13569,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13583,10 +13587,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121252803</v>
+        <v>121252835</v>
       </c>
       <c r="B100" t="n">
-        <v>105184</v>
+        <v>77988</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13595,25 +13599,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221725</v>
+        <v>6437</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13623,10 +13627,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>446013</v>
+        <v>446209</v>
       </c>
       <c r="R100" t="n">
-        <v>7026516</v>
+        <v>7026444</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13658,7 +13662,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13668,7 +13672,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13682,12 +13686,22 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal sumpskog/myr</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13705,7 +13719,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252826</v>
+        <v>121252814</v>
       </c>
       <c r="B101" t="n">
         <v>78604</v>
@@ -13745,10 +13759,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>446279</v>
+        <v>446185</v>
       </c>
       <c r="R101" t="n">
-        <v>7026520</v>
+        <v>7026627</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13780,7 +13794,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13790,7 +13804,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13804,7 +13818,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13819,7 +13833,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13969,10 +13983,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252812</v>
+        <v>121252820</v>
       </c>
       <c r="B103" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13985,21 +13999,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -14009,10 +14023,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>446185</v>
+        <v>446258</v>
       </c>
       <c r="R103" t="n">
-        <v>7026655</v>
+        <v>7026597</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -14044,7 +14058,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14054,7 +14068,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14068,7 +14082,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -14083,7 +14097,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14101,10 +14115,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121252836</v>
+        <v>121252801</v>
       </c>
       <c r="B104" t="n">
-        <v>78604</v>
+        <v>91393</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14113,25 +14127,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -14141,10 +14155,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>446201</v>
+        <v>445969</v>
       </c>
       <c r="R104" t="n">
-        <v>7026410</v>
+        <v>7026495</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14176,7 +14190,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14186,7 +14200,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14215,7 +14229,7 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14233,7 +14247,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252833</v>
+        <v>121252822</v>
       </c>
       <c r="B105" t="n">
         <v>78604</v>
@@ -14266,26 +14280,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>446233</v>
+        <v>446284</v>
       </c>
       <c r="R105" t="n">
-        <v>7026512</v>
+        <v>7026552</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14317,7 +14322,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14327,12 +14332,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14379,10 +14379,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121252825</v>
+        <v>121252836</v>
       </c>
       <c r="B106" t="n">
-        <v>78860</v>
+        <v>78604</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14391,25 +14391,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -14419,10 +14419,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>446278</v>
+        <v>446201</v>
       </c>
       <c r="R106" t="n">
-        <v>7026536</v>
+        <v>7026410</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14511,10 +14511,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121252811</v>
+        <v>121252803</v>
       </c>
       <c r="B107" t="n">
-        <v>90705</v>
+        <v>105185</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14523,25 +14523,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>221725</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -14551,10 +14551,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>446106</v>
+        <v>446013</v>
       </c>
       <c r="R107" t="n">
-        <v>7026528</v>
+        <v>7026516</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14610,22 +14610,12 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14643,10 +14633,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252802</v>
+        <v>121252818</v>
       </c>
       <c r="B108" t="n">
-        <v>90705</v>
+        <v>74522</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14655,25 +14645,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1108</v>
+        <v>6428</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14683,10 +14673,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445982</v>
+        <v>446209</v>
       </c>
       <c r="R108" t="n">
-        <v>7026514</v>
+        <v>7026630</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14718,7 +14708,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14728,7 +14718,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14742,7 +14732,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -14757,7 +14747,7 @@
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14775,10 +14765,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252839</v>
+        <v>121252825</v>
       </c>
       <c r="B109" t="n">
-        <v>90727</v>
+        <v>78860</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14787,25 +14777,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14815,10 +14805,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446209</v>
+        <v>446278</v>
       </c>
       <c r="R109" t="n">
-        <v>7026395</v>
+        <v>7026536</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14850,7 +14840,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14860,7 +14850,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14874,7 +14864,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -14889,7 +14879,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14907,10 +14897,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252804</v>
+        <v>121252833</v>
       </c>
       <c r="B110" t="n">
-        <v>97107</v>
+        <v>78604</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14919,38 +14909,47 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>446013</v>
+        <v>446233</v>
       </c>
       <c r="R110" t="n">
-        <v>7026514</v>
+        <v>7026512</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14982,7 +14981,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14992,7 +14991,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -15006,12 +15010,22 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15029,10 +15043,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252813</v>
+        <v>121252840</v>
       </c>
       <c r="B111" t="n">
-        <v>78604</v>
+        <v>77541</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15045,21 +15059,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -15069,10 +15083,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446166</v>
+        <v>446209</v>
       </c>
       <c r="R111" t="n">
-        <v>7026698</v>
+        <v>7026394</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15104,7 +15118,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15114,7 +15128,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15128,7 +15142,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -15143,7 +15157,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15161,10 +15175,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121252808</v>
+        <v>121252819</v>
       </c>
       <c r="B112" t="n">
-        <v>78638</v>
+        <v>77541</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15177,43 +15191,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>185</v>
+        <v>228579</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>446038</v>
+        <v>446258</v>
       </c>
       <c r="R112" t="n">
-        <v>7026546</v>
+        <v>7026597</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15245,7 +15250,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -15255,7 +15260,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15269,7 +15274,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -15284,7 +15289,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15302,10 +15307,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121252807</v>
+        <v>121252802</v>
       </c>
       <c r="B113" t="n">
-        <v>78604</v>
+        <v>90706</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15318,21 +15323,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -15342,10 +15347,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>446038</v>
+        <v>445982</v>
       </c>
       <c r="R113" t="n">
-        <v>7026546</v>
+        <v>7026514</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15377,7 +15382,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -15387,7 +15392,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15401,7 +15406,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -15416,7 +15421,7 @@
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15434,10 +15439,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121252815</v>
+        <v>121252811</v>
       </c>
       <c r="B114" t="n">
-        <v>57504</v>
+        <v>90706</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -15450,43 +15455,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>446189</v>
+        <v>446106</v>
       </c>
       <c r="R114" t="n">
-        <v>7026651</v>
+        <v>7026528</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15518,7 +15514,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -15528,7 +15524,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15542,7 +15538,22 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15560,10 +15571,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252830</v>
+        <v>121252827</v>
       </c>
       <c r="B115" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15576,21 +15587,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15635,7 +15646,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15645,7 +15656,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15674,7 +15685,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15692,10 +15703,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252837</v>
+        <v>121252807</v>
       </c>
       <c r="B116" t="n">
-        <v>77541</v>
+        <v>78604</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15708,21 +15719,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15732,10 +15743,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446201</v>
+        <v>446038</v>
       </c>
       <c r="R116" t="n">
-        <v>7026410</v>
+        <v>7026546</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15767,7 +15778,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15777,7 +15788,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15791,7 +15802,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -15806,7 +15817,7 @@
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15824,10 +15835,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252835</v>
+        <v>121252830</v>
       </c>
       <c r="B117" t="n">
-        <v>77988</v>
+        <v>74710</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15840,21 +15851,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15864,10 +15875,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446209</v>
+        <v>446252</v>
       </c>
       <c r="R117" t="n">
-        <v>7026444</v>
+        <v>7026536</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15899,7 +15910,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15909,7 +15920,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15923,22 +15934,22 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>I gammal sumpskog/myr</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15956,10 +15967,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252819</v>
+        <v>121252806</v>
       </c>
       <c r="B118" t="n">
-        <v>77541</v>
+        <v>74522</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15968,25 +15979,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15996,10 +16007,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446258</v>
+        <v>446038</v>
       </c>
       <c r="R118" t="n">
-        <v>7026597</v>
+        <v>7026546</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16031,7 +16042,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16041,7 +16052,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16055,7 +16066,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -16070,7 +16081,7 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16088,7 +16099,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252814</v>
+        <v>121252826</v>
       </c>
       <c r="B119" t="n">
         <v>78604</v>
@@ -16128,10 +16139,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446185</v>
+        <v>446279</v>
       </c>
       <c r="R119" t="n">
-        <v>7026627</v>
+        <v>7026520</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16163,7 +16174,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16173,7 +16184,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16187,7 +16198,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -16202,7 +16213,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16220,10 +16231,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121252820</v>
+        <v>121252821</v>
       </c>
       <c r="B120" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16236,21 +16247,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -16260,10 +16271,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446258</v>
+        <v>446282</v>
       </c>
       <c r="R120" t="n">
-        <v>7026597</v>
+        <v>7026592</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16295,7 +16306,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -16305,7 +16316,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16319,7 +16330,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -16334,7 +16345,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16352,10 +16363,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121252801</v>
+        <v>121252800</v>
       </c>
       <c r="B121" t="n">
-        <v>91392</v>
+        <v>57351</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -16364,38 +16375,43 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445969</v>
+        <v>446056</v>
       </c>
       <c r="R121" t="n">
-        <v>7026495</v>
+        <v>7026521</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16427,7 +16443,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -16437,7 +16453,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16454,19 +16475,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16484,10 +16495,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252810</v>
+        <v>121252817</v>
       </c>
       <c r="B122" t="n">
-        <v>74696</v>
+        <v>74694</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -16500,21 +16511,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>306</v>
+        <v>6439</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -16524,10 +16535,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446089</v>
+        <v>446209</v>
       </c>
       <c r="R122" t="n">
-        <v>7026536</v>
+        <v>7026630</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16559,7 +16570,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16569,7 +16580,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16578,13 +16589,12 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -16599,7 +16609,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16617,10 +16627,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252806</v>
+        <v>121252813</v>
       </c>
       <c r="B123" t="n">
-        <v>74522</v>
+        <v>78604</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16629,25 +16639,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16657,10 +16667,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446038</v>
+        <v>446166</v>
       </c>
       <c r="R123" t="n">
-        <v>7026546</v>
+        <v>7026698</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16692,7 +16702,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16702,7 +16712,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16716,7 +16726,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -16731,7 +16741,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -16749,10 +16759,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252800</v>
+        <v>121252804</v>
       </c>
       <c r="B124" t="n">
-        <v>57351</v>
+        <v>97108</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16761,43 +16771,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>221063</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>446056</v>
+        <v>446013</v>
       </c>
       <c r="R124" t="n">
-        <v>7026521</v>
+        <v>7026514</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16829,7 +16834,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16839,12 +16844,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -16878,6 +16878,127 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>121499846</v>
+      </c>
+      <c r="B125" t="n">
+        <v>57504</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>446188</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7026503</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -3551,10 +3551,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121117887</v>
+        <v>121117063</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3584,17 +3584,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svedaunsmyren, Jmt</t>
+          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446262</v>
+        <v>446063</v>
       </c>
       <c r="R23" t="n">
-        <v>7026371</v>
+        <v>7026497</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3626,7 +3635,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3636,12 +3645,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 stor garnlav</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3671,7 +3680,7 @@
         <v>121117416</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3794,10 +3803,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121117224</v>
+        <v>121117375</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
+        <v>77544</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3810,43 +3819,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446032</v>
+        <v>445930</v>
       </c>
       <c r="R25" t="n">
-        <v>7026520</v>
+        <v>7026568</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3888,7 +3888,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3908,17 +3913,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121117063</v>
+        <v>121117224</v>
       </c>
       <c r="B26" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3950,7 +3955,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3960,14 +3965,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
+          <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446063</v>
+        <v>446032</v>
       </c>
       <c r="R26" t="n">
-        <v>7026497</v>
+        <v>7026520</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3999,7 +4004,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4009,12 +4014,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4041,10 +4041,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121117375</v>
+        <v>121117887</v>
       </c>
       <c r="B27" t="n">
-        <v>77541</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4057,34 +4057,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svedaun, Svedaun, Jmt</t>
+          <t>Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445930</v>
+        <v>446262</v>
       </c>
       <c r="R27" t="n">
-        <v>7026568</v>
+        <v>7026371</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1 stor garnlav</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121134867</v>
+        <v>121134865</v>
       </c>
       <c r="B28" t="n">
-        <v>77541</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4174,34 +4174,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446244</v>
+        <v>446213</v>
       </c>
       <c r="R28" t="n">
-        <v>7026516</v>
+        <v>7026555</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4233,7 +4242,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4243,7 +4252,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4272,7 +4281,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4290,10 +4299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121134857</v>
+        <v>121134853</v>
       </c>
       <c r="B29" t="n">
-        <v>78604</v>
+        <v>74704</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4302,25 +4311,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4330,10 +4339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446075</v>
+        <v>445965</v>
       </c>
       <c r="R29" t="n">
-        <v>7026515</v>
+        <v>7026512</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4365,7 +4374,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4375,7 +4384,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4389,7 +4398,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4404,7 +4413,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4422,10 +4431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121134546</v>
+        <v>121134557</v>
       </c>
       <c r="B30" t="n">
-        <v>77541</v>
+        <v>74704</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4434,25 +4443,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>492</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4462,10 +4471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445987</v>
+        <v>446026</v>
       </c>
       <c r="R30" t="n">
-        <v>7026512</v>
+        <v>7026520</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4497,7 +4506,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4507,7 +4516,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4526,17 +4535,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4554,10 +4563,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121132934</v>
+        <v>121132943</v>
       </c>
       <c r="B31" t="n">
-        <v>78604</v>
+        <v>74713</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4570,21 +4579,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4594,10 +4603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446253</v>
+        <v>446259</v>
       </c>
       <c r="R31" t="n">
-        <v>7026514</v>
+        <v>7026469</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4658,7 +4667,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4676,10 +4685,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121132948</v>
+        <v>121134852</v>
       </c>
       <c r="B32" t="n">
-        <v>77541</v>
+        <v>90727</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4692,21 +4701,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4716,10 +4725,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446111</v>
+        <v>445963</v>
       </c>
       <c r="R32" t="n">
-        <v>7026483</v>
+        <v>7026504</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4746,12 +4755,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4765,7 +4784,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4780,7 +4799,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4798,10 +4817,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121134542</v>
+        <v>121134543</v>
       </c>
       <c r="B33" t="n">
-        <v>95642</v>
+        <v>98098</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4810,38 +4829,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446080</v>
+        <v>446069</v>
       </c>
       <c r="R33" t="n">
-        <v>7026521</v>
+        <v>7026527</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4873,7 +4901,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4883,7 +4911,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4900,19 +4933,9 @@
           <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>På mycket gammal granlåga # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4930,10 +4953,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121134863</v>
+        <v>121134538</v>
       </c>
       <c r="B34" t="n">
-        <v>78604</v>
+        <v>105188</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4942,25 +4965,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4970,10 +4993,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446203</v>
+        <v>446142</v>
       </c>
       <c r="R34" t="n">
-        <v>7026536</v>
+        <v>7026514</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5000,22 +5023,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5029,22 +5052,12 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5055,17 +5068,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121134859</v>
+        <v>121134873</v>
       </c>
       <c r="B35" t="n">
-        <v>74710</v>
+        <v>77544</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5078,21 +5091,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5102,10 +5115,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446158</v>
+        <v>446269</v>
       </c>
       <c r="R35" t="n">
-        <v>7026570</v>
+        <v>7026478</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5137,7 +5150,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5147,7 +5160,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5161,7 +5174,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5176,7 +5189,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5194,10 +5207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121134855</v>
+        <v>121134858</v>
       </c>
       <c r="B36" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5210,21 +5223,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5234,10 +5247,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446045</v>
+        <v>446092</v>
       </c>
       <c r="R36" t="n">
-        <v>7026526</v>
+        <v>7026520</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5269,7 +5282,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5279,7 +5292,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5308,7 +5321,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5326,10 +5339,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121134865</v>
+        <v>121132935</v>
       </c>
       <c r="B37" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5359,26 +5372,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446213</v>
+        <v>446246</v>
       </c>
       <c r="R37" t="n">
-        <v>7026555</v>
+        <v>7026518</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5405,22 +5409,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5434,7 +5428,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5449,7 +5443,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
+          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5467,10 +5461,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121134853</v>
+        <v>121134862</v>
       </c>
       <c r="B38" t="n">
-        <v>74701</v>
+        <v>74713</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5479,25 +5473,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5507,10 +5501,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445965</v>
+        <v>446197</v>
       </c>
       <c r="R38" t="n">
-        <v>7026512</v>
+        <v>7026538</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5542,7 +5536,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5552,7 +5546,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5566,7 +5560,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5581,7 +5575,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5599,10 +5593,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121134873</v>
+        <v>121134548</v>
       </c>
       <c r="B39" t="n">
-        <v>77541</v>
+        <v>88034</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5615,21 +5609,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5639,10 +5633,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446269</v>
+        <v>445938</v>
       </c>
       <c r="R39" t="n">
-        <v>7026478</v>
+        <v>7026514</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5669,22 +5663,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5698,7 +5692,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5713,7 +5707,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5724,17 +5718,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121134555</v>
+        <v>121134542</v>
       </c>
       <c r="B40" t="n">
-        <v>90675</v>
+        <v>95645</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5743,25 +5737,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5771,10 +5765,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446030</v>
+        <v>446080</v>
       </c>
       <c r="R40" t="n">
-        <v>7026523</v>
+        <v>7026521</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5806,7 +5800,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5816,7 +5810,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5830,7 +5824,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5845,7 +5839,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
+          <t>På mycket gammal granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5863,10 +5857,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121134877</v>
+        <v>121132950</v>
       </c>
       <c r="B41" t="n">
-        <v>77541</v>
+        <v>78770</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5875,38 +5869,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446271</v>
+        <v>446118</v>
       </c>
       <c r="R41" t="n">
-        <v>7026473</v>
+        <v>7026441</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5933,22 +5936,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1 bål</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5962,7 +5960,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5977,7 +5975,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5995,10 +5993,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121134540</v>
+        <v>121134537</v>
       </c>
       <c r="B42" t="n">
-        <v>74696</v>
+        <v>74697</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6011,21 +6009,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>306</v>
+        <v>6439</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6035,10 +6033,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446088</v>
+        <v>446153</v>
       </c>
       <c r="R42" t="n">
-        <v>7026528</v>
+        <v>7026500</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6070,7 +6068,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6080,7 +6078,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6089,7 +6087,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6100,17 +6097,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På björkhögstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6128,10 +6125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121134864</v>
+        <v>121132927</v>
       </c>
       <c r="B43" t="n">
-        <v>74710</v>
+        <v>78607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6144,21 +6141,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6168,10 +6165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446203</v>
+        <v>446305</v>
       </c>
       <c r="R43" t="n">
-        <v>7026536</v>
+        <v>7026607</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6198,22 +6195,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>60 cm lång bål</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6227,22 +6219,22 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6260,10 +6252,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121134880</v>
+        <v>121134859</v>
       </c>
       <c r="B44" t="n">
-        <v>56563</v>
+        <v>74713</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6272,47 +6264,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446259</v>
+        <v>446158</v>
       </c>
       <c r="R44" t="n">
-        <v>7026406</v>
+        <v>7026570</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6344,7 +6327,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6354,12 +6337,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Satt i gammal gran</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6373,7 +6351,22 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6391,10 +6384,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121132945</v>
+        <v>121134860</v>
       </c>
       <c r="B45" t="n">
-        <v>90728</v>
+        <v>78607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6407,34 +6400,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446220</v>
+        <v>446170</v>
       </c>
       <c r="R45" t="n">
-        <v>7026528</v>
+        <v>7026558</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6461,12 +6463,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6480,7 +6492,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6495,7 +6507,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>på gammal dubbelgran # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6513,10 +6525,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121134861</v>
+        <v>121134552</v>
       </c>
       <c r="B46" t="n">
-        <v>77541</v>
+        <v>77544</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6553,10 +6565,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>446197</v>
+        <v>445924</v>
       </c>
       <c r="R46" t="n">
-        <v>7026538</v>
+        <v>7026587</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6583,22 +6595,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6612,7 +6624,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6627,7 +6639,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6638,17 +6650,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121134852</v>
+        <v>121132948</v>
       </c>
       <c r="B47" t="n">
-        <v>90724</v>
+        <v>77544</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6661,21 +6673,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6685,10 +6697,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445963</v>
+        <v>446111</v>
       </c>
       <c r="R47" t="n">
-        <v>7026504</v>
+        <v>7026483</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6715,22 +6727,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6744,7 +6746,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6759,7 +6761,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6777,10 +6779,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121132930</v>
+        <v>121134541</v>
       </c>
       <c r="B48" t="n">
-        <v>77541</v>
+        <v>74705</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6793,21 +6795,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6817,10 +6819,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>446284</v>
+        <v>446088</v>
       </c>
       <c r="R48" t="n">
-        <v>7026556</v>
+        <v>7026528</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6847,12 +6849,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6866,7 +6878,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6881,7 +6893,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6892,17 +6904,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121134860</v>
+        <v>121132934</v>
       </c>
       <c r="B49" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6932,26 +6944,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446170</v>
+        <v>446253</v>
       </c>
       <c r="R49" t="n">
-        <v>7026558</v>
+        <v>7026514</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6978,22 +6981,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7007,7 +7000,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7022,7 +7015,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7040,10 +7033,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121132949</v>
+        <v>121134549</v>
       </c>
       <c r="B50" t="n">
-        <v>78604</v>
+        <v>74713</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7056,43 +7049,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446118</v>
+        <v>445936</v>
       </c>
       <c r="R50" t="n">
-        <v>7026441</v>
+        <v>7026522</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7119,17 +7103,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>7 bålar</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7143,7 +7132,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7158,7 +7147,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7169,17 +7158,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121134868</v>
+        <v>121134857</v>
       </c>
       <c r="B51" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7216,10 +7205,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446262</v>
+        <v>446075</v>
       </c>
       <c r="R51" t="n">
-        <v>7026488</v>
+        <v>7026515</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7251,7 +7240,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7261,7 +7250,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7275,7 +7264,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7290,7 +7279,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7308,10 +7297,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121134535</v>
+        <v>121134868</v>
       </c>
       <c r="B52" t="n">
-        <v>78767</v>
+        <v>78607</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7320,47 +7309,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446119</v>
+        <v>446262</v>
       </c>
       <c r="R52" t="n">
-        <v>7026442</v>
+        <v>7026488</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7387,27 +7367,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:41</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Samma som sedd tidigare i år</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7421,7 +7396,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -7436,7 +7411,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7447,17 +7422,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121134556</v>
+        <v>121134863</v>
       </c>
       <c r="B53" t="n">
-        <v>74715</v>
+        <v>78607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7470,21 +7445,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7494,10 +7469,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446026</v>
+        <v>446203</v>
       </c>
       <c r="R53" t="n">
-        <v>7026520</v>
+        <v>7026536</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7524,22 +7499,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7553,22 +7528,22 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7579,17 +7554,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121134849</v>
+        <v>121134871</v>
       </c>
       <c r="B54" t="n">
-        <v>91150</v>
+        <v>74525</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7598,25 +7573,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>6428</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7626,10 +7601,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445948</v>
+        <v>446269</v>
       </c>
       <c r="R54" t="n">
-        <v>7026487</v>
+        <v>7026478</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7661,7 +7636,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7671,7 +7646,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7685,7 +7660,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7700,7 +7675,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>På grov granlåga # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7718,10 +7693,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121134862</v>
+        <v>121132926</v>
       </c>
       <c r="B55" t="n">
-        <v>74710</v>
+        <v>56566</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7730,25 +7705,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7758,10 +7733,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446197</v>
+        <v>446305</v>
       </c>
       <c r="R55" t="n">
-        <v>7026538</v>
+        <v>7026607</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7788,22 +7763,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>uppflog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7817,22 +7787,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7850,10 +7805,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121134541</v>
+        <v>121134544</v>
       </c>
       <c r="B56" t="n">
-        <v>74702</v>
+        <v>90713</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7866,21 +7821,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7890,10 +7845,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446088</v>
+        <v>446005</v>
       </c>
       <c r="R56" t="n">
-        <v>7026528</v>
+        <v>7026502</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7925,7 +7880,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7935,7 +7890,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7964,7 +7919,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7982,10 +7937,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121132943</v>
+        <v>121132936</v>
       </c>
       <c r="B57" t="n">
-        <v>74710</v>
+        <v>77544</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7998,21 +7953,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8022,10 +7977,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446259</v>
+        <v>446254</v>
       </c>
       <c r="R57" t="n">
-        <v>7026469</v>
+        <v>7026486</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8086,7 +8041,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8104,10 +8059,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121132936</v>
+        <v>121134867</v>
       </c>
       <c r="B58" t="n">
-        <v>77541</v>
+        <v>77544</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8144,10 +8099,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446254</v>
+        <v>446244</v>
       </c>
       <c r="R58" t="n">
-        <v>7026486</v>
+        <v>7026516</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8174,12 +8129,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8193,7 +8158,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -8208,7 +8173,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8226,10 +8191,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121134858</v>
+        <v>121134540</v>
       </c>
       <c r="B59" t="n">
-        <v>90728</v>
+        <v>74699</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8238,25 +8203,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8266,10 +8231,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446092</v>
+        <v>446088</v>
       </c>
       <c r="R59" t="n">
-        <v>7026520</v>
+        <v>7026528</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8296,22 +8261,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8320,12 +8285,13 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -8340,7 +8306,7 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8351,17 +8317,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121134549</v>
+        <v>121132928</v>
       </c>
       <c r="B60" t="n">
-        <v>74710</v>
+        <v>78607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8374,34 +8340,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445936</v>
+        <v>446290</v>
       </c>
       <c r="R60" t="n">
-        <v>7026522</v>
+        <v>7026577</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8428,22 +8403,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>20 bålar</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8457,7 +8427,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8472,7 +8442,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8483,17 +8453,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121132950</v>
+        <v>121134855</v>
       </c>
       <c r="B61" t="n">
-        <v>78767</v>
+        <v>78607</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8502,47 +8472,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>446118</v>
+        <v>446045</v>
       </c>
       <c r="R61" t="n">
-        <v>7026441</v>
+        <v>7026526</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8569,17 +8530,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>1 bål</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8593,7 +8559,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8608,7 +8574,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8626,10 +8592,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121132932</v>
+        <v>121132945</v>
       </c>
       <c r="B62" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8642,21 +8608,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8666,10 +8632,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>446284</v>
+        <v>446220</v>
       </c>
       <c r="R62" t="n">
-        <v>7026556</v>
+        <v>7026528</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8730,7 +8696,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>på gammal dubbelgran # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8748,10 +8714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121134851</v>
+        <v>121134878</v>
       </c>
       <c r="B63" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8764,34 +8730,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445959</v>
+        <v>446262</v>
       </c>
       <c r="R63" t="n">
-        <v>7026504</v>
+        <v>7026436</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8823,7 +8798,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8833,7 +8808,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8847,7 +8822,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -8862,7 +8837,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8880,10 +8855,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121132927</v>
+        <v>121134880</v>
       </c>
       <c r="B64" t="n">
-        <v>78604</v>
+        <v>56566</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8892,38 +8867,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>446305</v>
+        <v>446259</v>
       </c>
       <c r="R64" t="n">
-        <v>7026607</v>
+        <v>7026406</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8950,17 +8934,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>60 cm lång bål</t>
+          <t>Satt i gammal gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8974,22 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9007,10 +8986,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121132944</v>
+        <v>121134864</v>
       </c>
       <c r="B65" t="n">
-        <v>78604</v>
+        <v>74713</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9023,21 +9002,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9047,10 +9026,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>446279</v>
+        <v>446203</v>
       </c>
       <c r="R65" t="n">
-        <v>7026455</v>
+        <v>7026536</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9077,17 +9056,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>40 cm lång bål</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9101,22 +9085,22 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9137,7 +9121,7 @@
         <v>121134875</v>
       </c>
       <c r="B66" t="n">
-        <v>74710</v>
+        <v>74713</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9266,10 +9250,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121134552</v>
+        <v>121132930</v>
       </c>
       <c r="B67" t="n">
-        <v>77541</v>
+        <v>77544</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9306,10 +9290,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445924</v>
+        <v>446284</v>
       </c>
       <c r="R67" t="n">
-        <v>7026587</v>
+        <v>7026556</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9336,22 +9320,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9365,7 +9339,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -9380,7 +9354,7 @@
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9391,17 +9365,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121132926</v>
+        <v>121132931</v>
       </c>
       <c r="B68" t="n">
-        <v>56563</v>
+        <v>74713</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9410,25 +9384,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9438,10 +9412,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>446305</v>
+        <v>446284</v>
       </c>
       <c r="R68" t="n">
-        <v>7026607</v>
+        <v>7026556</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9476,11 +9450,6 @@
           <t>2024-03-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>uppflog</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9492,7 +9461,22 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9510,10 +9494,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121134536</v>
+        <v>121134553</v>
       </c>
       <c r="B69" t="n">
-        <v>90706</v>
+        <v>74713</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9526,21 +9510,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9550,10 +9534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>446164</v>
+        <v>445925</v>
       </c>
       <c r="R69" t="n">
-        <v>7026463</v>
+        <v>7026580</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9585,7 +9569,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9595,7 +9579,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9609,7 +9593,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9624,7 +9608,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>På död gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9642,10 +9626,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121134869</v>
+        <v>121134849</v>
       </c>
       <c r="B70" t="n">
-        <v>90710</v>
+        <v>91153</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9654,25 +9638,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9682,10 +9666,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>446262</v>
+        <v>445948</v>
       </c>
       <c r="R70" t="n">
-        <v>7026488</v>
+        <v>7026487</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9717,7 +9701,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9727,7 +9711,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9741,7 +9725,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -9756,7 +9740,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På grov granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9774,10 +9758,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121134550</v>
+        <v>121134545</v>
       </c>
       <c r="B71" t="n">
-        <v>90481</v>
+        <v>78607</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9786,38 +9770,47 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3215</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445911</v>
+        <v>445987</v>
       </c>
       <c r="R71" t="n">
-        <v>7026564</v>
+        <v>7026510</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9849,7 +9842,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9859,7 +9852,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>10 bålar, den längsta 30 cm</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9873,12 +9871,22 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog, sumpskog/myr</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9896,10 +9904,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121134551</v>
+        <v>121134539</v>
       </c>
       <c r="B72" t="n">
-        <v>78604</v>
+        <v>74718</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9912,21 +9920,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9936,10 +9944,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445899</v>
+        <v>446088</v>
       </c>
       <c r="R72" t="n">
-        <v>7026589</v>
+        <v>7026528</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9971,7 +9979,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9981,7 +9989,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9995,7 +10003,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -10010,7 +10018,7 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10028,10 +10036,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121134866</v>
+        <v>121134536</v>
       </c>
       <c r="B73" t="n">
-        <v>90728</v>
+        <v>90709</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10044,21 +10052,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10068,10 +10076,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>446218</v>
+        <v>446164</v>
       </c>
       <c r="R73" t="n">
-        <v>7026544</v>
+        <v>7026463</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10098,22 +10106,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10127,7 +10135,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10142,7 +10150,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10153,17 +10161,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121134878</v>
+        <v>121134555</v>
       </c>
       <c r="B74" t="n">
-        <v>78604</v>
+        <v>90678</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10172,47 +10180,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>446262</v>
+        <v>446030</v>
       </c>
       <c r="R74" t="n">
-        <v>7026436</v>
+        <v>7026523</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10239,22 +10238,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10268,7 +10267,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -10283,7 +10282,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10294,17 +10293,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121132935</v>
+        <v>121134550</v>
       </c>
       <c r="B75" t="n">
-        <v>78604</v>
+        <v>90484</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10313,25 +10312,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10341,10 +10340,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>446246</v>
+        <v>445911</v>
       </c>
       <c r="R75" t="n">
-        <v>7026518</v>
+        <v>7026564</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10371,12 +10370,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10390,22 +10399,12 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal barrblandskog, sumpskog/myr</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10416,17 +10415,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121134544</v>
+        <v>121132932</v>
       </c>
       <c r="B76" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10439,21 +10438,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10463,10 +10462,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>446005</v>
+        <v>446284</v>
       </c>
       <c r="R76" t="n">
-        <v>7026502</v>
+        <v>7026556</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10493,22 +10492,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10522,7 +10511,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
@@ -10537,7 +10526,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10548,17 +10537,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121134548</v>
+        <v>121134558</v>
       </c>
       <c r="B77" t="n">
-        <v>88031</v>
+        <v>78607</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10571,21 +10560,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10595,10 +10584,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445938</v>
+        <v>446050</v>
       </c>
       <c r="R77" t="n">
-        <v>7026514</v>
+        <v>7026501</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10630,7 +10619,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10640,7 +10629,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10654,7 +10643,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gles gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -10669,7 +10658,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10687,10 +10676,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121134539</v>
+        <v>121132944</v>
       </c>
       <c r="B78" t="n">
-        <v>74715</v>
+        <v>78607</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10703,21 +10692,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10727,10 +10716,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>446088</v>
+        <v>446279</v>
       </c>
       <c r="R78" t="n">
-        <v>7026528</v>
+        <v>7026455</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10757,22 +10746,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>40 cm lång bål</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10786,22 +10770,22 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10812,17 +10796,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121134850</v>
+        <v>121132949</v>
       </c>
       <c r="B79" t="n">
-        <v>91643</v>
+        <v>78607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10831,38 +10815,47 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445960</v>
+        <v>446118</v>
       </c>
       <c r="R79" t="n">
-        <v>7026492</v>
+        <v>7026441</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10889,22 +10882,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>7 bålar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10918,12 +10906,22 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10941,10 +10939,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121134543</v>
+        <v>121134546</v>
       </c>
       <c r="B80" t="n">
-        <v>98095</v>
+        <v>77544</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10953,47 +10951,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>446069</v>
+        <v>445987</v>
       </c>
       <c r="R80" t="n">
-        <v>7026527</v>
+        <v>7026512</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11025,7 +11014,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11035,12 +11024,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11054,12 +11038,22 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11077,10 +11071,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121134553</v>
+        <v>121134869</v>
       </c>
       <c r="B81" t="n">
-        <v>74710</v>
+        <v>90713</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11093,21 +11087,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11117,10 +11111,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445925</v>
+        <v>446262</v>
       </c>
       <c r="R81" t="n">
-        <v>7026580</v>
+        <v>7026488</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11147,22 +11141,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11176,7 +11170,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -11191,7 +11185,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11202,17 +11196,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121134557</v>
+        <v>121134870</v>
       </c>
       <c r="B82" t="n">
-        <v>74701</v>
+        <v>91153</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11225,21 +11219,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>492</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11249,10 +11243,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>446026</v>
+        <v>446262</v>
       </c>
       <c r="R82" t="n">
-        <v>7026520</v>
+        <v>7026488</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11279,22 +11273,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11308,22 +11302,22 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11334,17 +11328,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121134871</v>
+        <v>121134851</v>
       </c>
       <c r="B83" t="n">
-        <v>74522</v>
+        <v>90713</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11353,25 +11347,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -11381,10 +11375,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>446269</v>
+        <v>445959</v>
       </c>
       <c r="R83" t="n">
-        <v>7026478</v>
+        <v>7026504</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11416,7 +11410,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11426,7 +11420,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11440,7 +11434,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -11455,7 +11449,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11473,10 +11467,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121134537</v>
+        <v>121134535</v>
       </c>
       <c r="B84" t="n">
-        <v>74694</v>
+        <v>78770</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11485,38 +11479,47 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6439</v>
+        <v>1249</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>446153</v>
+        <v>446119</v>
       </c>
       <c r="R84" t="n">
-        <v>7026500</v>
+        <v>7026442</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11548,7 +11551,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11558,7 +11561,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Samma som sedd tidigare i år</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11577,17 +11585,17 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>På björkhögstubbe # Betula pubescens</t>
+          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11605,10 +11613,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121134558</v>
+        <v>121134850</v>
       </c>
       <c r="B85" t="n">
-        <v>78604</v>
+        <v>91646</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11617,25 +11625,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11645,10 +11653,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>446050</v>
+        <v>445960</v>
       </c>
       <c r="R85" t="n">
-        <v>7026501</v>
+        <v>7026492</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11675,22 +11683,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11704,22 +11712,12 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>I gles gammal gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11730,17 +11728,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121132928</v>
+        <v>121134551</v>
       </c>
       <c r="B86" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11770,26 +11768,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>446290</v>
+        <v>445899</v>
       </c>
       <c r="R86" t="n">
-        <v>7026577</v>
+        <v>7026589</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11816,17 +11805,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>20 bålar</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11840,7 +11834,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>i gammal gles barrblandskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -11855,7 +11849,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11866,17 +11860,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121132931</v>
+        <v>121134877</v>
       </c>
       <c r="B87" t="n">
-        <v>74710</v>
+        <v>77544</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11889,21 +11883,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11913,10 +11907,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>446284</v>
+        <v>446271</v>
       </c>
       <c r="R87" t="n">
-        <v>7026556</v>
+        <v>7026473</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11943,12 +11937,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11962,7 +11966,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -11977,7 +11981,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11995,10 +11999,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121134538</v>
+        <v>121134861</v>
       </c>
       <c r="B88" t="n">
-        <v>105185</v>
+        <v>77544</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12007,25 +12011,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221725</v>
+        <v>228579</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -12035,10 +12039,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>446142</v>
+        <v>446197</v>
       </c>
       <c r="R88" t="n">
-        <v>7026514</v>
+        <v>7026538</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12065,22 +12069,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12094,12 +12098,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12110,17 +12124,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121134870</v>
+        <v>121134556</v>
       </c>
       <c r="B89" t="n">
-        <v>91150</v>
+        <v>74718</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12129,25 +12143,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1209</v>
+        <v>1467</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12157,10 +12171,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>446262</v>
+        <v>446026</v>
       </c>
       <c r="R89" t="n">
-        <v>7026488</v>
+        <v>7026520</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12187,22 +12201,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12216,22 +12230,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12242,17 +12256,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121134545</v>
+        <v>121134866</v>
       </c>
       <c r="B90" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12265,43 +12279,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445987</v>
+        <v>446218</v>
       </c>
       <c r="R90" t="n">
-        <v>7026510</v>
+        <v>7026544</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12328,27 +12333,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>10 bålar, den längsta 30 cm</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12388,17 +12388,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252824</v>
+        <v>121252802</v>
       </c>
       <c r="B91" t="n">
-        <v>77541</v>
+        <v>90709</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12411,21 +12411,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>446278</v>
+        <v>445982</v>
       </c>
       <c r="R91" t="n">
-        <v>7026536</v>
+        <v>7026514</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12527,10 +12527,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252810</v>
+        <v>121252837</v>
       </c>
       <c r="B92" t="n">
-        <v>74696</v>
+        <v>77544</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12539,25 +12539,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>306</v>
+        <v>228579</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>446089</v>
+        <v>446201</v>
       </c>
       <c r="R92" t="n">
-        <v>7026536</v>
+        <v>7026410</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12621,7 +12621,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -12642,7 +12641,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12660,10 +12659,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252839</v>
+        <v>121252826</v>
       </c>
       <c r="B93" t="n">
-        <v>90728</v>
+        <v>78607</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12676,21 +12675,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12700,10 +12699,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>446209</v>
+        <v>446279</v>
       </c>
       <c r="R93" t="n">
-        <v>7026395</v>
+        <v>7026520</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12735,7 +12734,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12745,7 +12744,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12759,7 +12758,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -12774,7 +12773,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12792,10 +12791,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121252812</v>
+        <v>121252818</v>
       </c>
       <c r="B94" t="n">
-        <v>78604</v>
+        <v>74525</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12804,25 +12803,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12832,10 +12831,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>446185</v>
+        <v>446209</v>
       </c>
       <c r="R94" t="n">
-        <v>7026655</v>
+        <v>7026630</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12867,7 +12866,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12877,7 +12876,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12906,7 +12905,7 @@
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12924,10 +12923,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252815</v>
+        <v>121252833</v>
       </c>
       <c r="B95" t="n">
-        <v>57504</v>
+        <v>78607</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12940,31 +12939,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -12973,10 +12972,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>446189</v>
+        <v>446233</v>
       </c>
       <c r="R95" t="n">
-        <v>7026651</v>
+        <v>7026512</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13008,7 +13007,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13018,7 +13017,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13032,7 +13036,22 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13050,10 +13069,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252808</v>
+        <v>121252824</v>
       </c>
       <c r="B96" t="n">
-        <v>78638</v>
+        <v>77544</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13066,43 +13085,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>228579</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446038</v>
+        <v>446278</v>
       </c>
       <c r="R96" t="n">
-        <v>7026546</v>
+        <v>7026536</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13134,7 +13144,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13144,7 +13154,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13158,7 +13168,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -13173,7 +13183,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13191,10 +13201,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252809</v>
+        <v>121252838</v>
       </c>
       <c r="B97" t="n">
-        <v>77541</v>
+        <v>74713</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13207,21 +13217,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -13231,10 +13241,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446044</v>
+        <v>446201</v>
       </c>
       <c r="R97" t="n">
-        <v>7026549</v>
+        <v>7026410</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13266,7 +13276,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13276,7 +13286,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13290,7 +13300,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -13305,7 +13315,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13323,10 +13333,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252838</v>
+        <v>121252806</v>
       </c>
       <c r="B98" t="n">
-        <v>74710</v>
+        <v>74525</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13335,25 +13345,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13363,10 +13373,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446201</v>
+        <v>446038</v>
       </c>
       <c r="R98" t="n">
-        <v>7026410</v>
+        <v>7026546</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13398,7 +13408,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13408,7 +13418,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13422,7 +13432,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -13437,7 +13447,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13455,10 +13465,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121252837</v>
+        <v>121252813</v>
       </c>
       <c r="B99" t="n">
-        <v>77541</v>
+        <v>78607</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13471,21 +13481,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -13495,10 +13505,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>446201</v>
+        <v>446166</v>
       </c>
       <c r="R99" t="n">
-        <v>7026410</v>
+        <v>7026698</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13530,7 +13540,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13540,7 +13550,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13554,7 +13564,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -13569,7 +13579,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13587,10 +13597,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121252835</v>
+        <v>121252840</v>
       </c>
       <c r="B100" t="n">
-        <v>77988</v>
+        <v>77544</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13603,21 +13613,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6437</v>
+        <v>228579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13630,7 +13640,7 @@
         <v>446209</v>
       </c>
       <c r="R100" t="n">
-        <v>7026444</v>
+        <v>7026394</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13662,7 +13672,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13672,7 +13682,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13686,22 +13696,22 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>I gammal sumpskog/myr</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13719,10 +13729,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252814</v>
+        <v>121252822</v>
       </c>
       <c r="B101" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13759,10 +13769,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>446185</v>
+        <v>446284</v>
       </c>
       <c r="R101" t="n">
-        <v>7026627</v>
+        <v>7026552</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13794,7 +13804,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13804,7 +13814,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13818,7 +13828,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13833,7 +13843,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13851,10 +13861,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121252823</v>
+        <v>121252803</v>
       </c>
       <c r="B102" t="n">
-        <v>78604</v>
+        <v>105188</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13863,25 +13873,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13891,10 +13901,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>446274</v>
+        <v>446013</v>
       </c>
       <c r="R102" t="n">
-        <v>7026540</v>
+        <v>7026516</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13926,7 +13936,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13936,7 +13946,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13950,22 +13960,12 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13983,10 +13983,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252820</v>
+        <v>121252823</v>
       </c>
       <c r="B103" t="n">
-        <v>74710</v>
+        <v>78607</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13999,21 +13999,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -14023,10 +14023,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>446258</v>
+        <v>446274</v>
       </c>
       <c r="R103" t="n">
-        <v>7026597</v>
+        <v>7026540</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14118,7 +14118,7 @@
         <v>121252801</v>
       </c>
       <c r="B104" t="n">
-        <v>91393</v>
+        <v>91396</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14247,10 +14247,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252822</v>
+        <v>121252839</v>
       </c>
       <c r="B105" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14263,21 +14263,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -14287,10 +14287,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>446284</v>
+        <v>446209</v>
       </c>
       <c r="R105" t="n">
-        <v>7026552</v>
+        <v>7026395</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14379,10 +14379,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121252836</v>
+        <v>121252825</v>
       </c>
       <c r="B106" t="n">
-        <v>78604</v>
+        <v>78863</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14391,25 +14391,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -14419,10 +14419,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>446201</v>
+        <v>446278</v>
       </c>
       <c r="R106" t="n">
-        <v>7026410</v>
+        <v>7026536</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14511,10 +14511,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121252803</v>
+        <v>121252811</v>
       </c>
       <c r="B107" t="n">
-        <v>105185</v>
+        <v>90709</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14523,25 +14523,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -14551,10 +14551,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>446013</v>
+        <v>446106</v>
       </c>
       <c r="R107" t="n">
-        <v>7026516</v>
+        <v>7026528</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14610,12 +14610,22 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14633,10 +14643,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252818</v>
+        <v>121252810</v>
       </c>
       <c r="B108" t="n">
-        <v>74522</v>
+        <v>74699</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14649,21 +14659,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6428</v>
+        <v>306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14673,10 +14683,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>446209</v>
+        <v>446089</v>
       </c>
       <c r="R108" t="n">
-        <v>7026630</v>
+        <v>7026536</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14708,7 +14718,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14718,7 +14728,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14727,12 +14737,13 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -14747,7 +14758,7 @@
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14765,10 +14776,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252825</v>
+        <v>121252821</v>
       </c>
       <c r="B109" t="n">
-        <v>78860</v>
+        <v>78607</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14777,25 +14788,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14805,10 +14816,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446278</v>
+        <v>446282</v>
       </c>
       <c r="R109" t="n">
-        <v>7026536</v>
+        <v>7026592</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14840,7 +14851,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14850,7 +14861,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14879,7 +14890,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14897,10 +14908,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252833</v>
+        <v>121252819</v>
       </c>
       <c r="B110" t="n">
-        <v>78604</v>
+        <v>77544</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14913,43 +14924,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>446233</v>
+        <v>446258</v>
       </c>
       <c r="R110" t="n">
-        <v>7026512</v>
+        <v>7026597</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14981,7 +14983,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14991,12 +14993,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -15010,7 +15007,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -15025,7 +15022,7 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15043,10 +15040,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252840</v>
+        <v>121252812</v>
       </c>
       <c r="B111" t="n">
-        <v>77541</v>
+        <v>78607</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15059,21 +15056,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -15083,10 +15080,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446209</v>
+        <v>446185</v>
       </c>
       <c r="R111" t="n">
-        <v>7026394</v>
+        <v>7026655</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15118,7 +15115,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15128,7 +15125,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15142,7 +15139,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -15157,7 +15154,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15175,10 +15172,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121252819</v>
+        <v>121252809</v>
       </c>
       <c r="B112" t="n">
-        <v>77541</v>
+        <v>77544</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15215,10 +15212,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>446258</v>
+        <v>446044</v>
       </c>
       <c r="R112" t="n">
-        <v>7026597</v>
+        <v>7026549</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15250,7 +15247,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -15260,7 +15257,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15274,7 +15271,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -15289,7 +15286,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15307,10 +15304,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121252802</v>
+        <v>121252815</v>
       </c>
       <c r="B113" t="n">
-        <v>90706</v>
+        <v>57507</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15323,34 +15320,43 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445982</v>
+        <v>446189</v>
       </c>
       <c r="R113" t="n">
-        <v>7026514</v>
+        <v>7026651</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15382,7 +15388,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -15392,7 +15398,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15406,22 +15412,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15439,10 +15430,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121252811</v>
+        <v>121252827</v>
       </c>
       <c r="B114" t="n">
-        <v>90706</v>
+        <v>78607</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -15455,21 +15446,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -15479,10 +15470,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>446106</v>
+        <v>446252</v>
       </c>
       <c r="R114" t="n">
-        <v>7026528</v>
+        <v>7026536</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15514,7 +15505,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -15524,7 +15515,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15538,7 +15529,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -15553,7 +15544,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15571,10 +15562,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252827</v>
+        <v>121252836</v>
       </c>
       <c r="B115" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15611,10 +15602,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446252</v>
+        <v>446201</v>
       </c>
       <c r="R115" t="n">
-        <v>7026536</v>
+        <v>7026410</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15646,7 +15637,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15656,7 +15647,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15670,7 +15661,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -15685,7 +15676,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15703,10 +15694,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252807</v>
+        <v>121252835</v>
       </c>
       <c r="B116" t="n">
-        <v>78604</v>
+        <v>77991</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15719,21 +15710,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15743,10 +15734,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446038</v>
+        <v>446209</v>
       </c>
       <c r="R116" t="n">
-        <v>7026546</v>
+        <v>7026444</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15778,7 +15769,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15788,7 +15779,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15802,22 +15793,22 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal sumpskog/myr</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15838,7 +15829,7 @@
         <v>121252830</v>
       </c>
       <c r="B117" t="n">
-        <v>74710</v>
+        <v>74713</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15967,10 +15958,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252806</v>
+        <v>121252814</v>
       </c>
       <c r="B118" t="n">
-        <v>74522</v>
+        <v>78607</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15979,25 +15970,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -16007,10 +15998,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446038</v>
+        <v>446185</v>
       </c>
       <c r="R118" t="n">
-        <v>7026546</v>
+        <v>7026627</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16042,7 +16033,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16052,7 +16043,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16066,7 +16057,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -16081,7 +16072,7 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16099,10 +16090,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252826</v>
+        <v>121252804</v>
       </c>
       <c r="B119" t="n">
-        <v>78604</v>
+        <v>97111</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16111,25 +16102,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -16139,10 +16130,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446279</v>
+        <v>446013</v>
       </c>
       <c r="R119" t="n">
-        <v>7026520</v>
+        <v>7026514</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16174,7 +16165,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16184,7 +16175,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16198,22 +16189,12 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16231,10 +16212,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121252821</v>
+        <v>121252820</v>
       </c>
       <c r="B120" t="n">
-        <v>78604</v>
+        <v>74713</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16247,21 +16228,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -16271,10 +16252,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446282</v>
+        <v>446258</v>
       </c>
       <c r="R120" t="n">
-        <v>7026592</v>
+        <v>7026597</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16306,7 +16287,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -16316,7 +16297,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16330,7 +16311,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -16345,7 +16326,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16363,10 +16344,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121252800</v>
+        <v>121252808</v>
       </c>
       <c r="B121" t="n">
-        <v>57351</v>
+        <v>78641</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -16379,27 +16360,31 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -16408,10 +16393,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>446056</v>
+        <v>446038</v>
       </c>
       <c r="R121" t="n">
-        <v>7026521</v>
+        <v>7026546</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16443,7 +16428,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -16453,12 +16438,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16472,12 +16452,22 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16495,10 +16485,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252817</v>
+        <v>121252800</v>
       </c>
       <c r="B122" t="n">
-        <v>74694</v>
+        <v>57354</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -16507,38 +16497,43 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446209</v>
+        <v>446056</v>
       </c>
       <c r="R122" t="n">
-        <v>7026630</v>
+        <v>7026521</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16570,7 +16565,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16580,7 +16575,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16594,22 +16594,12 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16627,10 +16617,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252813</v>
+        <v>121252817</v>
       </c>
       <c r="B123" t="n">
-        <v>78604</v>
+        <v>74697</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16639,25 +16629,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16667,10 +16657,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446166</v>
+        <v>446209</v>
       </c>
       <c r="R123" t="n">
-        <v>7026698</v>
+        <v>7026630</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16702,7 +16692,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16712,7 +16702,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16741,7 +16731,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -16759,10 +16749,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252804</v>
+        <v>121252807</v>
       </c>
       <c r="B124" t="n">
-        <v>97108</v>
+        <v>78607</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16771,25 +16761,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -16799,10 +16789,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>446013</v>
+        <v>446038</v>
       </c>
       <c r="R124" t="n">
-        <v>7026514</v>
+        <v>7026546</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16834,7 +16824,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16844,7 +16834,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16858,12 +16848,22 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -16884,7 +16884,7 @@
         <v>121499846</v>
       </c>
       <c r="B125" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -3551,7 +3551,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121117063</v>
+        <v>121117416</v>
       </c>
       <c r="B23" t="n">
         <v>78607</v>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3596,14 +3596,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
+          <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446063</v>
+        <v>445930</v>
       </c>
       <c r="R23" t="n">
-        <v>7026497</v>
+        <v>7026585</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Minst 20, långa Gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3677,7 +3677,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121117416</v>
+        <v>121117224</v>
       </c>
       <c r="B24" t="n">
         <v>78607</v>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445930</v>
+        <v>446032</v>
       </c>
       <c r="R24" t="n">
-        <v>7026585</v>
+        <v>7026520</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3771,12 +3771,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 20, långa Gammal gran</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3920,7 +3915,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121117224</v>
+        <v>121117063</v>
       </c>
       <c r="B26" t="n">
         <v>78607</v>
@@ -3955,7 +3950,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3965,14 +3960,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svedaun, Svedaun, Jmt</t>
+          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446032</v>
+        <v>446063</v>
       </c>
       <c r="R26" t="n">
-        <v>7026520</v>
+        <v>7026497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4004,7 +3999,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4014,7 +4009,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121134865</v>
+        <v>121134870</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>91153</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4170,47 +4170,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446213</v>
+        <v>446262</v>
       </c>
       <c r="R28" t="n">
-        <v>7026555</v>
+        <v>7026488</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4242,7 +4233,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4252,7 +4243,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4266,7 +4257,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4281,7 +4272,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4299,10 +4290,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121134853</v>
+        <v>121134865</v>
       </c>
       <c r="B29" t="n">
-        <v>74704</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4311,38 +4302,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445965</v>
+        <v>446213</v>
       </c>
       <c r="R29" t="n">
-        <v>7026512</v>
+        <v>7026555</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (26 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4431,10 +4431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121134557</v>
+        <v>121134852</v>
       </c>
       <c r="B30" t="n">
-        <v>74704</v>
+        <v>90727</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4443,25 +4443,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>492</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446026</v>
+        <v>445963</v>
       </c>
       <c r="R30" t="n">
-        <v>7026520</v>
+        <v>7026504</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4501,22 +4501,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4530,22 +4530,22 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4556,17 +4556,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121132943</v>
+        <v>121134548</v>
       </c>
       <c r="B31" t="n">
-        <v>74713</v>
+        <v>88034</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4579,21 +4579,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446259</v>
+        <v>445938</v>
       </c>
       <c r="R31" t="n">
-        <v>7026469</v>
+        <v>7026514</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4633,12 +4633,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4652,7 +4662,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4667,7 +4677,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
+          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4678,17 +4688,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121134852</v>
+        <v>121134539</v>
       </c>
       <c r="B32" t="n">
-        <v>90727</v>
+        <v>74718</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4701,21 +4711,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4725,10 +4735,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445963</v>
+        <v>446088</v>
       </c>
       <c r="R32" t="n">
-        <v>7026504</v>
+        <v>7026528</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4755,22 +4765,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4784,7 +4794,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4799,7 +4809,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4810,17 +4820,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121134543</v>
+        <v>121134857</v>
       </c>
       <c r="B33" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4829,47 +4839,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446069</v>
+        <v>446075</v>
       </c>
       <c r="R33" t="n">
-        <v>7026527</v>
+        <v>7026515</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4896,27 +4897,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4930,12 +4926,22 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4946,17 +4952,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121134538</v>
+        <v>121134545</v>
       </c>
       <c r="B34" t="n">
-        <v>105188</v>
+        <v>78607</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4965,38 +4971,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446142</v>
+        <v>445987</v>
       </c>
       <c r="R34" t="n">
-        <v>7026514</v>
+        <v>7026510</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5028,7 +5043,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5038,7 +5053,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>10 bålar, den längsta 30 cm</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5055,9 +5075,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5075,10 +5105,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121134873</v>
+        <v>121132934</v>
       </c>
       <c r="B35" t="n">
-        <v>77544</v>
+        <v>78607</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5091,21 +5121,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5115,10 +5145,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446269</v>
+        <v>446253</v>
       </c>
       <c r="R35" t="n">
-        <v>7026478</v>
+        <v>7026514</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5145,22 +5175,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5174,7 +5194,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5189,7 +5209,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5207,10 +5227,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121134858</v>
+        <v>121134549</v>
       </c>
       <c r="B36" t="n">
-        <v>90731</v>
+        <v>74713</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5223,21 +5243,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5247,10 +5267,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446092</v>
+        <v>445936</v>
       </c>
       <c r="R36" t="n">
-        <v>7026520</v>
+        <v>7026522</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5277,22 +5297,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5306,7 +5326,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5321,7 +5341,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5332,17 +5352,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121132935</v>
+        <v>121134861</v>
       </c>
       <c r="B37" t="n">
-        <v>78607</v>
+        <v>77544</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5355,21 +5375,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5379,10 +5399,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446246</v>
+        <v>446197</v>
       </c>
       <c r="R37" t="n">
-        <v>7026518</v>
+        <v>7026538</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5409,12 +5429,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5428,7 +5458,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5443,7 +5473,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5461,10 +5491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121134862</v>
+        <v>121134535</v>
       </c>
       <c r="B38" t="n">
-        <v>74713</v>
+        <v>78770</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5473,38 +5503,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446197</v>
+        <v>446119</v>
       </c>
       <c r="R38" t="n">
-        <v>7026538</v>
+        <v>7026442</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5531,22 +5570,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Samma som sedd tidigare i år</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5560,7 +5604,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5575,7 +5619,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5586,17 +5630,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121134548</v>
+        <v>121132930</v>
       </c>
       <c r="B39" t="n">
-        <v>88034</v>
+        <v>77544</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5609,21 +5653,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5633,10 +5677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445938</v>
+        <v>446284</v>
       </c>
       <c r="R39" t="n">
-        <v>7026514</v>
+        <v>7026556</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5663,22 +5707,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5692,7 +5726,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5707,7 +5741,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran (17 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5718,17 +5752,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121134542</v>
+        <v>121132935</v>
       </c>
       <c r="B40" t="n">
-        <v>95645</v>
+        <v>78607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5741,21 +5775,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5765,10 +5799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446080</v>
+        <v>446246</v>
       </c>
       <c r="R40" t="n">
-        <v>7026521</v>
+        <v>7026518</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5795,22 +5829,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>17:04</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>17:04</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5824,7 +5848,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäck som slingrar sig</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5839,7 +5863,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>På mycket gammal granlåga # Picea abies</t>
+          <t>på död gren på gammal levande gran (32 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5850,17 +5874,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121132950</v>
+        <v>121134869</v>
       </c>
       <c r="B41" t="n">
-        <v>78770</v>
+        <v>90713</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5869,47 +5893,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446118</v>
+        <v>446262</v>
       </c>
       <c r="R41" t="n">
-        <v>7026441</v>
+        <v>7026488</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5936,17 +5951,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>1 bål</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5960,7 +5980,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5975,7 +5995,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5993,10 +6013,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121134537</v>
+        <v>121134544</v>
       </c>
       <c r="B42" t="n">
-        <v>74697</v>
+        <v>90713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6005,25 +6025,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6033,10 +6053,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446153</v>
+        <v>446005</v>
       </c>
       <c r="R42" t="n">
-        <v>7026500</v>
+        <v>7026502</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6068,7 +6088,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6078,7 +6098,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6097,17 +6117,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>På björkhögstubbe # Betula pubescens</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6125,7 +6145,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121132927</v>
+        <v>121134860</v>
       </c>
       <c r="B43" t="n">
         <v>78607</v>
@@ -6158,17 +6178,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446305</v>
+        <v>446170</v>
       </c>
       <c r="R43" t="n">
-        <v>7026607</v>
+        <v>7026558</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6195,17 +6224,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>60 cm lång bål</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6219,22 +6253,22 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6252,10 +6286,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121134859</v>
+        <v>121132950</v>
       </c>
       <c r="B44" t="n">
-        <v>74713</v>
+        <v>78770</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6264,38 +6298,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446158</v>
+        <v>446118</v>
       </c>
       <c r="R44" t="n">
-        <v>7026570</v>
+        <v>7026441</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6322,22 +6365,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:07</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:07</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1 bål</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6351,7 +6389,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6366,7 +6404,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6384,10 +6422,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121134860</v>
+        <v>121132926</v>
       </c>
       <c r="B45" t="n">
-        <v>78607</v>
+        <v>56566</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6396,47 +6434,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446170</v>
+        <v>446305</v>
       </c>
       <c r="R45" t="n">
-        <v>7026558</v>
+        <v>7026607</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6463,22 +6492,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>uppflog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6492,22 +6516,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6525,10 +6534,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121134552</v>
+        <v>121134542</v>
       </c>
       <c r="B46" t="n">
-        <v>77544</v>
+        <v>95645</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6541,21 +6550,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228579</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6565,10 +6574,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445924</v>
+        <v>446080</v>
       </c>
       <c r="R46" t="n">
-        <v>7026587</v>
+        <v>7026521</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6600,7 +6609,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6610,7 +6619,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6624,7 +6633,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6639,7 +6648,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På mycket gammal granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6657,10 +6666,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121132948</v>
+        <v>121134557</v>
       </c>
       <c r="B47" t="n">
-        <v>77544</v>
+        <v>74704</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6669,25 +6678,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>492</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6697,10 +6706,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>446111</v>
+        <v>446026</v>
       </c>
       <c r="R47" t="n">
-        <v>7026483</v>
+        <v>7026520</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6727,12 +6736,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6746,22 +6765,22 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6772,17 +6791,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121134541</v>
+        <v>121134855</v>
       </c>
       <c r="B48" t="n">
-        <v>74705</v>
+        <v>78607</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6795,21 +6814,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6819,10 +6838,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>446088</v>
+        <v>446045</v>
       </c>
       <c r="R48" t="n">
-        <v>7026528</v>
+        <v>7026526</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6849,22 +6868,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6878,7 +6897,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6893,7 +6912,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6904,17 +6923,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121132934</v>
+        <v>121134556</v>
       </c>
       <c r="B49" t="n">
-        <v>78607</v>
+        <v>74718</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6927,21 +6946,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6951,10 +6970,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446253</v>
+        <v>446026</v>
       </c>
       <c r="R49" t="n">
-        <v>7026514</v>
+        <v>7026520</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6981,12 +7000,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7000,22 +7029,22 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På gammal grov björkstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7026,14 +7055,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121134549</v>
+        <v>121132931</v>
       </c>
       <c r="B50" t="n">
         <v>74713</v>
@@ -7073,10 +7102,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445936</v>
+        <v>446284</v>
       </c>
       <c r="R50" t="n">
-        <v>7026522</v>
+        <v>7026556</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7103,22 +7132,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7132,7 +7151,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7147,7 +7166,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7158,17 +7177,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121134857</v>
+        <v>121134553</v>
       </c>
       <c r="B51" t="n">
-        <v>78607</v>
+        <v>74713</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7181,21 +7200,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7205,10 +7224,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446075</v>
+        <v>445925</v>
       </c>
       <c r="R51" t="n">
-        <v>7026515</v>
+        <v>7026580</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7235,22 +7254,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7264,7 +7283,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7279,7 +7298,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7290,17 +7309,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121134868</v>
+        <v>121134862</v>
       </c>
       <c r="B52" t="n">
-        <v>78607</v>
+        <v>74713</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7313,21 +7332,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7337,10 +7356,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446262</v>
+        <v>446197</v>
       </c>
       <c r="R52" t="n">
-        <v>7026488</v>
+        <v>7026538</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7372,7 +7391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7382,7 +7401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7396,7 +7415,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -7411,7 +7430,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7429,10 +7448,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121134863</v>
+        <v>121134851</v>
       </c>
       <c r="B53" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7445,21 +7464,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7469,10 +7488,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446203</v>
+        <v>445959</v>
       </c>
       <c r="R53" t="n">
-        <v>7026536</v>
+        <v>7026504</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7504,7 +7523,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7514,7 +7533,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7528,7 +7547,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -7543,7 +7562,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7561,10 +7580,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121134871</v>
+        <v>121134551</v>
       </c>
       <c r="B54" t="n">
-        <v>74525</v>
+        <v>78607</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7573,25 +7592,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7601,10 +7620,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446269</v>
+        <v>445899</v>
       </c>
       <c r="R54" t="n">
-        <v>7026478</v>
+        <v>7026589</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7631,22 +7650,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7660,7 +7679,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7675,7 +7694,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7686,17 +7705,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121132926</v>
+        <v>121132949</v>
       </c>
       <c r="B55" t="n">
-        <v>56566</v>
+        <v>78607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7705,38 +7724,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446305</v>
+        <v>446118</v>
       </c>
       <c r="R55" t="n">
-        <v>7026607</v>
+        <v>7026441</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7773,7 +7801,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>uppflog</t>
+          <t>7 bålar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7787,7 +7815,22 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7805,10 +7848,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121134544</v>
+        <v>121132944</v>
       </c>
       <c r="B56" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7821,21 +7864,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7845,10 +7888,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446005</v>
+        <v>446279</v>
       </c>
       <c r="R56" t="n">
-        <v>7026502</v>
+        <v>7026455</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7875,22 +7918,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>40 cm lång bål</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7904,22 +7942,22 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7930,17 +7968,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121132936</v>
+        <v>121134850</v>
       </c>
       <c r="B57" t="n">
-        <v>77544</v>
+        <v>91646</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7949,25 +7987,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7977,10 +8015,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446254</v>
+        <v>445960</v>
       </c>
       <c r="R57" t="n">
-        <v>7026486</v>
+        <v>7026492</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8007,12 +8045,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8026,22 +8074,12 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8059,7 +8097,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121134867</v>
+        <v>121132936</v>
       </c>
       <c r="B58" t="n">
         <v>77544</v>
@@ -8099,10 +8137,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446244</v>
+        <v>446254</v>
       </c>
       <c r="R58" t="n">
-        <v>7026516</v>
+        <v>7026486</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8129,22 +8167,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8158,7 +8186,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -8173,7 +8201,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (30 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8191,10 +8219,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121134540</v>
+        <v>121132927</v>
       </c>
       <c r="B59" t="n">
-        <v>74699</v>
+        <v>78607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8203,25 +8231,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8231,10 +8259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446088</v>
+        <v>446305</v>
       </c>
       <c r="R59" t="n">
-        <v>7026528</v>
+        <v>7026607</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8261,22 +8289,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>60 cm lång bål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8285,28 +8308,27 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>på stam av levande gammal tall (21 cm dbh, ca 180 år gammal) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8317,14 +8339,14 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121132928</v>
+        <v>121134878</v>
       </c>
       <c r="B60" t="n">
         <v>78607</v>
@@ -8359,7 +8381,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8373,10 +8395,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446290</v>
+        <v>446262</v>
       </c>
       <c r="R60" t="n">
-        <v>7026577</v>
+        <v>7026436</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8403,17 +8425,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>20 bålar</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8427,7 +8454,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>i gammal gles barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8442,7 +8469,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
+          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8460,7 +8487,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121134855</v>
+        <v>121134868</v>
       </c>
       <c r="B61" t="n">
         <v>78607</v>
@@ -8500,10 +8527,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>446045</v>
+        <v>446262</v>
       </c>
       <c r="R61" t="n">
-        <v>7026526</v>
+        <v>7026488</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8535,7 +8562,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8545,7 +8572,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8559,7 +8586,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8574,7 +8601,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8592,10 +8619,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121132945</v>
+        <v>121134871</v>
       </c>
       <c r="B62" t="n">
-        <v>90731</v>
+        <v>74525</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8604,25 +8631,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6428</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8632,10 +8659,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>446220</v>
+        <v>446269</v>
       </c>
       <c r="R62" t="n">
-        <v>7026528</v>
+        <v>7026478</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8662,12 +8689,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8681,7 +8718,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8696,7 +8733,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>på gammal dubbelgran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8714,10 +8751,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121134878</v>
+        <v>121134543</v>
       </c>
       <c r="B63" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8726,35 +8763,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8763,10 +8800,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>446262</v>
+        <v>446069</v>
       </c>
       <c r="R63" t="n">
-        <v>7026436</v>
+        <v>7026527</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8793,22 +8830,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>12 gamla blomställningar, tät matta av skott inom 1,5x0,5 m</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8822,22 +8864,12 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog vid bäck som slingrar sig</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>På gammal gran (11 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8848,17 +8880,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121134880</v>
+        <v>121134537</v>
       </c>
       <c r="B64" t="n">
-        <v>56566</v>
+        <v>74697</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8871,43 +8903,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>6439</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>446259</v>
+        <v>446153</v>
       </c>
       <c r="R64" t="n">
-        <v>7026406</v>
+        <v>7026500</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8934,27 +8957,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Satt i gammal gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8968,7 +8986,22 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8979,17 +9012,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121134864</v>
+        <v>121134880</v>
       </c>
       <c r="B65" t="n">
-        <v>74713</v>
+        <v>56566</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8998,38 +9031,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>446203</v>
+        <v>446259</v>
       </c>
       <c r="R65" t="n">
-        <v>7026536</v>
+        <v>7026406</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9061,7 +9103,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9071,7 +9113,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Satt i gammal gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9085,22 +9132,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9118,10 +9150,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121134875</v>
+        <v>121134555</v>
       </c>
       <c r="B66" t="n">
-        <v>74713</v>
+        <v>90678</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9130,25 +9162,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9158,10 +9190,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>446269</v>
+        <v>446030</v>
       </c>
       <c r="R66" t="n">
-        <v>7026478</v>
+        <v>7026523</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9188,22 +9220,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9217,7 +9249,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9232,7 +9264,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9243,17 +9275,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121132930</v>
+        <v>121132945</v>
       </c>
       <c r="B67" t="n">
-        <v>77544</v>
+        <v>90731</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9266,21 +9298,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9290,10 +9322,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>446284</v>
+        <v>446220</v>
       </c>
       <c r="R67" t="n">
-        <v>7026556</v>
+        <v>7026528</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9354,7 +9386,7 @@
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>på gammal dubbelgran # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9372,7 +9404,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121132931</v>
+        <v>121134864</v>
       </c>
       <c r="B68" t="n">
         <v>74713</v>
@@ -9412,10 +9444,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>446284</v>
+        <v>446203</v>
       </c>
       <c r="R68" t="n">
-        <v>7026556</v>
+        <v>7026536</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9442,12 +9474,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9461,7 +9503,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9476,7 +9518,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9494,10 +9536,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121134553</v>
+        <v>121134867</v>
       </c>
       <c r="B69" t="n">
-        <v>74713</v>
+        <v>77544</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9510,21 +9552,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9534,10 +9576,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445925</v>
+        <v>446244</v>
       </c>
       <c r="R69" t="n">
-        <v>7026580</v>
+        <v>7026516</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9564,22 +9606,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9593,7 +9635,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9608,7 +9650,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9619,17 +9661,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121134849</v>
+        <v>121134877</v>
       </c>
       <c r="B70" t="n">
-        <v>91153</v>
+        <v>77544</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9638,25 +9680,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>228579</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9666,10 +9708,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445948</v>
+        <v>446271</v>
       </c>
       <c r="R70" t="n">
-        <v>7026487</v>
+        <v>7026473</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9701,7 +9743,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9711,7 +9753,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9725,7 +9767,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -9740,7 +9782,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>På grov granlåga # Picea abies</t>
+          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9758,10 +9800,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121134545</v>
+        <v>121132943</v>
       </c>
       <c r="B71" t="n">
-        <v>78607</v>
+        <v>74713</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9774,43 +9816,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445987</v>
+        <v>446259</v>
       </c>
       <c r="R71" t="n">
-        <v>7026510</v>
+        <v>7026469</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9837,27 +9870,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>10 bålar, den längsta 30 cm</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9871,7 +9889,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9886,7 +9904,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (20 cm dbh, ca 160 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9897,17 +9915,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121134539</v>
+        <v>121132932</v>
       </c>
       <c r="B72" t="n">
-        <v>74718</v>
+        <v>78607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9920,21 +9938,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9944,10 +9962,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>446088</v>
+        <v>446284</v>
       </c>
       <c r="R72" t="n">
-        <v>7026528</v>
+        <v>7026556</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9974,22 +9992,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10003,7 +10011,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -10018,7 +10026,7 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10029,17 +10037,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121134536</v>
+        <v>121134863</v>
       </c>
       <c r="B73" t="n">
-        <v>90709</v>
+        <v>78607</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10052,21 +10060,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10076,10 +10084,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>446164</v>
+        <v>446203</v>
       </c>
       <c r="R73" t="n">
-        <v>7026463</v>
+        <v>7026536</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10106,22 +10114,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10135,7 +10143,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10150,7 +10158,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>På död gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (18 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10161,17 +10169,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121134555</v>
+        <v>121134550</v>
       </c>
       <c r="B74" t="n">
-        <v>90678</v>
+        <v>90484</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10184,21 +10192,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10208,10 +10216,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>446030</v>
+        <v>445911</v>
       </c>
       <c r="R74" t="n">
-        <v>7026523</v>
+        <v>7026564</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10243,7 +10251,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10253,7 +10261,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10267,22 +10275,12 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal barrblandskog, sumpskog/myr</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>På gammal död gran (7 cm dbh, ca 130 år gammal ) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10300,10 +10298,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121134550</v>
+        <v>121134546</v>
       </c>
       <c r="B75" t="n">
-        <v>90484</v>
+        <v>77544</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10312,25 +10310,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3215</v>
+        <v>228579</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10340,10 +10338,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445911</v>
+        <v>445987</v>
       </c>
       <c r="R75" t="n">
-        <v>7026564</v>
+        <v>7026512</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10375,7 +10373,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10385,7 +10383,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10399,12 +10397,22 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog, sumpskog/myr</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10422,10 +10430,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121132932</v>
+        <v>121134873</v>
       </c>
       <c r="B76" t="n">
-        <v>78607</v>
+        <v>77544</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10438,21 +10446,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10462,10 +10470,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>446284</v>
+        <v>446269</v>
       </c>
       <c r="R76" t="n">
-        <v>7026556</v>
+        <v>7026478</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10492,12 +10500,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10511,7 +10529,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
@@ -10526,7 +10544,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>på gammal gran (13 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10544,10 +10562,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121134558</v>
+        <v>121134541</v>
       </c>
       <c r="B77" t="n">
-        <v>78607</v>
+        <v>74705</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10560,21 +10578,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10584,10 +10602,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>446050</v>
+        <v>446088</v>
       </c>
       <c r="R77" t="n">
-        <v>7026501</v>
+        <v>7026528</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10619,7 +10637,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10629,7 +10647,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10643,7 +10661,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>I gles gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -10658,7 +10676,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10676,10 +10694,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121132944</v>
+        <v>121134552</v>
       </c>
       <c r="B78" t="n">
-        <v>78607</v>
+        <v>77544</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10692,21 +10710,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10716,10 +10734,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>446279</v>
+        <v>445924</v>
       </c>
       <c r="R78" t="n">
-        <v>7026455</v>
+        <v>7026587</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10746,17 +10764,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>40 cm lång bål</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10770,22 +10793,22 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>på gren på gammal död tall (22 cm dbh) # Pinus sylvestris</t>
+          <t>På bark på stam av levande gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10796,17 +10819,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121132949</v>
+        <v>121134540</v>
       </c>
       <c r="B79" t="n">
-        <v>78607</v>
+        <v>74699</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10815,47 +10838,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>446118</v>
+        <v>446088</v>
       </c>
       <c r="R79" t="n">
-        <v>7026441</v>
+        <v>7026528</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10882,17 +10896,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>7 bålar</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10901,12 +10920,13 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -10921,7 +10941,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10932,17 +10952,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121134546</v>
+        <v>121134558</v>
       </c>
       <c r="B80" t="n">
-        <v>77544</v>
+        <v>78607</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10955,21 +10975,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10979,10 +10999,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445987</v>
+        <v>446050</v>
       </c>
       <c r="R80" t="n">
-        <v>7026512</v>
+        <v>7026501</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11014,7 +11034,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11024,7 +11044,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11038,7 +11058,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gles gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
@@ -11053,7 +11073,7 @@
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (45 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11071,10 +11091,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121134869</v>
+        <v>121134858</v>
       </c>
       <c r="B81" t="n">
-        <v>90713</v>
+        <v>90731</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11087,21 +11107,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11111,10 +11131,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>446262</v>
+        <v>446092</v>
       </c>
       <c r="R81" t="n">
-        <v>7026488</v>
+        <v>7026520</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11146,7 +11166,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11156,7 +11176,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11170,7 +11190,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -11185,7 +11205,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11203,10 +11223,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121134870</v>
+        <v>121134875</v>
       </c>
       <c r="B82" t="n">
-        <v>91153</v>
+        <v>74713</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11215,25 +11235,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11243,10 +11263,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>446262</v>
+        <v>446269</v>
       </c>
       <c r="R82" t="n">
-        <v>7026488</v>
+        <v>7026478</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11278,7 +11298,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11288,7 +11308,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11317,7 +11337,7 @@
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11335,10 +11355,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121134851</v>
+        <v>121134538</v>
       </c>
       <c r="B83" t="n">
-        <v>90713</v>
+        <v>105188</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11347,25 +11367,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -11375,10 +11395,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445959</v>
+        <v>446142</v>
       </c>
       <c r="R83" t="n">
-        <v>7026504</v>
+        <v>7026514</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11405,22 +11425,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11434,22 +11454,12 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11460,17 +11470,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121134535</v>
+        <v>121132948</v>
       </c>
       <c r="B84" t="n">
-        <v>78770</v>
+        <v>77544</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11479,47 +11489,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>446119</v>
+        <v>446111</v>
       </c>
       <c r="R84" t="n">
-        <v>7026442</v>
+        <v>7026483</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11546,27 +11547,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Samma som sedd tidigare i år</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11580,7 +11566,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11595,7 +11581,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>På gren på gammal gran (20 cm dbh, ca 170 år) # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11606,17 +11592,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121134850</v>
+        <v>121134536</v>
       </c>
       <c r="B85" t="n">
-        <v>91646</v>
+        <v>90709</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11625,25 +11611,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11653,10 +11639,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445960</v>
+        <v>446164</v>
       </c>
       <c r="R85" t="n">
-        <v>7026492</v>
+        <v>7026463</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11683,22 +11669,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11712,12 +11698,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>I gammal granskog med rikligt med lågor, bröt</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11728,17 +11724,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121134551</v>
+        <v>121134849</v>
       </c>
       <c r="B86" t="n">
-        <v>78607</v>
+        <v>91153</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11747,25 +11743,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11775,10 +11771,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445899</v>
+        <v>445948</v>
       </c>
       <c r="R86" t="n">
-        <v>7026589</v>
+        <v>7026487</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11805,22 +11801,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11834,7 +11830,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -11849,7 +11845,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På grov granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11860,17 +11856,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121134877</v>
+        <v>121134866</v>
       </c>
       <c r="B87" t="n">
-        <v>77544</v>
+        <v>90731</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11883,21 +11879,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11907,10 +11903,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>446271</v>
+        <v>446218</v>
       </c>
       <c r="R87" t="n">
-        <v>7026473</v>
+        <v>7026544</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11942,7 +11938,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11952,7 +11948,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11966,7 +11962,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -11981,7 +11977,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>På gammal gran (23 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11999,10 +11995,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121134861</v>
+        <v>121134859</v>
       </c>
       <c r="B88" t="n">
-        <v>77544</v>
+        <v>74713</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12015,21 +12011,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -12039,10 +12035,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>446197</v>
+        <v>446158</v>
       </c>
       <c r="R88" t="n">
-        <v>7026538</v>
+        <v>7026570</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12074,7 +12070,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12084,7 +12080,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12113,7 +12109,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 130 år) # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12131,10 +12127,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121134556</v>
+        <v>121134853</v>
       </c>
       <c r="B89" t="n">
-        <v>74718</v>
+        <v>74704</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12143,25 +12139,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1467</v>
+        <v>492</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12171,10 +12167,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>446026</v>
+        <v>445965</v>
       </c>
       <c r="R89" t="n">
-        <v>7026520</v>
+        <v>7026512</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12201,22 +12197,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12230,22 +12226,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med rikligt med lågor, bröt</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>På gammal grov björkstubbe # Betula pubescens</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12256,17 +12252,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121134866</v>
+        <v>121132928</v>
       </c>
       <c r="B90" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12279,34 +12275,43 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>446218</v>
+        <v>446290</v>
       </c>
       <c r="R90" t="n">
-        <v>7026544</v>
+        <v>7026577</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12333,22 +12338,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>20 bålar</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (12 cm dbh, ca 130 år) # Picea abies</t>
+          <t>på grenar på gammal gran (24 cm dbh, ca 180 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12395,10 +12395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252802</v>
+        <v>121252804</v>
       </c>
       <c r="B91" t="n">
-        <v>90709</v>
+        <v>97111</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12407,25 +12407,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1108</v>
+        <v>221063</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12435,7 +12435,7 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445982</v>
+        <v>446013</v>
       </c>
       <c r="R91" t="n">
         <v>7026514</v>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12497,19 +12497,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12527,10 +12517,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252837</v>
+        <v>121252833</v>
       </c>
       <c r="B92" t="n">
-        <v>77544</v>
+        <v>78607</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12543,34 +12533,43 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>446201</v>
+        <v>446233</v>
       </c>
       <c r="R92" t="n">
-        <v>7026410</v>
+        <v>7026512</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12602,7 +12601,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12612,7 +12611,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12626,7 +12630,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -12641,7 +12645,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12659,10 +12663,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252826</v>
+        <v>121252800</v>
       </c>
       <c r="B93" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12675,34 +12679,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>446279</v>
+        <v>446056</v>
       </c>
       <c r="R93" t="n">
-        <v>7026520</v>
+        <v>7026521</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12734,7 +12743,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12744,7 +12753,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12758,22 +12772,12 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12791,7 +12795,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121252818</v>
+        <v>121252806</v>
       </c>
       <c r="B94" t="n">
         <v>74525</v>
@@ -12831,10 +12835,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>446209</v>
+        <v>446038</v>
       </c>
       <c r="R94" t="n">
-        <v>7026630</v>
+        <v>7026546</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12866,7 +12870,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12876,7 +12880,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12890,7 +12894,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -12905,7 +12909,7 @@
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12923,10 +12927,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252833</v>
+        <v>121252801</v>
       </c>
       <c r="B95" t="n">
-        <v>78607</v>
+        <v>91396</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12935,47 +12939,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>446233</v>
+        <v>445969</v>
       </c>
       <c r="R95" t="n">
-        <v>7026512</v>
+        <v>7026495</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13007,7 +13002,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13017,12 +13012,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13036,7 +13026,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -13051,7 +13041,7 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13069,10 +13059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252824</v>
+        <v>121252820</v>
       </c>
       <c r="B96" t="n">
-        <v>77544</v>
+        <v>74713</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13085,21 +13075,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -13109,10 +13099,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446278</v>
+        <v>446258</v>
       </c>
       <c r="R96" t="n">
-        <v>7026536</v>
+        <v>7026597</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13144,7 +13134,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13154,7 +13144,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13168,7 +13158,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -13183,7 +13173,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13201,10 +13191,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252838</v>
+        <v>121252839</v>
       </c>
       <c r="B97" t="n">
-        <v>74713</v>
+        <v>90731</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13217,21 +13207,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -13241,10 +13231,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446201</v>
+        <v>446209</v>
       </c>
       <c r="R97" t="n">
-        <v>7026410</v>
+        <v>7026395</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13276,7 +13266,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13286,7 +13276,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13300,7 +13290,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -13315,7 +13305,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13333,10 +13323,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252806</v>
+        <v>121252838</v>
       </c>
       <c r="B98" t="n">
-        <v>74525</v>
+        <v>74713</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13345,25 +13335,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6428</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13373,10 +13363,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446038</v>
+        <v>446201</v>
       </c>
       <c r="R98" t="n">
-        <v>7026546</v>
+        <v>7026410</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13408,7 +13398,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13418,7 +13408,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13432,7 +13422,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -13447,7 +13437,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13465,7 +13455,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121252813</v>
+        <v>121252822</v>
       </c>
       <c r="B99" t="n">
         <v>78607</v>
@@ -13505,10 +13495,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>446166</v>
+        <v>446284</v>
       </c>
       <c r="R99" t="n">
-        <v>7026698</v>
+        <v>7026552</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13540,7 +13530,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13550,7 +13540,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13564,7 +13554,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -13579,7 +13569,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13597,10 +13587,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121252840</v>
+        <v>121252818</v>
       </c>
       <c r="B100" t="n">
-        <v>77544</v>
+        <v>74525</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13609,25 +13599,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13640,7 +13630,7 @@
         <v>446209</v>
       </c>
       <c r="R100" t="n">
-        <v>7026394</v>
+        <v>7026630</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13672,7 +13662,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13682,7 +13672,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13696,7 +13686,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -13711,7 +13701,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13729,7 +13719,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252822</v>
+        <v>121252813</v>
       </c>
       <c r="B101" t="n">
         <v>78607</v>
@@ -13769,10 +13759,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>446284</v>
+        <v>446166</v>
       </c>
       <c r="R101" t="n">
-        <v>7026552</v>
+        <v>7026698</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13804,7 +13794,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13814,7 +13804,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13828,7 +13818,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13843,7 +13833,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13861,10 +13851,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121252803</v>
+        <v>121252817</v>
       </c>
       <c r="B102" t="n">
-        <v>105188</v>
+        <v>74697</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13877,21 +13867,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221725</v>
+        <v>6439</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13901,10 +13891,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>446013</v>
+        <v>446209</v>
       </c>
       <c r="R102" t="n">
-        <v>7026516</v>
+        <v>7026630</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13936,7 +13926,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13946,7 +13936,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13960,12 +13950,22 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13983,7 +13983,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252823</v>
+        <v>121252807</v>
       </c>
       <c r="B103" t="n">
         <v>78607</v>
@@ -14023,10 +14023,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>446274</v>
+        <v>446038</v>
       </c>
       <c r="R103" t="n">
-        <v>7026540</v>
+        <v>7026546</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14115,10 +14115,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121252801</v>
+        <v>121252830</v>
       </c>
       <c r="B104" t="n">
-        <v>91396</v>
+        <v>74713</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14127,25 +14127,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -14155,10 +14155,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445969</v>
+        <v>446252</v>
       </c>
       <c r="R104" t="n">
-        <v>7026495</v>
+        <v>7026536</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14190,7 +14190,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14247,10 +14247,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252839</v>
+        <v>121252808</v>
       </c>
       <c r="B105" t="n">
-        <v>90731</v>
+        <v>78641</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14263,34 +14263,43 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>446209</v>
+        <v>446038</v>
       </c>
       <c r="R105" t="n">
-        <v>7026395</v>
+        <v>7026546</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14322,7 +14331,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14332,7 +14341,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14346,7 +14355,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -14361,7 +14370,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14379,10 +14388,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121252825</v>
+        <v>121252836</v>
       </c>
       <c r="B106" t="n">
-        <v>78863</v>
+        <v>78607</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14391,25 +14400,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -14419,10 +14428,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>446278</v>
+        <v>446201</v>
       </c>
       <c r="R106" t="n">
-        <v>7026536</v>
+        <v>7026410</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14454,7 +14463,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14464,7 +14473,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14478,7 +14487,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -14493,7 +14502,7 @@
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14511,10 +14520,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121252811</v>
+        <v>121252812</v>
       </c>
       <c r="B107" t="n">
-        <v>90709</v>
+        <v>78607</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14527,21 +14536,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -14551,10 +14560,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>446106</v>
+        <v>446185</v>
       </c>
       <c r="R107" t="n">
-        <v>7026528</v>
+        <v>7026655</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14586,7 +14595,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14596,7 +14605,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14610,7 +14619,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -14625,7 +14634,7 @@
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14643,10 +14652,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252810</v>
+        <v>121252811</v>
       </c>
       <c r="B108" t="n">
-        <v>74699</v>
+        <v>90709</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14655,25 +14664,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>306</v>
+        <v>1108</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14683,10 +14692,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>446089</v>
+        <v>446106</v>
       </c>
       <c r="R108" t="n">
-        <v>7026536</v>
+        <v>7026528</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14718,7 +14727,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14728,7 +14737,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14737,13 +14746,12 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal granskog</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -14758,7 +14766,7 @@
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14776,7 +14784,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252821</v>
+        <v>121252814</v>
       </c>
       <c r="B109" t="n">
         <v>78607</v>
@@ -14816,10 +14824,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446282</v>
+        <v>446185</v>
       </c>
       <c r="R109" t="n">
-        <v>7026592</v>
+        <v>7026627</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14851,7 +14859,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14861,7 +14869,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14875,7 +14883,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -14890,7 +14898,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14908,7 +14916,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252819</v>
+        <v>121252837</v>
       </c>
       <c r="B110" t="n">
         <v>77544</v>
@@ -14948,10 +14956,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>446258</v>
+        <v>446201</v>
       </c>
       <c r="R110" t="n">
-        <v>7026597</v>
+        <v>7026410</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14983,7 +14991,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14993,7 +15001,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -15022,7 +15030,7 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15040,10 +15048,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252812</v>
+        <v>121252840</v>
       </c>
       <c r="B111" t="n">
-        <v>78607</v>
+        <v>77544</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15056,21 +15064,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -15080,10 +15088,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446185</v>
+        <v>446209</v>
       </c>
       <c r="R111" t="n">
-        <v>7026655</v>
+        <v>7026394</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15115,7 +15123,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15125,7 +15133,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15139,7 +15147,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -15154,7 +15162,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15172,10 +15180,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121252809</v>
+        <v>121252803</v>
       </c>
       <c r="B112" t="n">
-        <v>77544</v>
+        <v>105188</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15184,25 +15192,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -15212,10 +15220,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>446044</v>
+        <v>446013</v>
       </c>
       <c r="R112" t="n">
-        <v>7026549</v>
+        <v>7026516</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15247,7 +15255,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -15257,7 +15265,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15271,22 +15279,12 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15304,10 +15302,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121252815</v>
+        <v>121252825</v>
       </c>
       <c r="B113" t="n">
-        <v>57507</v>
+        <v>78863</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15316,47 +15314,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103021</v>
+        <v>6459</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>446189</v>
+        <v>446278</v>
       </c>
       <c r="R113" t="n">
-        <v>7026651</v>
+        <v>7026536</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15388,7 +15377,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -15398,7 +15387,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15412,7 +15401,22 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15430,10 +15434,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121252827</v>
+        <v>121252819</v>
       </c>
       <c r="B114" t="n">
-        <v>78607</v>
+        <v>77544</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -15446,21 +15450,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -15470,10 +15474,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>446252</v>
+        <v>446258</v>
       </c>
       <c r="R114" t="n">
-        <v>7026536</v>
+        <v>7026597</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15505,7 +15509,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -15515,7 +15519,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15529,7 +15533,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -15544,7 +15548,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15562,10 +15566,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252836</v>
+        <v>121252810</v>
       </c>
       <c r="B115" t="n">
-        <v>78607</v>
+        <v>74699</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15574,25 +15578,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15602,10 +15606,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446201</v>
+        <v>446089</v>
       </c>
       <c r="R115" t="n">
-        <v>7026410</v>
+        <v>7026536</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15637,7 +15641,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15647,7 +15651,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15656,6 +15660,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -15676,7 +15681,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15694,10 +15699,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252835</v>
+        <v>121252823</v>
       </c>
       <c r="B116" t="n">
-        <v>77991</v>
+        <v>78607</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15710,21 +15715,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15734,10 +15739,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446209</v>
+        <v>446274</v>
       </c>
       <c r="R116" t="n">
-        <v>7026444</v>
+        <v>7026540</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15769,7 +15774,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15779,7 +15784,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15793,22 +15798,22 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>I gammal sumpskog/myr</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15826,10 +15831,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252830</v>
+        <v>121252835</v>
       </c>
       <c r="B117" t="n">
-        <v>74713</v>
+        <v>77991</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15842,21 +15847,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15866,10 +15871,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446252</v>
+        <v>446209</v>
       </c>
       <c r="R117" t="n">
-        <v>7026536</v>
+        <v>7026444</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15901,7 +15906,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15911,7 +15916,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15925,22 +15930,22 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal sumpskog/myr</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15958,10 +15963,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252814</v>
+        <v>121252815</v>
       </c>
       <c r="B118" t="n">
-        <v>78607</v>
+        <v>57507</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15974,34 +15979,43 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446185</v>
+        <v>446189</v>
       </c>
       <c r="R118" t="n">
-        <v>7026627</v>
+        <v>7026651</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16033,7 +16047,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16043,7 +16057,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16058,21 +16072,6 @@
       <c r="AI118" t="inlineStr">
         <is>
           <t>I gammal gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16090,10 +16089,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252804</v>
+        <v>121252809</v>
       </c>
       <c r="B119" t="n">
-        <v>97111</v>
+        <v>77544</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16102,25 +16101,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221063</v>
+        <v>228579</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -16130,10 +16129,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446013</v>
+        <v>446044</v>
       </c>
       <c r="R119" t="n">
-        <v>7026514</v>
+        <v>7026549</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16165,7 +16164,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16175,7 +16174,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16189,12 +16188,22 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16212,10 +16221,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121252820</v>
+        <v>121252826</v>
       </c>
       <c r="B120" t="n">
-        <v>74713</v>
+        <v>78607</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16228,21 +16237,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -16252,10 +16261,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446258</v>
+        <v>446279</v>
       </c>
       <c r="R120" t="n">
-        <v>7026597</v>
+        <v>7026520</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16287,7 +16296,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -16297,7 +16306,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16311,7 +16320,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -16326,7 +16335,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16344,10 +16353,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121252808</v>
+        <v>121252821</v>
       </c>
       <c r="B121" t="n">
-        <v>78641</v>
+        <v>78607</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -16360,43 +16369,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>446038</v>
+        <v>446282</v>
       </c>
       <c r="R121" t="n">
-        <v>7026546</v>
+        <v>7026592</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16452,7 +16452,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16485,10 +16485,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252800</v>
+        <v>121252824</v>
       </c>
       <c r="B122" t="n">
-        <v>57354</v>
+        <v>77544</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -16501,39 +16501,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446056</v>
+        <v>446278</v>
       </c>
       <c r="R122" t="n">
-        <v>7026521</v>
+        <v>7026536</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16565,7 +16560,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16575,12 +16570,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16594,12 +16584,22 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16617,10 +16617,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252817</v>
+        <v>121252802</v>
       </c>
       <c r="B123" t="n">
-        <v>74697</v>
+        <v>90709</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16629,25 +16629,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16657,10 +16657,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446209</v>
+        <v>445982</v>
       </c>
       <c r="R123" t="n">
-        <v>7026630</v>
+        <v>7026514</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -16749,7 +16749,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252807</v>
+        <v>121252827</v>
       </c>
       <c r="B124" t="n">
         <v>78607</v>
@@ -16789,10 +16789,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>446038</v>
+        <v>446252</v>
       </c>
       <c r="R124" t="n">
-        <v>7026546</v>
+        <v>7026536</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -4827,10 +4827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121134857</v>
+        <v>121134549</v>
       </c>
       <c r="B33" t="n">
-        <v>78607</v>
+        <v>74713</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4843,21 +4843,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446075</v>
+        <v>445936</v>
       </c>
       <c r="R33" t="n">
-        <v>7026515</v>
+        <v>7026522</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4897,22 +4897,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4952,14 +4952,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121134545</v>
+        <v>121134857</v>
       </c>
       <c r="B34" t="n">
         <v>78607</v>
@@ -4992,26 +4992,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445987</v>
+        <v>446075</v>
       </c>
       <c r="R34" t="n">
-        <v>7026510</v>
+        <v>7026515</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5038,27 +5029,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>10 bålar, den längsta 30 cm</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5072,7 +5058,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5087,7 +5073,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>På gamla döda granar # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5098,14 +5084,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121132934</v>
+        <v>121134545</v>
       </c>
       <c r="B35" t="n">
         <v>78607</v>
@@ -5138,17 +5124,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446253</v>
+        <v>445987</v>
       </c>
       <c r="R35" t="n">
-        <v>7026514</v>
+        <v>7026510</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5175,12 +5170,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>10 bålar, den längsta 30 cm</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5194,7 +5204,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5209,7 +5219,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
+          <t>På gamla döda granar # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5220,17 +5230,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121134549</v>
+        <v>121132934</v>
       </c>
       <c r="B36" t="n">
-        <v>74713</v>
+        <v>78607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5243,21 +5253,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5267,10 +5277,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445936</v>
+        <v>446253</v>
       </c>
       <c r="R36" t="n">
-        <v>7026522</v>
+        <v>7026514</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5297,22 +5307,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>på grenar på gammal död gran (30 cm dbh, ca 170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -6286,10 +6286,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121132950</v>
+        <v>121132926</v>
       </c>
       <c r="B44" t="n">
-        <v>78770</v>
+        <v>56566</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6298,47 +6298,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1249</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446118</v>
+        <v>446305</v>
       </c>
       <c r="R44" t="n">
-        <v>7026441</v>
+        <v>7026607</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6375,7 +6366,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1 bål</t>
+          <t>uppflog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6389,22 +6380,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
+          <t>i gammal sumpig och dikad barrblandskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6422,10 +6398,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121132926</v>
+        <v>121132950</v>
       </c>
       <c r="B45" t="n">
-        <v>56566</v>
+        <v>78770</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6434,38 +6410,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>1249</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446305</v>
+        <v>446118</v>
       </c>
       <c r="R45" t="n">
-        <v>7026607</v>
+        <v>7026441</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6502,7 +6487,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>uppflog</t>
+          <t>1 bål</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6516,7 +6501,22 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>i gammal sumpig och dikad barrblandskog</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>på bark på död grankvist på gammal gran (170 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -10826,10 +10826,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121134540</v>
+        <v>121134558</v>
       </c>
       <c r="B79" t="n">
-        <v>74699</v>
+        <v>78607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10838,25 +10838,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>446088</v>
+        <v>446050</v>
       </c>
       <c r="R79" t="n">
-        <v>7026528</v>
+        <v>7026501</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10920,13 +10920,12 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gles gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -10941,7 +10940,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>På gammal grov granhögstubbe # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10959,10 +10958,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121134558</v>
+        <v>121134875</v>
       </c>
       <c r="B80" t="n">
-        <v>78607</v>
+        <v>74713</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10975,21 +10974,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10999,10 +10998,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>446050</v>
+        <v>446269</v>
       </c>
       <c r="R80" t="n">
-        <v>7026501</v>
+        <v>7026478</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11029,22 +11028,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11058,7 +11057,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>I gles gammal gransumpskog</t>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
@@ -11073,7 +11072,7 @@
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11084,17 +11083,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121134858</v>
+        <v>121132948</v>
       </c>
       <c r="B81" t="n">
-        <v>90731</v>
+        <v>77544</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11107,21 +11106,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11131,10 +11130,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>446092</v>
+        <v>446111</v>
       </c>
       <c r="R81" t="n">
-        <v>7026520</v>
+        <v>7026483</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11161,22 +11160,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11190,7 +11179,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>I gammal granskog med tall och glasbjörk</t>
+          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -11205,7 +11194,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11223,10 +11212,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121134875</v>
+        <v>121134540</v>
       </c>
       <c r="B82" t="n">
-        <v>74713</v>
+        <v>74699</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11235,25 +11224,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11263,10 +11252,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>446269</v>
+        <v>446088</v>
       </c>
       <c r="R82" t="n">
-        <v>7026478</v>
+        <v>7026528</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11293,22 +11282,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11317,12 +11306,13 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog med tall och glasbjörk</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -11337,7 +11327,7 @@
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år) # Picea abies</t>
+          <t>På gammal grov granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11348,17 +11338,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121134538</v>
+        <v>121134858</v>
       </c>
       <c r="B83" t="n">
-        <v>105188</v>
+        <v>90731</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11367,25 +11357,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -11395,10 +11385,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>446142</v>
+        <v>446092</v>
       </c>
       <c r="R83" t="n">
-        <v>7026514</v>
+        <v>7026520</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11425,22 +11415,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11454,12 +11444,22 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11470,17 +11470,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121132948</v>
+        <v>121134538</v>
       </c>
       <c r="B84" t="n">
-        <v>77544</v>
+        <v>105188</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11489,25 +11489,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11517,10 +11517,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>446111</v>
+        <v>446142</v>
       </c>
       <c r="R84" t="n">
-        <v>7026483</v>
+        <v>7026514</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11547,12 +11547,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11566,22 +11576,12 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>i gammal dikad granskog med inslag av tall och glasbjörk.</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (25 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -12927,10 +12927,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252801</v>
+        <v>121252820</v>
       </c>
       <c r="B95" t="n">
-        <v>91396</v>
+        <v>74713</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12939,25 +12939,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445969</v>
+        <v>446258</v>
       </c>
       <c r="R95" t="n">
-        <v>7026495</v>
+        <v>7026597</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13059,7 +13059,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252820</v>
+        <v>121252838</v>
       </c>
       <c r="B96" t="n">
         <v>74713</v>
@@ -13099,10 +13099,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446258</v>
+        <v>446201</v>
       </c>
       <c r="R96" t="n">
-        <v>7026597</v>
+        <v>7026410</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13191,10 +13191,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252839</v>
+        <v>121252801</v>
       </c>
       <c r="B97" t="n">
-        <v>90731</v>
+        <v>91396</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13203,25 +13203,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -13231,10 +13231,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446209</v>
+        <v>445969</v>
       </c>
       <c r="R97" t="n">
-        <v>7026395</v>
+        <v>7026495</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13266,7 +13266,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13323,10 +13323,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252838</v>
+        <v>121252839</v>
       </c>
       <c r="B98" t="n">
-        <v>74713</v>
+        <v>90731</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13339,21 +13339,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13363,10 +13363,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446201</v>
+        <v>446209</v>
       </c>
       <c r="R98" t="n">
-        <v>7026410</v>
+        <v>7026395</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13398,7 +13398,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -15963,10 +15963,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252815</v>
+        <v>121252809</v>
       </c>
       <c r="B118" t="n">
-        <v>57507</v>
+        <v>77544</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15979,43 +15979,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446189</v>
+        <v>446044</v>
       </c>
       <c r="R118" t="n">
-        <v>7026651</v>
+        <v>7026549</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16047,7 +16038,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16057,7 +16048,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16071,7 +16062,22 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16089,10 +16095,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252809</v>
+        <v>121252815</v>
       </c>
       <c r="B119" t="n">
-        <v>77544</v>
+        <v>57507</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16105,34 +16111,43 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446044</v>
+        <v>446189</v>
       </c>
       <c r="R119" t="n">
-        <v>7026549</v>
+        <v>7026651</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16164,7 +16179,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16174,7 +16189,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16188,22 +16203,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -12927,10 +12927,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252820</v>
+        <v>121252801</v>
       </c>
       <c r="B95" t="n">
-        <v>74713</v>
+        <v>91396</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12939,25 +12939,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>446258</v>
+        <v>445969</v>
       </c>
       <c r="R95" t="n">
-        <v>7026597</v>
+        <v>7026495</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13059,10 +13059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252838</v>
+        <v>121252839</v>
       </c>
       <c r="B96" t="n">
-        <v>74713</v>
+        <v>90731</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13075,21 +13075,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -13099,10 +13099,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446201</v>
+        <v>446209</v>
       </c>
       <c r="R96" t="n">
-        <v>7026410</v>
+        <v>7026395</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13191,10 +13191,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252801</v>
+        <v>121252820</v>
       </c>
       <c r="B97" t="n">
-        <v>91396</v>
+        <v>74713</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13203,25 +13203,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -13231,10 +13231,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445969</v>
+        <v>446258</v>
       </c>
       <c r="R97" t="n">
-        <v>7026495</v>
+        <v>7026597</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13266,7 +13266,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13323,10 +13323,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252839</v>
+        <v>121252838</v>
       </c>
       <c r="B98" t="n">
-        <v>90731</v>
+        <v>74713</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13339,21 +13339,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13363,10 +13363,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446209</v>
+        <v>446201</v>
       </c>
       <c r="R98" t="n">
-        <v>7026395</v>
+        <v>7026410</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13398,7 +13398,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -15963,10 +15963,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252809</v>
+        <v>121252815</v>
       </c>
       <c r="B118" t="n">
-        <v>77544</v>
+        <v>57507</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15979,34 +15979,43 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446044</v>
+        <v>446189</v>
       </c>
       <c r="R118" t="n">
-        <v>7026549</v>
+        <v>7026651</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16038,7 +16047,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16048,7 +16057,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16062,22 +16071,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16095,10 +16089,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252815</v>
+        <v>121252809</v>
       </c>
       <c r="B119" t="n">
-        <v>57507</v>
+        <v>77544</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16111,43 +16105,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446189</v>
+        <v>446044</v>
       </c>
       <c r="R119" t="n">
-        <v>7026651</v>
+        <v>7026549</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16179,7 +16164,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16189,7 +16174,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16203,7 +16188,22 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16485,10 +16485,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252824</v>
+        <v>121252802</v>
       </c>
       <c r="B122" t="n">
-        <v>77544</v>
+        <v>90709</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -16501,21 +16501,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -16525,10 +16525,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446278</v>
+        <v>445982</v>
       </c>
       <c r="R122" t="n">
-        <v>7026536</v>
+        <v>7026514</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16617,10 +16617,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252802</v>
+        <v>121252827</v>
       </c>
       <c r="B123" t="n">
-        <v>90709</v>
+        <v>78607</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16633,21 +16633,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16657,10 +16657,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445982</v>
+        <v>446252</v>
       </c>
       <c r="R123" t="n">
-        <v>7026514</v>
+        <v>7026536</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -16749,10 +16749,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252827</v>
+        <v>121252824</v>
       </c>
       <c r="B124" t="n">
-        <v>78607</v>
+        <v>77544</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16765,21 +16765,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -16789,7 +16789,7 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>446252</v>
+        <v>446278</v>
       </c>
       <c r="R124" t="n">
         <v>7026536</v>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -12395,10 +12395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252804</v>
+        <v>121252837</v>
       </c>
       <c r="B91" t="n">
-        <v>97111</v>
+        <v>77545</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12407,25 +12407,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221063</v>
+        <v>228579</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>446013</v>
+        <v>446201</v>
       </c>
       <c r="R91" t="n">
-        <v>7026514</v>
+        <v>7026410</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12497,9 +12497,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12517,10 +12527,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252833</v>
+        <v>121252824</v>
       </c>
       <c r="B92" t="n">
-        <v>78607</v>
+        <v>77545</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12533,43 +12543,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>446233</v>
+        <v>446278</v>
       </c>
       <c r="R92" t="n">
-        <v>7026512</v>
+        <v>7026536</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12601,7 +12602,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12611,12 +12612,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12645,7 +12641,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12663,10 +12659,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252800</v>
+        <v>121252801</v>
       </c>
       <c r="B93" t="n">
-        <v>57354</v>
+        <v>91402</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12675,43 +12671,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>446056</v>
+        <v>445969</v>
       </c>
       <c r="R93" t="n">
-        <v>7026521</v>
+        <v>7026495</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12743,7 +12734,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12753,12 +12744,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12775,9 +12761,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12795,10 +12791,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121252806</v>
+        <v>121252808</v>
       </c>
       <c r="B94" t="n">
-        <v>74525</v>
+        <v>78642</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12807,28 +12803,37 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6428</v>
+        <v>185</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
@@ -12870,7 +12875,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12880,7 +12885,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12927,10 +12932,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252801</v>
+        <v>121252803</v>
       </c>
       <c r="B95" t="n">
-        <v>91396</v>
+        <v>105194</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12943,21 +12948,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>221725</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12967,10 +12972,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445969</v>
+        <v>446013</v>
       </c>
       <c r="R95" t="n">
-        <v>7026495</v>
+        <v>7026516</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13002,7 +13007,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13012,7 +13017,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13029,19 +13034,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13059,10 +13054,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252839</v>
+        <v>121252807</v>
       </c>
       <c r="B96" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13075,21 +13070,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -13099,10 +13094,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446209</v>
+        <v>446038</v>
       </c>
       <c r="R96" t="n">
-        <v>7026395</v>
+        <v>7026546</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13134,7 +13129,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13144,7 +13139,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13158,7 +13153,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -13173,7 +13168,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13191,10 +13186,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252820</v>
+        <v>121252836</v>
       </c>
       <c r="B97" t="n">
-        <v>74713</v>
+        <v>78608</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13207,21 +13202,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -13231,10 +13226,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446258</v>
+        <v>446201</v>
       </c>
       <c r="R97" t="n">
-        <v>7026597</v>
+        <v>7026410</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13266,7 +13261,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13276,7 +13271,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13305,7 +13300,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13323,10 +13318,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252838</v>
+        <v>121252812</v>
       </c>
       <c r="B98" t="n">
-        <v>74713</v>
+        <v>78608</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13339,21 +13334,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13363,10 +13358,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446201</v>
+        <v>446185</v>
       </c>
       <c r="R98" t="n">
-        <v>7026410</v>
+        <v>7026655</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13398,7 +13393,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13408,7 +13403,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13422,7 +13417,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -13437,7 +13432,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13455,10 +13450,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121252822</v>
+        <v>121252818</v>
       </c>
       <c r="B99" t="n">
-        <v>78607</v>
+        <v>74526</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13467,25 +13462,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -13495,10 +13490,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>446284</v>
+        <v>446209</v>
       </c>
       <c r="R99" t="n">
-        <v>7026552</v>
+        <v>7026630</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13530,7 +13525,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13540,7 +13535,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13554,7 +13549,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -13569,7 +13564,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13587,10 +13582,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121252818</v>
+        <v>121252840</v>
       </c>
       <c r="B100" t="n">
-        <v>74525</v>
+        <v>77545</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13599,25 +13594,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13630,7 +13625,7 @@
         <v>446209</v>
       </c>
       <c r="R100" t="n">
-        <v>7026630</v>
+        <v>7026394</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13662,7 +13657,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13672,7 +13667,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13686,7 +13681,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -13701,7 +13696,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13719,10 +13714,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252813</v>
+        <v>121252810</v>
       </c>
       <c r="B101" t="n">
-        <v>78607</v>
+        <v>74700</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13731,25 +13726,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -13759,10 +13754,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>446166</v>
+        <v>446089</v>
       </c>
       <c r="R101" t="n">
-        <v>7026698</v>
+        <v>7026536</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13794,7 +13789,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13804,7 +13799,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13813,12 +13808,13 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13833,7 +13829,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13851,10 +13847,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121252817</v>
+        <v>121252811</v>
       </c>
       <c r="B102" t="n">
-        <v>74697</v>
+        <v>90715</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13863,25 +13859,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13891,10 +13887,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>446209</v>
+        <v>446106</v>
       </c>
       <c r="R102" t="n">
-        <v>7026630</v>
+        <v>7026528</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13926,7 +13922,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13936,7 +13932,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13950,7 +13946,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>i gammal granskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13965,7 +13961,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13983,10 +13979,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252807</v>
+        <v>121252806</v>
       </c>
       <c r="B103" t="n">
-        <v>78607</v>
+        <v>74526</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13995,25 +13991,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -14115,10 +14111,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121252830</v>
+        <v>121252814</v>
       </c>
       <c r="B104" t="n">
-        <v>74713</v>
+        <v>78608</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14131,21 +14127,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -14155,10 +14151,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>446252</v>
+        <v>446185</v>
       </c>
       <c r="R104" t="n">
-        <v>7026536</v>
+        <v>7026627</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14190,7 +14186,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14200,7 +14196,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14214,7 +14210,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -14229,7 +14225,7 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14247,10 +14243,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252808</v>
+        <v>121252813</v>
       </c>
       <c r="B105" t="n">
-        <v>78641</v>
+        <v>78608</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14263,43 +14259,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>446038</v>
+        <v>446166</v>
       </c>
       <c r="R105" t="n">
-        <v>7026546</v>
+        <v>7026698</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14331,7 +14318,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14341,7 +14328,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14355,7 +14342,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -14370,7 +14357,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14388,10 +14375,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121252836</v>
+        <v>121252815</v>
       </c>
       <c r="B106" t="n">
-        <v>78607</v>
+        <v>57508</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14404,34 +14391,43 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>446201</v>
+        <v>446189</v>
       </c>
       <c r="R106" t="n">
-        <v>7026410</v>
+        <v>7026651</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14463,7 +14459,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14473,7 +14469,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14487,22 +14483,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14520,10 +14501,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121252812</v>
+        <v>121252804</v>
       </c>
       <c r="B107" t="n">
-        <v>78607</v>
+        <v>97117</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14532,25 +14513,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -14560,10 +14541,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>446185</v>
+        <v>446013</v>
       </c>
       <c r="R107" t="n">
-        <v>7026655</v>
+        <v>7026514</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14595,7 +14576,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14605,7 +14586,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14619,22 +14600,12 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14652,10 +14623,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252811</v>
+        <v>121252825</v>
       </c>
       <c r="B108" t="n">
-        <v>90709</v>
+        <v>78864</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14664,25 +14635,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1108</v>
+        <v>6459</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14692,10 +14663,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>446106</v>
+        <v>446278</v>
       </c>
       <c r="R108" t="n">
-        <v>7026528</v>
+        <v>7026536</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14727,7 +14698,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14737,7 +14708,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14751,7 +14722,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -14766,7 +14737,7 @@
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14784,10 +14755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252814</v>
+        <v>121252800</v>
       </c>
       <c r="B109" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14800,34 +14771,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446185</v>
+        <v>446056</v>
       </c>
       <c r="R109" t="n">
-        <v>7026627</v>
+        <v>7026521</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14859,7 +14835,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14869,7 +14845,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14883,22 +14864,12 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14916,10 +14887,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252837</v>
+        <v>121252823</v>
       </c>
       <c r="B110" t="n">
-        <v>77544</v>
+        <v>78608</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14932,21 +14903,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -14956,10 +14927,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>446201</v>
+        <v>446274</v>
       </c>
       <c r="R110" t="n">
-        <v>7026410</v>
+        <v>7026540</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14991,7 +14962,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -15001,7 +14972,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -15015,7 +14986,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -15030,7 +15001,7 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15048,10 +15019,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252840</v>
+        <v>121252830</v>
       </c>
       <c r="B111" t="n">
-        <v>77544</v>
+        <v>74714</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15064,21 +15035,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -15088,10 +15059,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446209</v>
+        <v>446252</v>
       </c>
       <c r="R111" t="n">
-        <v>7026394</v>
+        <v>7026536</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15123,7 +15094,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15133,7 +15104,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15147,7 +15118,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -15162,7 +15133,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15180,10 +15151,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121252803</v>
+        <v>121252826</v>
       </c>
       <c r="B112" t="n">
-        <v>105188</v>
+        <v>78608</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15192,25 +15163,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -15220,10 +15191,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>446013</v>
+        <v>446279</v>
       </c>
       <c r="R112" t="n">
-        <v>7026516</v>
+        <v>7026520</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15255,7 +15226,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -15265,7 +15236,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15279,12 +15250,22 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15302,10 +15283,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121252825</v>
+        <v>121252839</v>
       </c>
       <c r="B113" t="n">
-        <v>78863</v>
+        <v>90737</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15314,25 +15295,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -15342,10 +15323,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>446278</v>
+        <v>446209</v>
       </c>
       <c r="R113" t="n">
-        <v>7026536</v>
+        <v>7026395</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15377,7 +15358,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -15387,7 +15368,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15401,7 +15382,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -15416,7 +15397,7 @@
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15437,7 +15418,7 @@
         <v>121252819</v>
       </c>
       <c r="B114" t="n">
-        <v>77544</v>
+        <v>77545</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -15566,10 +15547,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252810</v>
+        <v>121252817</v>
       </c>
       <c r="B115" t="n">
-        <v>74699</v>
+        <v>74698</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15582,21 +15563,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>306</v>
+        <v>6439</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15606,10 +15587,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446089</v>
+        <v>446209</v>
       </c>
       <c r="R115" t="n">
-        <v>7026536</v>
+        <v>7026630</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15641,7 +15622,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15651,7 +15632,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15660,13 +15641,12 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -15681,7 +15661,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15699,10 +15679,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252823</v>
+        <v>121252827</v>
       </c>
       <c r="B116" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15739,10 +15719,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446274</v>
+        <v>446252</v>
       </c>
       <c r="R116" t="n">
-        <v>7026540</v>
+        <v>7026536</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15774,7 +15754,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15784,7 +15764,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15813,7 +15793,7 @@
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15831,10 +15811,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252835</v>
+        <v>121252838</v>
       </c>
       <c r="B117" t="n">
-        <v>77991</v>
+        <v>74714</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15847,21 +15827,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15871,10 +15851,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446209</v>
+        <v>446201</v>
       </c>
       <c r="R117" t="n">
-        <v>7026444</v>
+        <v>7026410</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15906,7 +15886,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15916,7 +15896,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15930,22 +15910,22 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>I gammal sumpskog/myr</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15963,10 +15943,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252815</v>
+        <v>121252835</v>
       </c>
       <c r="B118" t="n">
-        <v>57507</v>
+        <v>77992</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15979,43 +15959,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446189</v>
+        <v>446209</v>
       </c>
       <c r="R118" t="n">
-        <v>7026651</v>
+        <v>7026444</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16047,7 +16018,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16057,7 +16028,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16071,7 +16042,22 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal sumpskog/myr</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16089,10 +16075,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252809</v>
+        <v>121252802</v>
       </c>
       <c r="B119" t="n">
-        <v>77544</v>
+        <v>90715</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16105,21 +16091,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -16129,10 +16115,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446044</v>
+        <v>445982</v>
       </c>
       <c r="R119" t="n">
-        <v>7026549</v>
+        <v>7026514</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16164,7 +16150,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16174,7 +16160,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16188,7 +16174,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -16203,7 +16189,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16221,10 +16207,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121252826</v>
+        <v>121252820</v>
       </c>
       <c r="B120" t="n">
-        <v>78607</v>
+        <v>74714</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16237,21 +16223,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -16261,10 +16247,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446279</v>
+        <v>446258</v>
       </c>
       <c r="R120" t="n">
-        <v>7026520</v>
+        <v>7026597</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16296,7 +16282,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -16306,7 +16292,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16320,7 +16306,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -16335,7 +16321,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16356,7 +16342,7 @@
         <v>121252821</v>
       </c>
       <c r="B121" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -16485,10 +16471,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252802</v>
+        <v>121252822</v>
       </c>
       <c r="B122" t="n">
-        <v>90709</v>
+        <v>78608</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -16501,21 +16487,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -16525,10 +16511,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445982</v>
+        <v>446284</v>
       </c>
       <c r="R122" t="n">
-        <v>7026514</v>
+        <v>7026552</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16560,7 +16546,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16570,7 +16556,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16584,7 +16570,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -16599,7 +16585,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16617,10 +16603,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252827</v>
+        <v>121252809</v>
       </c>
       <c r="B123" t="n">
-        <v>78607</v>
+        <v>77545</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16633,21 +16619,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16657,10 +16643,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446252</v>
+        <v>446044</v>
       </c>
       <c r="R123" t="n">
-        <v>7026536</v>
+        <v>7026549</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16692,7 +16678,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16702,7 +16688,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16716,7 +16702,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -16731,7 +16717,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -16749,10 +16735,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252824</v>
+        <v>121252833</v>
       </c>
       <c r="B124" t="n">
-        <v>77544</v>
+        <v>78608</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16765,34 +16751,43 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>446278</v>
+        <v>446233</v>
       </c>
       <c r="R124" t="n">
-        <v>7026536</v>
+        <v>7026512</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16824,7 +16819,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16834,7 +16829,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -16884,7 +16884,7 @@
         <v>121499846</v>
       </c>
       <c r="B125" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -14755,10 +14755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252800</v>
+        <v>121252830</v>
       </c>
       <c r="B109" t="n">
-        <v>57355</v>
+        <v>74714</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14771,39 +14771,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446056</v>
+        <v>446252</v>
       </c>
       <c r="R109" t="n">
-        <v>7026521</v>
+        <v>7026536</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14835,7 +14830,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14845,12 +14840,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14864,12 +14854,22 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -15019,10 +15019,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252830</v>
+        <v>121252800</v>
       </c>
       <c r="B111" t="n">
-        <v>74714</v>
+        <v>57355</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15035,34 +15035,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446252</v>
+        <v>446056</v>
       </c>
       <c r="R111" t="n">
-        <v>7026536</v>
+        <v>7026521</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15094,7 +15099,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15104,7 +15109,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15118,22 +15128,12 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -16471,10 +16471,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252822</v>
+        <v>121252809</v>
       </c>
       <c r="B122" t="n">
-        <v>78608</v>
+        <v>77545</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -16487,21 +16487,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -16511,10 +16511,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446284</v>
+        <v>446044</v>
       </c>
       <c r="R122" t="n">
-        <v>7026552</v>
+        <v>7026549</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16546,7 +16546,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -16585,7 +16585,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16603,10 +16603,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252809</v>
+        <v>121252822</v>
       </c>
       <c r="B123" t="n">
-        <v>77545</v>
+        <v>78608</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16619,21 +16619,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16643,10 +16643,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446044</v>
+        <v>446284</v>
       </c>
       <c r="R123" t="n">
-        <v>7026549</v>
+        <v>7026552</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16678,7 +16678,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -12395,10 +12395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252837</v>
+        <v>121252801</v>
       </c>
       <c r="B91" t="n">
-        <v>77545</v>
+        <v>91403</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12407,25 +12407,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>446201</v>
+        <v>445969</v>
       </c>
       <c r="R91" t="n">
-        <v>7026410</v>
+        <v>7026495</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12527,10 +12527,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252824</v>
+        <v>121252809</v>
       </c>
       <c r="B92" t="n">
-        <v>77545</v>
+        <v>77546</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>446278</v>
+        <v>446044</v>
       </c>
       <c r="R92" t="n">
-        <v>7026536</v>
+        <v>7026549</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12659,10 +12659,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252801</v>
+        <v>121252838</v>
       </c>
       <c r="B93" t="n">
-        <v>91402</v>
+        <v>74715</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12671,25 +12671,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445969</v>
+        <v>446201</v>
       </c>
       <c r="R93" t="n">
-        <v>7026495</v>
+        <v>7026410</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12791,10 +12791,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121252808</v>
+        <v>121252840</v>
       </c>
       <c r="B94" t="n">
-        <v>78642</v>
+        <v>77546</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12807,43 +12807,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>185</v>
+        <v>228579</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>446038</v>
+        <v>446209</v>
       </c>
       <c r="R94" t="n">
-        <v>7026546</v>
+        <v>7026394</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12875,7 +12866,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12885,7 +12876,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12899,7 +12890,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -12914,7 +12905,7 @@
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12932,10 +12923,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252803</v>
+        <v>121252802</v>
       </c>
       <c r="B95" t="n">
-        <v>105194</v>
+        <v>90716</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12944,25 +12935,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12972,10 +12963,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>446013</v>
+        <v>445982</v>
       </c>
       <c r="R95" t="n">
-        <v>7026516</v>
+        <v>7026514</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13007,7 +12998,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13017,7 +13008,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13034,9 +13025,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13054,10 +13055,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252807</v>
+        <v>121252800</v>
       </c>
       <c r="B96" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13070,34 +13071,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446038</v>
+        <v>446056</v>
       </c>
       <c r="R96" t="n">
-        <v>7026546</v>
+        <v>7026521</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13129,7 +13135,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13139,7 +13145,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13153,22 +13164,12 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13186,10 +13187,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252836</v>
+        <v>121252808</v>
       </c>
       <c r="B97" t="n">
-        <v>78608</v>
+        <v>78643</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13202,34 +13203,43 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446201</v>
+        <v>446038</v>
       </c>
       <c r="R97" t="n">
-        <v>7026410</v>
+        <v>7026546</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13261,7 +13271,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13271,7 +13281,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13285,7 +13295,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -13300,7 +13310,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13318,10 +13328,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252812</v>
+        <v>121252839</v>
       </c>
       <c r="B98" t="n">
-        <v>78608</v>
+        <v>90738</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13334,21 +13344,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13358,10 +13368,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446185</v>
+        <v>446209</v>
       </c>
       <c r="R98" t="n">
-        <v>7026655</v>
+        <v>7026395</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13393,7 +13403,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13403,7 +13413,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13417,7 +13427,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -13432,7 +13442,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13450,10 +13460,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121252818</v>
+        <v>121252806</v>
       </c>
       <c r="B99" t="n">
-        <v>74526</v>
+        <v>74527</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13490,10 +13500,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>446209</v>
+        <v>446038</v>
       </c>
       <c r="R99" t="n">
-        <v>7026630</v>
+        <v>7026546</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13525,7 +13535,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13535,7 +13545,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13549,7 +13559,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -13564,7 +13574,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13582,10 +13592,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121252840</v>
+        <v>121252813</v>
       </c>
       <c r="B100" t="n">
-        <v>77545</v>
+        <v>78609</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13598,21 +13608,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13622,10 +13632,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>446209</v>
+        <v>446166</v>
       </c>
       <c r="R100" t="n">
-        <v>7026394</v>
+        <v>7026698</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13657,7 +13667,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13667,7 +13677,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13681,7 +13691,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -13696,7 +13706,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13714,10 +13724,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252810</v>
+        <v>121252825</v>
       </c>
       <c r="B101" t="n">
-        <v>74700</v>
+        <v>78865</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13730,21 +13740,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>306</v>
+        <v>6459</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -13754,7 +13764,7 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>446089</v>
+        <v>446278</v>
       </c>
       <c r="R101" t="n">
         <v>7026536</v>
@@ -13789,7 +13799,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13799,7 +13809,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13808,13 +13818,12 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13829,7 +13838,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13847,10 +13856,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121252811</v>
+        <v>121252810</v>
       </c>
       <c r="B102" t="n">
-        <v>90715</v>
+        <v>74701</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13859,25 +13868,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1108</v>
+        <v>306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13887,10 +13896,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>446106</v>
+        <v>446089</v>
       </c>
       <c r="R102" t="n">
-        <v>7026528</v>
+        <v>7026536</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13922,7 +13931,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13932,7 +13941,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13941,12 +13950,13 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13961,7 +13971,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13979,10 +13989,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252806</v>
+        <v>121252837</v>
       </c>
       <c r="B103" t="n">
-        <v>74526</v>
+        <v>77546</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13991,25 +14001,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -14019,10 +14029,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>446038</v>
+        <v>446201</v>
       </c>
       <c r="R103" t="n">
-        <v>7026546</v>
+        <v>7026410</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -14054,7 +14064,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14064,7 +14074,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14078,7 +14088,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -14093,7 +14103,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14111,10 +14121,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121252814</v>
+        <v>121252827</v>
       </c>
       <c r="B104" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14151,10 +14161,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>446185</v>
+        <v>446252</v>
       </c>
       <c r="R104" t="n">
-        <v>7026627</v>
+        <v>7026536</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14186,7 +14196,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14196,7 +14206,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14210,7 +14220,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -14225,7 +14235,7 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14243,10 +14253,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252813</v>
+        <v>121252830</v>
       </c>
       <c r="B105" t="n">
-        <v>78608</v>
+        <v>74715</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14259,21 +14269,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -14283,10 +14293,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>446166</v>
+        <v>446252</v>
       </c>
       <c r="R105" t="n">
-        <v>7026698</v>
+        <v>7026536</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14318,7 +14328,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14328,7 +14338,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14342,7 +14352,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -14357,7 +14367,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14378,7 +14388,7 @@
         <v>121252815</v>
       </c>
       <c r="B106" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14504,7 +14514,7 @@
         <v>121252804</v>
       </c>
       <c r="B107" t="n">
-        <v>97117</v>
+        <v>97118</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14623,10 +14633,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252825</v>
+        <v>121252835</v>
       </c>
       <c r="B108" t="n">
-        <v>78864</v>
+        <v>77993</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14635,25 +14645,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6459</v>
+        <v>6437</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14663,10 +14673,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>446278</v>
+        <v>446209</v>
       </c>
       <c r="R108" t="n">
-        <v>7026536</v>
+        <v>7026444</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14698,7 +14708,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14708,7 +14718,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14722,22 +14732,22 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal sumpskog/myr</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14755,10 +14765,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252830</v>
+        <v>121252812</v>
       </c>
       <c r="B109" t="n">
-        <v>74714</v>
+        <v>78609</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14771,21 +14781,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14795,10 +14805,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446252</v>
+        <v>446185</v>
       </c>
       <c r="R109" t="n">
-        <v>7026536</v>
+        <v>7026655</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14830,7 +14840,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14840,7 +14850,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14854,7 +14864,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -14869,7 +14879,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14887,10 +14897,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252823</v>
+        <v>121252803</v>
       </c>
       <c r="B110" t="n">
-        <v>78608</v>
+        <v>105195</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14899,25 +14909,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -14927,10 +14937,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>446274</v>
+        <v>446013</v>
       </c>
       <c r="R110" t="n">
-        <v>7026540</v>
+        <v>7026516</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14962,7 +14972,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14972,7 +14982,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14986,22 +14996,12 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15019,10 +15019,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252800</v>
+        <v>121252819</v>
       </c>
       <c r="B111" t="n">
-        <v>57355</v>
+        <v>77546</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15035,39 +15035,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446056</v>
+        <v>446258</v>
       </c>
       <c r="R111" t="n">
-        <v>7026521</v>
+        <v>7026597</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15099,7 +15094,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15109,12 +15104,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15131,9 +15121,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15151,10 +15151,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121252826</v>
+        <v>121252818</v>
       </c>
       <c r="B112" t="n">
-        <v>78608</v>
+        <v>74527</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15163,25 +15163,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>446279</v>
+        <v>446209</v>
       </c>
       <c r="R112" t="n">
-        <v>7026520</v>
+        <v>7026630</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15283,10 +15283,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121252839</v>
+        <v>121252814</v>
       </c>
       <c r="B113" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15299,21 +15299,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -15323,10 +15323,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>446209</v>
+        <v>446185</v>
       </c>
       <c r="R113" t="n">
-        <v>7026395</v>
+        <v>7026627</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15415,10 +15415,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121252819</v>
+        <v>121252826</v>
       </c>
       <c r="B114" t="n">
-        <v>77545</v>
+        <v>78609</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -15431,21 +15431,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -15455,10 +15455,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>446258</v>
+        <v>446279</v>
       </c>
       <c r="R114" t="n">
-        <v>7026597</v>
+        <v>7026520</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15547,10 +15547,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252817</v>
+        <v>121252833</v>
       </c>
       <c r="B115" t="n">
-        <v>74698</v>
+        <v>78609</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15559,38 +15559,47 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446209</v>
+        <v>446233</v>
       </c>
       <c r="R115" t="n">
-        <v>7026630</v>
+        <v>7026512</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15622,7 +15631,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15632,7 +15641,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15646,7 +15660,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -15661,7 +15675,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15679,10 +15693,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252827</v>
+        <v>121252811</v>
       </c>
       <c r="B116" t="n">
-        <v>78608</v>
+        <v>90716</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15695,21 +15709,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15719,10 +15733,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446252</v>
+        <v>446106</v>
       </c>
       <c r="R116" t="n">
-        <v>7026536</v>
+        <v>7026528</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15754,7 +15768,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15764,7 +15778,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15778,7 +15792,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>i gammal granskog</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -15793,7 +15807,7 @@
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15811,10 +15825,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252838</v>
+        <v>121252820</v>
       </c>
       <c r="B117" t="n">
-        <v>74714</v>
+        <v>74715</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15851,10 +15865,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446201</v>
+        <v>446258</v>
       </c>
       <c r="R117" t="n">
-        <v>7026410</v>
+        <v>7026597</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15886,7 +15900,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15896,7 +15910,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15925,7 +15939,7 @@
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15943,10 +15957,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252835</v>
+        <v>121252824</v>
       </c>
       <c r="B118" t="n">
-        <v>77992</v>
+        <v>77546</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15959,21 +15973,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6437</v>
+        <v>228579</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15983,10 +15997,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446209</v>
+        <v>446278</v>
       </c>
       <c r="R118" t="n">
-        <v>7026444</v>
+        <v>7026536</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16018,7 +16032,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16028,7 +16042,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16042,22 +16056,22 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I gammal sumpskog/myr</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16075,10 +16089,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252802</v>
+        <v>121252823</v>
       </c>
       <c r="B119" t="n">
-        <v>90715</v>
+        <v>78609</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16091,21 +16105,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -16115,10 +16129,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445982</v>
+        <v>446274</v>
       </c>
       <c r="R119" t="n">
-        <v>7026514</v>
+        <v>7026540</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16150,7 +16164,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16160,7 +16174,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16174,7 +16188,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -16189,7 +16203,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16207,10 +16221,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121252820</v>
+        <v>121252836</v>
       </c>
       <c r="B120" t="n">
-        <v>74714</v>
+        <v>78609</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16223,21 +16237,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -16247,10 +16261,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446258</v>
+        <v>446201</v>
       </c>
       <c r="R120" t="n">
-        <v>7026597</v>
+        <v>7026410</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16282,7 +16296,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -16292,7 +16306,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16321,7 +16335,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16339,10 +16353,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121252821</v>
+        <v>121252817</v>
       </c>
       <c r="B121" t="n">
-        <v>78608</v>
+        <v>74699</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -16351,25 +16365,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -16379,10 +16393,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>446282</v>
+        <v>446209</v>
       </c>
       <c r="R121" t="n">
-        <v>7026592</v>
+        <v>7026630</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16414,7 +16428,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -16424,7 +16438,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16438,7 +16452,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -16453,7 +16467,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16471,10 +16485,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252809</v>
+        <v>121252807</v>
       </c>
       <c r="B122" t="n">
-        <v>77545</v>
+        <v>78609</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -16487,21 +16501,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -16511,10 +16525,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446044</v>
+        <v>446038</v>
       </c>
       <c r="R122" t="n">
-        <v>7026549</v>
+        <v>7026546</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16546,7 +16560,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16556,7 +16570,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16585,7 +16599,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16603,10 +16617,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252822</v>
+        <v>121252821</v>
       </c>
       <c r="B123" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16643,10 +16657,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446284</v>
+        <v>446282</v>
       </c>
       <c r="R123" t="n">
-        <v>7026552</v>
+        <v>7026592</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16678,7 +16692,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16688,7 +16702,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16735,10 +16749,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252833</v>
+        <v>121252822</v>
       </c>
       <c r="B124" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16768,26 +16782,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>446233</v>
+        <v>446284</v>
       </c>
       <c r="R124" t="n">
-        <v>7026512</v>
+        <v>7026552</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16819,7 +16824,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16829,12 +16834,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -16884,7 +16884,7 @@
         <v>121499846</v>
       </c>
       <c r="B125" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -12395,10 +12395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252801</v>
+        <v>121252800</v>
       </c>
       <c r="B91" t="n">
-        <v>91403</v>
+        <v>57356</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12407,38 +12407,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445969</v>
+        <v>446056</v>
       </c>
       <c r="R91" t="n">
-        <v>7026495</v>
+        <v>7026521</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12470,7 +12475,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12480,7 +12485,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12497,19 +12507,9 @@
           <t>I gammal granskog</t>
         </is>
       </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12527,10 +12527,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252809</v>
+        <v>121252833</v>
       </c>
       <c r="B92" t="n">
-        <v>77546</v>
+        <v>78609</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12543,34 +12543,43 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>446044</v>
+        <v>446233</v>
       </c>
       <c r="R92" t="n">
-        <v>7026549</v>
+        <v>7026512</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12602,7 +12611,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12612,7 +12621,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12626,7 +12640,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -12641,7 +12655,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12659,10 +12673,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252838</v>
+        <v>121252812</v>
       </c>
       <c r="B93" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12675,21 +12689,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12699,10 +12713,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>446201</v>
+        <v>446185</v>
       </c>
       <c r="R93" t="n">
-        <v>7026410</v>
+        <v>7026655</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12734,7 +12748,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12744,7 +12758,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12758,7 +12772,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -12773,7 +12787,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12791,10 +12805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121252840</v>
+        <v>121252806</v>
       </c>
       <c r="B94" t="n">
-        <v>77546</v>
+        <v>74527</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12803,25 +12817,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12831,10 +12845,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>446209</v>
+        <v>446038</v>
       </c>
       <c r="R94" t="n">
-        <v>7026394</v>
+        <v>7026546</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12866,7 +12880,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12876,7 +12890,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12890,7 +12904,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -12905,7 +12919,7 @@
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12923,10 +12937,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252802</v>
+        <v>121252801</v>
       </c>
       <c r="B95" t="n">
-        <v>90716</v>
+        <v>91403</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12935,25 +12949,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12963,10 +12977,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445982</v>
+        <v>445969</v>
       </c>
       <c r="R95" t="n">
-        <v>7026514</v>
+        <v>7026495</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12998,7 +13012,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13008,7 +13022,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13037,7 +13051,7 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13055,10 +13069,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252800</v>
+        <v>121252804</v>
       </c>
       <c r="B96" t="n">
-        <v>57356</v>
+        <v>97118</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13067,43 +13081,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>221063</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446056</v>
+        <v>446013</v>
       </c>
       <c r="R96" t="n">
-        <v>7026521</v>
+        <v>7026514</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13135,7 +13144,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13145,12 +13154,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13169,7 +13173,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13187,10 +13191,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252808</v>
+        <v>121252817</v>
       </c>
       <c r="B97" t="n">
-        <v>78643</v>
+        <v>74699</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13199,47 +13203,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446038</v>
+        <v>446209</v>
       </c>
       <c r="R97" t="n">
-        <v>7026546</v>
+        <v>7026630</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13271,7 +13266,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13281,7 +13276,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13295,7 +13290,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -13310,7 +13305,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13328,10 +13323,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252839</v>
+        <v>121252838</v>
       </c>
       <c r="B98" t="n">
-        <v>90738</v>
+        <v>74715</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13344,21 +13339,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13368,10 +13363,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446209</v>
+        <v>446201</v>
       </c>
       <c r="R98" t="n">
-        <v>7026395</v>
+        <v>7026410</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13403,7 +13398,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13413,7 +13408,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13427,7 +13422,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -13442,7 +13437,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13460,10 +13455,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121252806</v>
+        <v>121252826</v>
       </c>
       <c r="B99" t="n">
-        <v>74527</v>
+        <v>78609</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13472,25 +13467,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -13500,10 +13495,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>446038</v>
+        <v>446279</v>
       </c>
       <c r="R99" t="n">
-        <v>7026546</v>
+        <v>7026520</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13535,7 +13530,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13545,7 +13540,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13559,7 +13554,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -13574,7 +13569,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13592,10 +13587,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121252813</v>
+        <v>121252808</v>
       </c>
       <c r="B100" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13608,34 +13603,43 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>446166</v>
+        <v>446038</v>
       </c>
       <c r="R100" t="n">
-        <v>7026698</v>
+        <v>7026546</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13667,7 +13671,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13677,7 +13681,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13691,7 +13695,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -13706,7 +13710,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13724,10 +13728,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252825</v>
+        <v>121252824</v>
       </c>
       <c r="B101" t="n">
-        <v>78865</v>
+        <v>77546</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13736,25 +13740,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6459</v>
+        <v>228579</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -13838,7 +13842,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13856,10 +13860,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121252810</v>
+        <v>121252813</v>
       </c>
       <c r="B102" t="n">
-        <v>74701</v>
+        <v>78609</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13868,25 +13872,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13896,10 +13900,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>446089</v>
+        <v>446166</v>
       </c>
       <c r="R102" t="n">
-        <v>7026536</v>
+        <v>7026698</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13931,7 +13935,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13941,7 +13945,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13950,13 +13954,12 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13971,7 +13974,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13989,10 +13992,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252837</v>
+        <v>121252807</v>
       </c>
       <c r="B103" t="n">
-        <v>77546</v>
+        <v>78609</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -14005,21 +14008,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -14029,10 +14032,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>446201</v>
+        <v>446038</v>
       </c>
       <c r="R103" t="n">
-        <v>7026410</v>
+        <v>7026546</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -14064,7 +14067,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14074,7 +14077,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14088,7 +14091,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -14103,7 +14106,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14121,7 +14124,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121252827</v>
+        <v>121252823</v>
       </c>
       <c r="B104" t="n">
         <v>78609</v>
@@ -14161,10 +14164,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>446252</v>
+        <v>446274</v>
       </c>
       <c r="R104" t="n">
-        <v>7026536</v>
+        <v>7026540</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14196,7 +14199,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14206,7 +14209,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14235,7 +14238,7 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14253,10 +14256,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252830</v>
+        <v>121252803</v>
       </c>
       <c r="B105" t="n">
-        <v>74715</v>
+        <v>105195</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14265,25 +14268,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -14293,10 +14296,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>446252</v>
+        <v>446013</v>
       </c>
       <c r="R105" t="n">
-        <v>7026536</v>
+        <v>7026516</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14328,7 +14331,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14338,7 +14341,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14352,22 +14355,12 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14385,10 +14378,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121252815</v>
+        <v>121252802</v>
       </c>
       <c r="B106" t="n">
-        <v>57509</v>
+        <v>90716</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14401,43 +14394,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>446189</v>
+        <v>445982</v>
       </c>
       <c r="R106" t="n">
-        <v>7026651</v>
+        <v>7026514</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14469,7 +14453,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14479,7 +14463,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14493,7 +14477,22 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14511,10 +14510,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121252804</v>
+        <v>121252811</v>
       </c>
       <c r="B107" t="n">
-        <v>97118</v>
+        <v>90716</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14523,25 +14522,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221063</v>
+        <v>1108</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -14551,10 +14550,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>446013</v>
+        <v>446106</v>
       </c>
       <c r="R107" t="n">
-        <v>7026514</v>
+        <v>7026528</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14586,7 +14585,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14596,7 +14595,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14610,12 +14609,22 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14633,10 +14642,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252835</v>
+        <v>121252827</v>
       </c>
       <c r="B108" t="n">
-        <v>77993</v>
+        <v>78609</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14649,21 +14658,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14673,10 +14682,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>446209</v>
+        <v>446252</v>
       </c>
       <c r="R108" t="n">
-        <v>7026444</v>
+        <v>7026536</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14708,7 +14717,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14718,7 +14727,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14732,22 +14741,22 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>I gammal sumpskog/myr</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14765,10 +14774,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252812</v>
+        <v>121252809</v>
       </c>
       <c r="B109" t="n">
-        <v>78609</v>
+        <v>77546</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14781,21 +14790,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14805,10 +14814,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446185</v>
+        <v>446044</v>
       </c>
       <c r="R109" t="n">
-        <v>7026655</v>
+        <v>7026549</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14840,7 +14849,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14850,7 +14859,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14864,7 +14873,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -14879,7 +14888,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14897,10 +14906,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252803</v>
+        <v>121252839</v>
       </c>
       <c r="B110" t="n">
-        <v>105195</v>
+        <v>90738</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14909,25 +14918,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -14937,10 +14946,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>446013</v>
+        <v>446209</v>
       </c>
       <c r="R110" t="n">
-        <v>7026516</v>
+        <v>7026395</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14972,7 +14981,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14982,7 +14991,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14996,12 +15005,22 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid dike</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15019,7 +15038,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252819</v>
+        <v>121252837</v>
       </c>
       <c r="B111" t="n">
         <v>77546</v>
@@ -15059,10 +15078,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446258</v>
+        <v>446201</v>
       </c>
       <c r="R111" t="n">
-        <v>7026597</v>
+        <v>7026410</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15094,7 +15113,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15104,7 +15123,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15133,7 +15152,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15151,10 +15170,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121252818</v>
+        <v>121252819</v>
       </c>
       <c r="B112" t="n">
-        <v>74527</v>
+        <v>77546</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15163,25 +15182,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -15191,10 +15210,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>446209</v>
+        <v>446258</v>
       </c>
       <c r="R112" t="n">
-        <v>7026630</v>
+        <v>7026597</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15226,7 +15245,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -15236,7 +15255,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15250,7 +15269,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -15265,7 +15284,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15283,10 +15302,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121252814</v>
+        <v>121252820</v>
       </c>
       <c r="B113" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15299,21 +15318,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -15323,10 +15342,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>446185</v>
+        <v>446258</v>
       </c>
       <c r="R113" t="n">
-        <v>7026627</v>
+        <v>7026597</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15358,7 +15377,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -15368,7 +15387,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15382,7 +15401,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -15397,7 +15416,7 @@
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15415,7 +15434,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121252826</v>
+        <v>121252822</v>
       </c>
       <c r="B114" t="n">
         <v>78609</v>
@@ -15455,10 +15474,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>446279</v>
+        <v>446284</v>
       </c>
       <c r="R114" t="n">
-        <v>7026520</v>
+        <v>7026552</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15490,7 +15509,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -15500,7 +15519,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15529,7 +15548,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15547,10 +15566,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252833</v>
+        <v>121252815</v>
       </c>
       <c r="B115" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15563,31 +15582,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -15596,10 +15615,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446233</v>
+        <v>446189</v>
       </c>
       <c r="R115" t="n">
-        <v>7026512</v>
+        <v>7026651</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15631,7 +15650,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15641,12 +15660,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15660,22 +15674,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15693,10 +15692,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252811</v>
+        <v>121252836</v>
       </c>
       <c r="B116" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15709,21 +15708,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15733,10 +15732,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446106</v>
+        <v>446201</v>
       </c>
       <c r="R116" t="n">
-        <v>7026528</v>
+        <v>7026410</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15768,7 +15767,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15778,7 +15777,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15792,7 +15791,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -15807,7 +15806,7 @@
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15825,10 +15824,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252820</v>
+        <v>121252835</v>
       </c>
       <c r="B117" t="n">
-        <v>74715</v>
+        <v>77993</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15841,21 +15840,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15865,10 +15864,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446258</v>
+        <v>446209</v>
       </c>
       <c r="R117" t="n">
-        <v>7026597</v>
+        <v>7026444</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15900,7 +15899,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15910,7 +15909,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15924,22 +15923,22 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal sumpskog/myr</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15957,10 +15956,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252824</v>
+        <v>121252830</v>
       </c>
       <c r="B118" t="n">
-        <v>77546</v>
+        <v>74715</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15973,21 +15972,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15997,7 +15996,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446278</v>
+        <v>446252</v>
       </c>
       <c r="R118" t="n">
         <v>7026536</v>
@@ -16032,7 +16031,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16042,7 +16041,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16071,7 +16070,7 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16089,7 +16088,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252823</v>
+        <v>121252814</v>
       </c>
       <c r="B119" t="n">
         <v>78609</v>
@@ -16129,10 +16128,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446274</v>
+        <v>446185</v>
       </c>
       <c r="R119" t="n">
-        <v>7026540</v>
+        <v>7026627</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16164,7 +16163,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16174,7 +16173,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16188,7 +16187,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -16203,7 +16202,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16221,10 +16220,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121252836</v>
+        <v>121252818</v>
       </c>
       <c r="B120" t="n">
-        <v>78609</v>
+        <v>74527</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16233,25 +16232,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -16261,10 +16260,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446201</v>
+        <v>446209</v>
       </c>
       <c r="R120" t="n">
-        <v>7026410</v>
+        <v>7026630</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16296,7 +16295,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -16306,7 +16305,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16320,7 +16319,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -16335,7 +16334,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16353,10 +16352,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121252817</v>
+        <v>121252825</v>
       </c>
       <c r="B121" t="n">
-        <v>74699</v>
+        <v>78865</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -16369,21 +16368,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6439</v>
+        <v>6459</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -16393,10 +16392,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>446209</v>
+        <v>446278</v>
       </c>
       <c r="R121" t="n">
-        <v>7026630</v>
+        <v>7026536</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16428,7 +16427,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -16438,7 +16437,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16452,7 +16451,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -16467,7 +16466,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16485,7 +16484,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252807</v>
+        <v>121252821</v>
       </c>
       <c r="B122" t="n">
         <v>78609</v>
@@ -16525,10 +16524,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446038</v>
+        <v>446282</v>
       </c>
       <c r="R122" t="n">
-        <v>7026546</v>
+        <v>7026592</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16560,7 +16559,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16570,7 +16569,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16584,7 +16583,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -16599,7 +16598,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16617,10 +16616,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252821</v>
+        <v>121252810</v>
       </c>
       <c r="B123" t="n">
-        <v>78609</v>
+        <v>74701</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16629,25 +16628,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16657,10 +16656,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446282</v>
+        <v>446089</v>
       </c>
       <c r="R123" t="n">
-        <v>7026592</v>
+        <v>7026536</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16692,7 +16691,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16702,7 +16701,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16711,12 +16710,13 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -16749,10 +16749,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252822</v>
+        <v>121252840</v>
       </c>
       <c r="B124" t="n">
-        <v>78609</v>
+        <v>77546</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16765,21 +16765,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -16789,10 +16789,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>446284</v>
+        <v>446209</v>
       </c>
       <c r="R124" t="n">
-        <v>7026552</v>
+        <v>7026394</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -12395,10 +12395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252800</v>
+        <v>121252810</v>
       </c>
       <c r="B91" t="n">
-        <v>57356</v>
+        <v>74701</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12407,43 +12407,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>446056</v>
+        <v>446089</v>
       </c>
       <c r="R91" t="n">
-        <v>7026521</v>
+        <v>7026536</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12475,7 +12470,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12485,12 +12480,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12499,6 +12489,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12507,9 +12498,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12527,7 +12528,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252833</v>
+        <v>121252827</v>
       </c>
       <c r="B92" t="n">
         <v>78609</v>
@@ -12560,26 +12561,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>446233</v>
+        <v>446252</v>
       </c>
       <c r="R92" t="n">
-        <v>7026512</v>
+        <v>7026536</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12611,7 +12603,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12621,12 +12613,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12655,7 +12642,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12673,7 +12660,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252812</v>
+        <v>121252814</v>
       </c>
       <c r="B93" t="n">
         <v>78609</v>
@@ -12716,7 +12703,7 @@
         <v>446185</v>
       </c>
       <c r="R93" t="n">
-        <v>7026655</v>
+        <v>7026627</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12748,7 +12735,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12758,7 +12745,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12787,7 +12774,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12805,10 +12792,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121252806</v>
+        <v>121252840</v>
       </c>
       <c r="B94" t="n">
-        <v>74527</v>
+        <v>77546</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12817,25 +12804,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12845,10 +12832,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>446038</v>
+        <v>446209</v>
       </c>
       <c r="R94" t="n">
-        <v>7026546</v>
+        <v>7026394</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12880,7 +12867,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12890,7 +12877,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12904,7 +12891,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -12919,7 +12906,7 @@
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12937,10 +12924,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252801</v>
+        <v>121252808</v>
       </c>
       <c r="B95" t="n">
-        <v>91403</v>
+        <v>78643</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12949,38 +12936,47 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>185</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445969</v>
+        <v>446038</v>
       </c>
       <c r="R95" t="n">
-        <v>7026495</v>
+        <v>7026546</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13012,7 +13008,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13022,7 +13018,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13036,7 +13032,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -13051,7 +13047,7 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13191,10 +13187,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252817</v>
+        <v>121252837</v>
       </c>
       <c r="B97" t="n">
-        <v>74699</v>
+        <v>77546</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13203,25 +13199,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -13231,10 +13227,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446209</v>
+        <v>446201</v>
       </c>
       <c r="R97" t="n">
-        <v>7026630</v>
+        <v>7026410</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13266,7 +13262,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13276,7 +13272,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13290,7 +13286,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -13305,7 +13301,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13323,10 +13319,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252838</v>
+        <v>121252833</v>
       </c>
       <c r="B98" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13339,34 +13335,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446201</v>
+        <v>446233</v>
       </c>
       <c r="R98" t="n">
-        <v>7026410</v>
+        <v>7026512</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13398,7 +13403,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13408,7 +13413,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13422,7 +13432,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -13437,7 +13447,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13455,7 +13465,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121252826</v>
+        <v>121252821</v>
       </c>
       <c r="B99" t="n">
         <v>78609</v>
@@ -13495,10 +13505,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>446279</v>
+        <v>446282</v>
       </c>
       <c r="R99" t="n">
-        <v>7026520</v>
+        <v>7026592</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13530,7 +13540,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13540,7 +13550,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13569,7 +13579,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13587,10 +13597,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121252808</v>
+        <v>121252826</v>
       </c>
       <c r="B100" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13603,43 +13613,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>446038</v>
+        <v>446279</v>
       </c>
       <c r="R100" t="n">
-        <v>7026546</v>
+        <v>7026520</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13671,7 +13672,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13681,7 +13682,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13695,7 +13696,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -13710,7 +13711,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13728,7 +13729,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252824</v>
+        <v>121252819</v>
       </c>
       <c r="B101" t="n">
         <v>77546</v>
@@ -13768,10 +13769,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>446278</v>
+        <v>446258</v>
       </c>
       <c r="R101" t="n">
-        <v>7026536</v>
+        <v>7026597</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13803,7 +13804,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13813,7 +13814,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13827,7 +13828,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13842,7 +13843,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13860,10 +13861,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121252813</v>
+        <v>121252839</v>
       </c>
       <c r="B102" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13876,21 +13877,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13900,10 +13901,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>446166</v>
+        <v>446209</v>
       </c>
       <c r="R102" t="n">
-        <v>7026698</v>
+        <v>7026395</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13935,7 +13936,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13945,7 +13946,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13959,7 +13960,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13974,7 +13975,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13992,10 +13993,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252807</v>
+        <v>121252800</v>
       </c>
       <c r="B103" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -14008,34 +14009,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>446038</v>
+        <v>446056</v>
       </c>
       <c r="R103" t="n">
-        <v>7026546</v>
+        <v>7026521</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -14067,7 +14073,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14077,7 +14083,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14091,22 +14102,12 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14124,7 +14125,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121252823</v>
+        <v>121252836</v>
       </c>
       <c r="B104" t="n">
         <v>78609</v>
@@ -14164,10 +14165,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>446274</v>
+        <v>446201</v>
       </c>
       <c r="R104" t="n">
-        <v>7026540</v>
+        <v>7026410</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14199,7 +14200,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14209,7 +14210,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14223,7 +14224,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -14238,7 +14239,7 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14256,10 +14257,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252803</v>
+        <v>121252802</v>
       </c>
       <c r="B105" t="n">
-        <v>105195</v>
+        <v>90716</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14268,25 +14269,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -14296,10 +14297,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>446013</v>
+        <v>445982</v>
       </c>
       <c r="R105" t="n">
-        <v>7026516</v>
+        <v>7026514</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14331,7 +14332,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14341,7 +14342,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14358,9 +14359,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14378,10 +14389,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121252802</v>
+        <v>121252815</v>
       </c>
       <c r="B106" t="n">
-        <v>90716</v>
+        <v>57509</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14394,34 +14405,43 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445982</v>
+        <v>446189</v>
       </c>
       <c r="R106" t="n">
-        <v>7026514</v>
+        <v>7026651</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14453,7 +14473,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14463,7 +14483,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14477,22 +14497,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14510,10 +14515,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121252811</v>
+        <v>121252835</v>
       </c>
       <c r="B107" t="n">
-        <v>90716</v>
+        <v>77993</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14526,21 +14531,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>6437</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -14550,10 +14555,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>446106</v>
+        <v>446209</v>
       </c>
       <c r="R107" t="n">
-        <v>7026528</v>
+        <v>7026444</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14585,7 +14590,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14595,7 +14600,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14609,22 +14614,22 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal sumpskog/myr</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14642,10 +14647,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252827</v>
+        <v>121252820</v>
       </c>
       <c r="B108" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14658,21 +14663,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14682,10 +14687,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>446252</v>
+        <v>446258</v>
       </c>
       <c r="R108" t="n">
-        <v>7026536</v>
+        <v>7026597</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14717,7 +14722,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14727,7 +14732,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14741,7 +14746,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -14756,7 +14761,7 @@
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14774,10 +14779,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252809</v>
+        <v>121252838</v>
       </c>
       <c r="B109" t="n">
-        <v>77546</v>
+        <v>74715</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14790,21 +14795,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14814,10 +14819,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446044</v>
+        <v>446201</v>
       </c>
       <c r="R109" t="n">
-        <v>7026549</v>
+        <v>7026410</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14849,7 +14854,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14859,7 +14864,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14873,7 +14878,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -14888,7 +14893,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14906,10 +14911,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252839</v>
+        <v>121252801</v>
       </c>
       <c r="B110" t="n">
-        <v>90738</v>
+        <v>91403</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14918,25 +14923,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -14946,10 +14951,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>446209</v>
+        <v>445969</v>
       </c>
       <c r="R110" t="n">
-        <v>7026395</v>
+        <v>7026495</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14981,7 +14986,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14991,7 +14996,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -15005,7 +15010,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -15020,7 +15025,7 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15038,10 +15043,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252837</v>
+        <v>121252812</v>
       </c>
       <c r="B111" t="n">
-        <v>77546</v>
+        <v>78609</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15054,21 +15059,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -15078,10 +15083,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446201</v>
+        <v>446185</v>
       </c>
       <c r="R111" t="n">
-        <v>7026410</v>
+        <v>7026655</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15113,7 +15118,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15123,7 +15128,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15137,7 +15142,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -15152,7 +15157,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15170,10 +15175,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121252819</v>
+        <v>121252807</v>
       </c>
       <c r="B112" t="n">
-        <v>77546</v>
+        <v>78609</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15186,21 +15191,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -15210,10 +15215,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>446258</v>
+        <v>446038</v>
       </c>
       <c r="R112" t="n">
-        <v>7026597</v>
+        <v>7026546</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15245,7 +15250,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -15255,7 +15260,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15269,7 +15274,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -15284,7 +15289,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15302,10 +15307,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121252820</v>
+        <v>121252822</v>
       </c>
       <c r="B113" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15318,21 +15323,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -15342,10 +15347,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>446258</v>
+        <v>446284</v>
       </c>
       <c r="R113" t="n">
-        <v>7026597</v>
+        <v>7026552</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15377,7 +15382,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -15387,7 +15392,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15401,7 +15406,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -15416,7 +15421,7 @@
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15434,10 +15439,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121252822</v>
+        <v>121252824</v>
       </c>
       <c r="B114" t="n">
-        <v>78609</v>
+        <v>77546</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -15450,21 +15455,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -15474,10 +15479,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>446284</v>
+        <v>446278</v>
       </c>
       <c r="R114" t="n">
-        <v>7026552</v>
+        <v>7026536</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15509,7 +15514,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -15519,7 +15524,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15548,7 +15553,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15566,10 +15571,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252815</v>
+        <v>121252817</v>
       </c>
       <c r="B115" t="n">
-        <v>57509</v>
+        <v>74699</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15578,47 +15583,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446189</v>
+        <v>446209</v>
       </c>
       <c r="R115" t="n">
-        <v>7026651</v>
+        <v>7026630</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15675,6 +15671,21 @@
       <c r="AI115" t="inlineStr">
         <is>
           <t>I gammal gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15692,7 +15703,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252836</v>
+        <v>121252823</v>
       </c>
       <c r="B116" t="n">
         <v>78609</v>
@@ -15732,10 +15743,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446201</v>
+        <v>446274</v>
       </c>
       <c r="R116" t="n">
-        <v>7026410</v>
+        <v>7026540</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15767,7 +15778,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15777,7 +15788,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15791,7 +15802,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -15806,7 +15817,7 @@
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15824,10 +15835,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252835</v>
+        <v>121252825</v>
       </c>
       <c r="B117" t="n">
-        <v>77993</v>
+        <v>78865</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15836,25 +15847,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6437</v>
+        <v>6459</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15864,10 +15875,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446209</v>
+        <v>446278</v>
       </c>
       <c r="R117" t="n">
-        <v>7026444</v>
+        <v>7026536</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15899,7 +15910,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15909,7 +15920,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15923,22 +15934,22 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>I gammal sumpskog/myr</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
+          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15956,10 +15967,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252830</v>
+        <v>121252806</v>
       </c>
       <c r="B118" t="n">
-        <v>74715</v>
+        <v>74527</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15968,25 +15979,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15996,10 +16007,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446252</v>
+        <v>446038</v>
       </c>
       <c r="R118" t="n">
-        <v>7026536</v>
+        <v>7026546</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16031,7 +16042,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16041,7 +16052,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16055,7 +16066,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -16070,7 +16081,7 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16088,10 +16099,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252814</v>
+        <v>121252803</v>
       </c>
       <c r="B119" t="n">
-        <v>78609</v>
+        <v>105195</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16100,25 +16111,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -16128,10 +16139,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446185</v>
+        <v>446013</v>
       </c>
       <c r="R119" t="n">
-        <v>7026627</v>
+        <v>7026516</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16163,7 +16174,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16173,7 +16184,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16187,22 +16198,12 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16220,10 +16221,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121252818</v>
+        <v>121252809</v>
       </c>
       <c r="B120" t="n">
-        <v>74527</v>
+        <v>77546</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16232,25 +16233,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -16260,10 +16261,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446209</v>
+        <v>446044</v>
       </c>
       <c r="R120" t="n">
-        <v>7026630</v>
+        <v>7026549</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16295,7 +16296,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -16305,7 +16306,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16319,7 +16320,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -16334,7 +16335,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16352,10 +16353,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121252825</v>
+        <v>121252811</v>
       </c>
       <c r="B121" t="n">
-        <v>78865</v>
+        <v>90716</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -16364,25 +16365,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6459</v>
+        <v>1108</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -16392,10 +16393,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>446278</v>
+        <v>446106</v>
       </c>
       <c r="R121" t="n">
-        <v>7026536</v>
+        <v>7026528</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16427,7 +16428,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -16437,7 +16438,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16451,7 +16452,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>i gammal granskog</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -16466,7 +16467,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16484,7 +16485,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252821</v>
+        <v>121252813</v>
       </c>
       <c r="B122" t="n">
         <v>78609</v>
@@ -16524,10 +16525,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446282</v>
+        <v>446166</v>
       </c>
       <c r="R122" t="n">
-        <v>7026592</v>
+        <v>7026698</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16559,7 +16560,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16569,7 +16570,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16583,7 +16584,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -16598,7 +16599,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16616,10 +16617,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252810</v>
+        <v>121252830</v>
       </c>
       <c r="B123" t="n">
-        <v>74701</v>
+        <v>74715</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16628,25 +16629,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>306</v>
+        <v>6440</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16656,7 +16657,7 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446089</v>
+        <v>446252</v>
       </c>
       <c r="R123" t="n">
         <v>7026536</v>
@@ -16691,7 +16692,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16701,7 +16702,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16710,13 +16711,12 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -16749,10 +16749,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252840</v>
+        <v>121252818</v>
       </c>
       <c r="B124" t="n">
-        <v>77546</v>
+        <v>74527</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16761,25 +16761,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -16792,7 +16792,7 @@
         <v>446209</v>
       </c>
       <c r="R124" t="n">
-        <v>7026394</v>
+        <v>7026630</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -12395,10 +12395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252810</v>
+        <v>121252807</v>
       </c>
       <c r="B91" t="n">
-        <v>74701</v>
+        <v>78609</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12407,25 +12407,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>446089</v>
+        <v>446038</v>
       </c>
       <c r="R91" t="n">
-        <v>7026536</v>
+        <v>7026546</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12489,13 +12489,12 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -12510,7 +12509,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12528,10 +12527,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252827</v>
+        <v>121252811</v>
       </c>
       <c r="B92" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12544,21 +12543,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12568,10 +12567,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>446252</v>
+        <v>446106</v>
       </c>
       <c r="R92" t="n">
-        <v>7026536</v>
+        <v>7026528</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12603,7 +12602,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12613,7 +12612,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12627,7 +12626,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>i gammal granskog</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -12642,7 +12641,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12660,10 +12659,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252814</v>
+        <v>121252802</v>
       </c>
       <c r="B93" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12676,21 +12675,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12700,10 +12699,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>446185</v>
+        <v>445982</v>
       </c>
       <c r="R93" t="n">
-        <v>7026627</v>
+        <v>7026514</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12735,7 +12734,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12745,7 +12744,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12759,7 +12758,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -12774,7 +12773,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12792,10 +12791,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121252840</v>
+        <v>121252812</v>
       </c>
       <c r="B94" t="n">
-        <v>77546</v>
+        <v>78609</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12808,21 +12807,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12832,10 +12831,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>446209</v>
+        <v>446185</v>
       </c>
       <c r="R94" t="n">
-        <v>7026394</v>
+        <v>7026655</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12867,7 +12866,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12877,7 +12876,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12891,7 +12890,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -12906,7 +12905,7 @@
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12924,10 +12923,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121252808</v>
+        <v>121252801</v>
       </c>
       <c r="B95" t="n">
-        <v>78643</v>
+        <v>91403</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12936,47 +12935,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>185</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>446038</v>
+        <v>445969</v>
       </c>
       <c r="R95" t="n">
-        <v>7026546</v>
+        <v>7026495</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13008,7 +12998,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13018,7 +13008,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13032,7 +13022,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -13047,7 +13037,7 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13065,10 +13055,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121252804</v>
+        <v>121252820</v>
       </c>
       <c r="B96" t="n">
-        <v>97118</v>
+        <v>74715</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13077,25 +13067,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221063</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -13105,10 +13095,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>446013</v>
+        <v>446258</v>
       </c>
       <c r="R96" t="n">
-        <v>7026514</v>
+        <v>7026597</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13140,7 +13130,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13150,7 +13140,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13167,9 +13157,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121252837</v>
+        <v>121252822</v>
       </c>
       <c r="B97" t="n">
-        <v>77546</v>
+        <v>78609</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13203,21 +13203,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>446201</v>
+        <v>446284</v>
       </c>
       <c r="R97" t="n">
-        <v>7026410</v>
+        <v>7026552</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13319,7 +13319,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121252833</v>
+        <v>121252821</v>
       </c>
       <c r="B98" t="n">
         <v>78609</v>
@@ -13352,26 +13352,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>446233</v>
+        <v>446282</v>
       </c>
       <c r="R98" t="n">
-        <v>7026512</v>
+        <v>7026592</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13403,7 +13394,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13413,12 +13404,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13447,7 +13433,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13465,10 +13451,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121252821</v>
+        <v>121252818</v>
       </c>
       <c r="B99" t="n">
-        <v>78609</v>
+        <v>74527</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13477,25 +13463,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -13505,10 +13491,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>446282</v>
+        <v>446209</v>
       </c>
       <c r="R99" t="n">
-        <v>7026592</v>
+        <v>7026630</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13540,7 +13526,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13550,7 +13536,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13564,7 +13550,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -13579,7 +13565,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13597,10 +13583,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121252826</v>
+        <v>121252815</v>
       </c>
       <c r="B100" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13613,34 +13599,43 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>446279</v>
+        <v>446189</v>
       </c>
       <c r="R100" t="n">
-        <v>7026520</v>
+        <v>7026651</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13672,7 +13667,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13682,7 +13677,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13696,22 +13691,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13729,7 +13709,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121252819</v>
+        <v>121252809</v>
       </c>
       <c r="B101" t="n">
         <v>77546</v>
@@ -13769,10 +13749,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>446258</v>
+        <v>446044</v>
       </c>
       <c r="R101" t="n">
-        <v>7026597</v>
+        <v>7026549</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13804,7 +13784,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13814,7 +13794,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13828,7 +13808,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13843,7 +13823,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13861,10 +13841,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121252839</v>
+        <v>121252800</v>
       </c>
       <c r="B102" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13877,34 +13857,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>446209</v>
+        <v>446056</v>
       </c>
       <c r="R102" t="n">
-        <v>7026395</v>
+        <v>7026521</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13936,7 +13921,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13946,7 +13931,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13960,22 +13950,12 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>Gammal gran med ringhack</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13993,10 +13973,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121252800</v>
+        <v>121252840</v>
       </c>
       <c r="B103" t="n">
-        <v>57356</v>
+        <v>77546</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -14009,39 +13989,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>446056</v>
+        <v>446209</v>
       </c>
       <c r="R103" t="n">
-        <v>7026521</v>
+        <v>7026394</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -14073,7 +14048,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14083,12 +14058,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14102,12 +14072,22 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid dike</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Gammal gran med ringhack</t>
+          <t>På bark på stam av levande gammal gran (29 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14125,10 +14105,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121252836</v>
+        <v>121252810</v>
       </c>
       <c r="B104" t="n">
-        <v>78609</v>
+        <v>74701</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14137,25 +14117,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -14165,10 +14145,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>446201</v>
+        <v>446089</v>
       </c>
       <c r="R104" t="n">
-        <v>7026410</v>
+        <v>7026536</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14200,7 +14180,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14210,7 +14190,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14219,6 +14199,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -14239,7 +14220,7 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14257,10 +14238,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252802</v>
+        <v>121252839</v>
       </c>
       <c r="B105" t="n">
-        <v>90716</v>
+        <v>90738</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14273,21 +14254,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -14297,10 +14278,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445982</v>
+        <v>446209</v>
       </c>
       <c r="R105" t="n">
-        <v>7026514</v>
+        <v>7026395</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14332,7 +14313,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14342,7 +14323,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14356,7 +14337,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -14371,7 +14352,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14389,10 +14370,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121252815</v>
+        <v>121252830</v>
       </c>
       <c r="B106" t="n">
-        <v>57509</v>
+        <v>74715</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14405,43 +14386,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>446189</v>
+        <v>446252</v>
       </c>
       <c r="R106" t="n">
-        <v>7026651</v>
+        <v>7026536</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14473,7 +14445,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14483,7 +14455,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14497,7 +14469,22 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14515,10 +14502,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121252835</v>
+        <v>121252833</v>
       </c>
       <c r="B107" t="n">
-        <v>77993</v>
+        <v>78609</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14531,34 +14518,43 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>446209</v>
+        <v>446233</v>
       </c>
       <c r="R107" t="n">
-        <v>7026444</v>
+        <v>7026512</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14590,7 +14586,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14600,7 +14596,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14614,22 +14615,22 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>I gammal sumpskog/myr</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14647,10 +14648,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252820</v>
+        <v>121252814</v>
       </c>
       <c r="B108" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14663,21 +14664,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14687,10 +14688,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>446258</v>
+        <v>446185</v>
       </c>
       <c r="R108" t="n">
-        <v>7026597</v>
+        <v>7026627</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14722,7 +14723,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14732,7 +14733,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14746,7 +14747,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -14761,7 +14762,7 @@
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14779,10 +14780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252838</v>
+        <v>121252823</v>
       </c>
       <c r="B109" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14795,21 +14796,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14819,10 +14820,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446201</v>
+        <v>446274</v>
       </c>
       <c r="R109" t="n">
-        <v>7026410</v>
+        <v>7026540</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14854,7 +14855,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14864,7 +14865,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14878,7 +14879,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -14893,7 +14894,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14911,10 +14912,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121252801</v>
+        <v>121252838</v>
       </c>
       <c r="B110" t="n">
-        <v>91403</v>
+        <v>74715</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14923,25 +14924,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -14951,10 +14952,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445969</v>
+        <v>446201</v>
       </c>
       <c r="R110" t="n">
-        <v>7026495</v>
+        <v>7026410</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14986,7 +14987,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14996,7 +14997,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -15025,7 +15026,7 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (40 cm dbh) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15043,7 +15044,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121252812</v>
+        <v>121252826</v>
       </c>
       <c r="B111" t="n">
         <v>78609</v>
@@ -15083,10 +15084,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>446185</v>
+        <v>446279</v>
       </c>
       <c r="R111" t="n">
-        <v>7026655</v>
+        <v>7026520</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15118,7 +15119,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15128,7 +15129,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15142,7 +15143,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -15157,7 +15158,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran, 13 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (26 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15175,10 +15176,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121252807</v>
+        <v>121252817</v>
       </c>
       <c r="B112" t="n">
-        <v>78609</v>
+        <v>74699</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15187,25 +15188,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -15215,10 +15216,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>446038</v>
+        <v>446209</v>
       </c>
       <c r="R112" t="n">
-        <v>7026546</v>
+        <v>7026630</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15250,7 +15251,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -15260,7 +15261,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15274,7 +15275,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -15289,7 +15290,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På ved på gammal granhögstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15307,10 +15308,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121252822</v>
+        <v>121252806</v>
       </c>
       <c r="B113" t="n">
-        <v>78609</v>
+        <v>74527</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15319,25 +15320,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -15347,10 +15348,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>446284</v>
+        <v>446038</v>
       </c>
       <c r="R113" t="n">
-        <v>7026552</v>
+        <v>7026546</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15382,7 +15383,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -15392,7 +15393,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15406,7 +15407,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -15421,7 +15422,7 @@
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15439,7 +15440,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121252824</v>
+        <v>121252837</v>
       </c>
       <c r="B114" t="n">
         <v>77546</v>
@@ -15479,10 +15480,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>446278</v>
+        <v>446201</v>
       </c>
       <c r="R114" t="n">
-        <v>7026536</v>
+        <v>7026410</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15514,7 +15515,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -15524,7 +15525,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15538,7 +15539,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -15553,7 +15554,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15571,10 +15572,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121252817</v>
+        <v>121252824</v>
       </c>
       <c r="B115" t="n">
-        <v>74699</v>
+        <v>77546</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15583,25 +15584,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15611,10 +15612,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446209</v>
+        <v>446278</v>
       </c>
       <c r="R115" t="n">
-        <v>7026630</v>
+        <v>7026536</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15646,7 +15647,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15656,7 +15657,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15670,7 +15671,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -15685,7 +15686,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15703,10 +15704,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121252823</v>
+        <v>121252803</v>
       </c>
       <c r="B116" t="n">
-        <v>78609</v>
+        <v>105195</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15715,25 +15716,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15743,10 +15744,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446274</v>
+        <v>446013</v>
       </c>
       <c r="R116" t="n">
-        <v>7026540</v>
+        <v>7026516</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15778,7 +15779,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15788,7 +15789,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15802,22 +15803,12 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15835,10 +15826,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121252825</v>
+        <v>121252808</v>
       </c>
       <c r="B117" t="n">
-        <v>78865</v>
+        <v>78643</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15847,38 +15838,47 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6459</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446278</v>
+        <v>446038</v>
       </c>
       <c r="R117" t="n">
-        <v>7026536</v>
+        <v>7026546</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15967,10 +15967,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121252806</v>
+        <v>121252835</v>
       </c>
       <c r="B118" t="n">
-        <v>74527</v>
+        <v>77993</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15979,25 +15979,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6428</v>
+        <v>6437</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -16007,10 +16007,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>446038</v>
+        <v>446209</v>
       </c>
       <c r="R118" t="n">
-        <v>7026546</v>
+        <v>7026444</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16066,22 +16066,22 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>I gammal sumpskog/myr</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På ved på gammal död tall (11 cm dbh, över 200 år) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16099,10 +16099,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121252803</v>
+        <v>121252836</v>
       </c>
       <c r="B119" t="n">
-        <v>105195</v>
+        <v>78609</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16111,25 +16111,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -16139,10 +16139,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446013</v>
+        <v>446201</v>
       </c>
       <c r="R119" t="n">
-        <v>7026516</v>
+        <v>7026410</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16201,9 +16201,19 @@
           <t>I gammal granskog</t>
         </is>
       </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På döda grenar på levande gammal gran (28 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16221,10 +16231,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121252809</v>
+        <v>121252804</v>
       </c>
       <c r="B120" t="n">
-        <v>77546</v>
+        <v>97118</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16233,25 +16243,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228579</v>
+        <v>221063</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -16261,10 +16271,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446044</v>
+        <v>446013</v>
       </c>
       <c r="R120" t="n">
-        <v>7026549</v>
+        <v>7026514</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16296,7 +16306,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -16306,7 +16316,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16320,22 +16330,12 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16353,10 +16353,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121252811</v>
+        <v>121252819</v>
       </c>
       <c r="B121" t="n">
-        <v>90716</v>
+        <v>77546</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -16369,21 +16369,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -16393,10 +16393,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>446106</v>
+        <v>446258</v>
       </c>
       <c r="R121" t="n">
-        <v>7026528</v>
+        <v>7026597</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16452,7 +16452,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16485,10 +16485,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121252813</v>
+        <v>121252825</v>
       </c>
       <c r="B122" t="n">
-        <v>78609</v>
+        <v>78865</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -16497,25 +16497,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -16525,10 +16525,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>446166</v>
+        <v>446278</v>
       </c>
       <c r="R122" t="n">
-        <v>7026698</v>
+        <v>7026536</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (20 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16617,10 +16617,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121252830</v>
+        <v>121252813</v>
       </c>
       <c r="B123" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16633,21 +16633,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -16657,10 +16657,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446252</v>
+        <v>446166</v>
       </c>
       <c r="R123" t="n">
-        <v>7026536</v>
+        <v>7026698</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal död gran, 8 cm dbh, ca 170 år gammal # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -16749,10 +16749,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121252818</v>
+        <v>121252827</v>
       </c>
       <c r="B124" t="n">
-        <v>74527</v>
+        <v>78609</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16761,25 +16761,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -16789,10 +16789,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>446209</v>
+        <v>446252</v>
       </c>
       <c r="R124" t="n">
-        <v>7026630</v>
+        <v>7026536</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -12395,10 +12395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121252807</v>
+        <v>121252811</v>
       </c>
       <c r="B91" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12411,21 +12411,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>446038</v>
+        <v>446106</v>
       </c>
       <c r="R91" t="n">
-        <v>7026546</v>
+        <v>7026528</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>I gammal granskog vid bäckar och källor</t>
+          <t>i gammal granskog</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På gammal död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12527,7 +12527,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121252811</v>
+        <v>121252802</v>
       </c>
       <c r="B92" t="n">
         <v>90716</v>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>446106</v>
+        <v>445982</v>
       </c>
       <c r="R92" t="n">
-        <v>7026528</v>
+        <v>7026514</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På gammal död gran # Picea abies</t>
+          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12659,10 +12659,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121252802</v>
+        <v>121252807</v>
       </c>
       <c r="B93" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12675,21 +12675,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445982</v>
+        <v>446038</v>
       </c>
       <c r="R93" t="n">
-        <v>7026514</v>
+        <v>7026546</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal granskog vid bäckar och källor</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (60 cm dbh) # Picea abies</t>
+          <t>På döda grenar på gammal gran (29 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -14105,10 +14105,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121252810</v>
+        <v>121252830</v>
       </c>
       <c r="B104" t="n">
-        <v>74701</v>
+        <v>74715</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14117,25 +14117,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>306</v>
+        <v>6440</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -14145,7 +14145,7 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>446089</v>
+        <v>446252</v>
       </c>
       <c r="R104" t="n">
         <v>7026536</v>
@@ -14180,7 +14180,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14199,13 +14199,12 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -14220,7 +14219,7 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
+          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14238,10 +14237,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121252839</v>
+        <v>121252833</v>
       </c>
       <c r="B105" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14254,34 +14253,43 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>446209</v>
+        <v>446233</v>
       </c>
       <c r="R105" t="n">
-        <v>7026395</v>
+        <v>7026512</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14313,7 +14321,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14323,7 +14331,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Längsta bål 50 cm</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14337,7 +14350,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>I gammal granskog vid dike</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -14352,7 +14365,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14370,10 +14383,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121252830</v>
+        <v>121252814</v>
       </c>
       <c r="B106" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14386,21 +14399,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -14410,10 +14423,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>446252</v>
+        <v>446185</v>
       </c>
       <c r="R106" t="n">
-        <v>7026536</v>
+        <v>7026627</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14445,7 +14458,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14455,7 +14468,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14469,7 +14482,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -14484,7 +14497,7 @@
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>På bark på stam av gammal levande gran (14 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14502,7 +14515,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121252833</v>
+        <v>121252823</v>
       </c>
       <c r="B107" t="n">
         <v>78609</v>
@@ -14535,26 +14548,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>446233</v>
+        <v>446274</v>
       </c>
       <c r="R107" t="n">
-        <v>7026512</v>
+        <v>7026540</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14586,7 +14590,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14596,12 +14600,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Längsta bål 50 cm</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14630,7 +14629,7 @@
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (37 cm dbh, ca 170 år gammal) # Picea abies</t>
+          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14648,10 +14647,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121252814</v>
+        <v>121252810</v>
       </c>
       <c r="B108" t="n">
-        <v>78609</v>
+        <v>74701</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14660,25 +14659,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14688,10 +14687,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>446185</v>
+        <v>446089</v>
       </c>
       <c r="R108" t="n">
-        <v>7026627</v>
+        <v>7026536</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14723,7 +14722,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14733,7 +14732,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14742,12 +14741,13 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran # Picea abies</t>
+          <t>På gammal död granhögstubbe (50 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14780,10 +14780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121252823</v>
+        <v>121252839</v>
       </c>
       <c r="B109" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14796,21 +14796,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14820,10 +14820,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>446274</v>
+        <v>446209</v>
       </c>
       <c r="R109" t="n">
-        <v>7026540</v>
+        <v>7026395</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14855,7 +14855,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>I gammal granskog vid dike</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran (40 cm dbh, ca 150 år gammal) # Picea abies</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 150 år gammal) # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -16884,7 +16884,7 @@
         <v>121499846</v>
       </c>
       <c r="B125" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 59464-2023 artfynd.xlsx
+++ b/artfynd/A 59464-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115025770</v>
+        <v>121134869</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alsen (Ede, Alsen), Jmt</t>
+          <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446267</v>
+        <v>446262</v>
       </c>
       <c r="R2" t="n">
-        <v>7026383</v>
+        <v>7026488</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -790,63 +795,52 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115026106</v>
+        <v>121134870</v>
       </c>
       <c r="B3" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Alsen, Mellan Svedaunsmyran och Svedaun (Alsen, Mellan Svedaunsmyran och Svedaun), Jmt</t>
+          <t>Djuprönningen, 0,7-1 km v. om Edestjärnen, 2,5 km SSV Alsens kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446276</v>
+        <v>446262</v>
       </c>
       <c r="R3" t="n">
-        <v>7026426</v>
+        <v>7026488</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,27 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med spillning här, misstänker tjäderspelplats</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +893,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>I gammal gransumpskog med tall och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>På granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -920,54 +929,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115025966</v>
+        <v>115222635</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svedaunsmyren (Svedaunsmyren), Jmt</t>
+          <t>Alsen, Alsen, Mellan Svedaunsmyran och Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446256</v>
+        <v>446216</v>
       </c>
       <c r="R4" t="n">
-        <v>7026389</v>
+        <v>7026596</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +1003,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1001,7 +1013,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1009,6 +1021,11 @@
           <t>10:42</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal död gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1035,79 +1052,78 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115026112</v>
+        <v>115025601</v>
       </c>
       <c r="B5" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svedaunsmyren (Svedaunsmyren), Jmt</t>
+          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446240</v>
+        <v>446269</v>
       </c>
       <c r="R5" t="n">
-        <v>7026472</v>
+        <v>7026379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,7 +1155,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,12 +1165,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Under tall</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,6 +1176,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1174,26 +1205,21 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115026041</v>
+        <v>115025966</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1214,27 +1240,18 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Alsen (Alsen, Mellan Svedaunsmyran och Svedaun), Jmt</t>
+          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446269</v>
+        <v>446256</v>
       </c>
       <c r="R6" t="n">
-        <v>7026418</v>
+        <v>7026389</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,7 +1283,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1276,12 +1293,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal gran, över 150 år</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1321,31 +1333,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115025601</v>
+        <v>115026009</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1368,7 +1375,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1379,14 +1386,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svedaunsmyren (Svedaunsmyren), Jmt</t>
+          <t>Svedaunsmyren, Svedaunsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446269</v>
+        <v>446293</v>
       </c>
       <c r="R7" t="n">
-        <v>7026379</v>
+        <v>7026426</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,7 +1425,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1428,7 +1435,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1440,6 +1447,11 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>gran</